--- a/artfynd/A 35482-2025 artfynd.xlsx
+++ b/artfynd/A 35482-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1746,6 +1746,989 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127473274</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>443961</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6766739</v>
+      </c>
+      <c r="S11" t="n">
+        <v>9</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På 8 tallstammar</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127471682</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ilbäcken, Ilbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>443986</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6766603</v>
+      </c>
+      <c r="S12" t="n">
+        <v>9</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127473637</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Oxeråsbäcken, Oxeråsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>444013</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6766733</v>
+      </c>
+      <c r="S13" t="n">
+        <v>9</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På tallstammen flera</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127473199</v>
+      </c>
+      <c r="B14" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>443957</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6766708</v>
+      </c>
+      <c r="S14" t="n">
+        <v>9</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127473038</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>443877</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6766678</v>
+      </c>
+      <c r="S15" t="n">
+        <v>9</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127472077</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ilbäcken, Ilbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>443939</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6766640</v>
+      </c>
+      <c r="S16" t="n">
+        <v>9</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127467710</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>443823</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6766604</v>
+      </c>
+      <c r="S17" t="n">
+        <v>9</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127473294</v>
+      </c>
+      <c r="B18" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>443964</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6766733</v>
+      </c>
+      <c r="S18" t="n">
+        <v>9</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127471795</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Ilbäcken, Ilbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>443980</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6766599</v>
+      </c>
+      <c r="S19" t="n">
+        <v>9</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35482-2025 artfynd.xlsx
+++ b/artfynd/A 35482-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1751,7 +1751,7 @@
         <v>127473274</v>
       </c>
       <c r="B11" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>127471682</v>
       </c>
       <c r="B12" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>127473637</v>
       </c>
       <c r="B13" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>127473199</v>
       </c>
       <c r="B14" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>127473038</v>
       </c>
       <c r="B15" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>127472077</v>
       </c>
       <c r="B16" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         <v>127467710</v>
       </c>
       <c r="B17" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>127473294</v>
       </c>
       <c r="B18" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>127471795</v>
       </c>
       <c r="B19" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2728,6 +2728,8191 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127620991</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>443391</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6766953</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127619035</v>
+      </c>
+      <c r="B21" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>443270</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6767248</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>127618950</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>443268</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6767266</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>127606899</v>
+      </c>
+      <c r="B23" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>443830</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6766958</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>127613169</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>443649</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6767135</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På 3 tallstammar</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>127618623</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>443293</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6767447</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>127618438</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>443259</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6767420</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>127608276</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>443801</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6767090</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På 3 tallstammar</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>127619053</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>443270</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6767248</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>127618987</v>
+      </c>
+      <c r="B29" t="n">
+        <v>56853</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>443268</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6767266</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>127618680</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>443307</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6767347</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>127608356</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>443663</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6767132</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På 3 tallstammar</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>127621213</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>443486</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6766960</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>127619291</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>443357</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6767070</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På 5 tallstammar</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>127618880</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>443282</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6767309</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Har ant. ätit dubbelögda bastborre</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>127613386</v>
+      </c>
+      <c r="B35" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>443311</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6767409</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>127618701</v>
+      </c>
+      <c r="B36" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>443327</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6767322</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>1 låga och 3 torraka</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>127618637</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>443286</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6767436</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>127608027</v>
+      </c>
+      <c r="B38" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>443898</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6766974</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>127606633</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>443864</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6766815</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På 5 tallstammar</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>127613359</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>443350</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6767430</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På 3 tallstammar</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>127608263</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>443820</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6767096</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På 3 tallstammar</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>127618474</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>443254</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6767417</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>127608047</v>
+      </c>
+      <c r="B43" t="n">
+        <v>78776</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>443798</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6767031</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>127608039</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>443868</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6766980</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På 3 tallstammar</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>127619167</v>
+      </c>
+      <c r="B45" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>443339</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6767141</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På raka</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>127618548</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>443265</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6767455</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>127618485</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>443251</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6767415</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>127621072</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>443404</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6766973</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På 3 tallstammar</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>127621265</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>443543</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6766974</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>127613428</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>443272</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6767422</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>127618557</v>
+      </c>
+      <c r="B51" t="n">
+        <v>78777</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>443265</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6767455</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>127608059</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>443812</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6767031</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>127618673</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>443294</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6767362</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>127621090</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>443420</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6767000</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>På 3 tallstammar</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>127620953</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>443383</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6766953</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>127618689</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>443307</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6767350</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>127620831</v>
+      </c>
+      <c r="B57" t="n">
+        <v>43939</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>443380</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6767035</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>127618707</v>
+      </c>
+      <c r="B58" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>443350</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6767334</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>På torraka</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>127618512</v>
+      </c>
+      <c r="B59" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>443254</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6767421</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>127618534</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>443258</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6767430</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>På 2 tallstammar</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>127618554</v>
+      </c>
+      <c r="B61" t="n">
+        <v>78776</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>443265</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6767455</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>127608048</v>
+      </c>
+      <c r="B62" t="n">
+        <v>78777</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>443798</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6767031</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>127621155</v>
+      </c>
+      <c r="B63" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>443504</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6766983</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>127606882</v>
+      </c>
+      <c r="B64" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>443860</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6766863</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>127621194</v>
+      </c>
+      <c r="B65" t="n">
+        <v>57821</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>443486</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6766960</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>127621185</v>
+      </c>
+      <c r="B66" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>443486</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6766960</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>127620944</v>
+      </c>
+      <c r="B67" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>443383</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6766978</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På 5 tallstammar</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>127618716</v>
+      </c>
+      <c r="B68" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>443350</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6767334</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>127618658</v>
+      </c>
+      <c r="B69" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>443286</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6767436</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>På tallraka</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>127619056</v>
+      </c>
+      <c r="B70" t="n">
+        <v>57658</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>443270</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6767248</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>127608037</v>
+      </c>
+      <c r="B71" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>443868</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6766980</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>127608339</v>
+      </c>
+      <c r="B72" t="n">
+        <v>91350</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>443750</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6767090</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>127606827</v>
+      </c>
+      <c r="B73" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>443866</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6766858</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>127606796</v>
+      </c>
+      <c r="B74" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>443860</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6766854</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>127619016</v>
+      </c>
+      <c r="B75" t="n">
+        <v>78776</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>443270</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6767260</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>127619038</v>
+      </c>
+      <c r="B76" t="n">
+        <v>4773</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>443270</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6767248</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>127621131</v>
+      </c>
+      <c r="B77" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>443495</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6766975</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>På tall och gran rikligt</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>127619183</v>
+      </c>
+      <c r="B78" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>443347</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6767103</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>På låga</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>127619312</v>
+      </c>
+      <c r="B79" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>443370</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6767060</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>På 3 tallstammar</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>127619158</v>
+      </c>
+      <c r="B80" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>443344</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6767154</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>På raka</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>127618895</v>
+      </c>
+      <c r="B81" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>443282</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6767309</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>127618498</v>
+      </c>
+      <c r="B82" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>443249</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6767415</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>På 3 tallstammar</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>127618615</v>
+      </c>
+      <c r="B83" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>443293</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6767447</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>127618897</v>
+      </c>
+      <c r="B84" t="n">
+        <v>58031</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>443282</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6767309</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>127620818</v>
+      </c>
+      <c r="B85" t="n">
+        <v>78776</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>443357</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6767054</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>127621268</v>
+      </c>
+      <c r="B86" t="n">
+        <v>78776</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>443543</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6766974</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>127621011</v>
+      </c>
+      <c r="B87" t="n">
+        <v>78776</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>443400</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6766956</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF87" t="inlineStr"/>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>127618762</v>
+      </c>
+      <c r="B88" t="n">
+        <v>92620</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>443291</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6767297</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Förra årets Fkr.</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF88" t="inlineStr"/>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>127618666</v>
+      </c>
+      <c r="B89" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>443292</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6767366</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>På 2 tallstammar</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF89" t="inlineStr"/>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>127613349</v>
+      </c>
+      <c r="B90" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>443363</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6767418</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF90" t="inlineStr"/>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>127606939</v>
+      </c>
+      <c r="B91" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>443852</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6766955</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>På 9 tallstammar</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF91" t="inlineStr"/>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>127608341</v>
+      </c>
+      <c r="B92" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>443750</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6767090</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF92" t="inlineStr"/>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>127613395</v>
+      </c>
+      <c r="B93" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>443299</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6767410</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF93" t="inlineStr"/>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>127608010</v>
+      </c>
+      <c r="B94" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>443876</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6766959</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF94" t="inlineStr"/>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>127619059</v>
+      </c>
+      <c r="B95" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>443270</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6767248</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF95" t="inlineStr"/>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>127613400</v>
+      </c>
+      <c r="B96" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>443299</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6767410</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>På 2 tallstammar</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF96" t="inlineStr"/>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>127613372</v>
+      </c>
+      <c r="B97" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>443331</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6767409</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF97" t="inlineStr"/>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35482-2025 artfynd.xlsx
+++ b/artfynd/A 35482-2025 artfynd.xlsx
@@ -2837,43 +2837,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127619035</v>
+        <v>127613169</v>
       </c>
       <c r="B21" t="n">
-        <v>5177</v>
+        <v>79018</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2881,10 +2875,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>443270</v>
+        <v>443649</v>
       </c>
       <c r="R21" t="n">
-        <v>6767248</v>
+        <v>6767135</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2917,6 +2911,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På 3 tallstammar</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3054,10 +3053,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127606899</v>
+        <v>127619035</v>
       </c>
       <c r="B23" t="n">
-        <v>8450</v>
+        <v>5177</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3065,21 +3064,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3088,7 +3087,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3098,10 +3097,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>443830</v>
+        <v>443270</v>
       </c>
       <c r="R23" t="n">
-        <v>6766958</v>
+        <v>6767248</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3161,37 +3160,43 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127613169</v>
+        <v>127606899</v>
       </c>
       <c r="B24" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3199,10 +3204,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>443649</v>
+        <v>443830</v>
       </c>
       <c r="R24" t="n">
-        <v>6767135</v>
+        <v>6766958</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3235,11 +3240,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På 3 tallstammar</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3267,10 +3267,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127618623</v>
+        <v>127619053</v>
       </c>
       <c r="B25" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3278,26 +3278,31 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3305,10 +3310,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>443293</v>
+        <v>443270</v>
       </c>
       <c r="R25" t="n">
-        <v>6767447</v>
+        <v>6767248</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3349,7 +3354,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3368,37 +3372,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127618438</v>
+        <v>127618987</v>
       </c>
       <c r="B26" t="n">
-        <v>79018</v>
+        <v>56853</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3406,10 +3423,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>443259</v>
+        <v>443268</v>
       </c>
       <c r="R26" t="n">
-        <v>6767420</v>
+        <v>6767266</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3450,7 +3467,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3469,7 +3485,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127608276</v>
+        <v>127618623</v>
       </c>
       <c r="B27" t="n">
         <v>79018</v>
@@ -3507,10 +3523,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>443801</v>
+        <v>443293</v>
       </c>
       <c r="R27" t="n">
-        <v>6767090</v>
+        <v>6767447</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3543,11 +3559,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På 3 tallstammar</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3575,10 +3586,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127619053</v>
+        <v>127608276</v>
       </c>
       <c r="B28" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3586,31 +3597,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3618,10 +3624,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>443270</v>
+        <v>443801</v>
       </c>
       <c r="R28" t="n">
-        <v>6767248</v>
+        <v>6767090</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3656,12 +3662,18 @@
           <t>2025-08-14</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På 3 tallstammar</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3680,50 +3692,37 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127618987</v>
+        <v>127618438</v>
       </c>
       <c r="B29" t="n">
-        <v>56853</v>
+        <v>79018</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3731,10 +3730,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>443268</v>
+        <v>443259</v>
       </c>
       <c r="R29" t="n">
-        <v>6767266</v>
+        <v>6767420</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3775,6 +3774,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4000,10 +4000,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127621213</v>
+        <v>127619291</v>
       </c>
       <c r="B32" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4011,31 +4011,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4043,10 +4038,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>443486</v>
+        <v>443357</v>
       </c>
       <c r="R32" t="n">
-        <v>6766960</v>
+        <v>6767070</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4083,7 +4078,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På 5 tallstammar</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4092,6 +4087,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4110,10 +4106,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127619291</v>
+        <v>127621213</v>
       </c>
       <c r="B33" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4121,26 +4117,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4148,10 +4149,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>443357</v>
+        <v>443486</v>
       </c>
       <c r="R33" t="n">
-        <v>6767070</v>
+        <v>6766960</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4188,7 +4189,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På 5 tallstammar</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4197,7 +4198,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4433,43 +4433,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127618701</v>
+        <v>127606633</v>
       </c>
       <c r="B36" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4477,10 +4471,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>443327</v>
+        <v>443864</v>
       </c>
       <c r="R36" t="n">
-        <v>6767322</v>
+        <v>6766815</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4517,7 +4511,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>1 låga och 3 torraka</t>
+          <t>På 5 tallstammar</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4646,43 +4640,37 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127608027</v>
+        <v>127608263</v>
       </c>
       <c r="B38" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4690,10 +4678,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>443898</v>
+        <v>443820</v>
       </c>
       <c r="R38" t="n">
-        <v>6766974</v>
+        <v>6767096</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4726,6 +4714,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På 3 tallstammar</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4753,7 +4746,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127606633</v>
+        <v>127613359</v>
       </c>
       <c r="B39" t="n">
         <v>79018</v>
@@ -4791,10 +4784,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>443864</v>
+        <v>443350</v>
       </c>
       <c r="R39" t="n">
-        <v>6766815</v>
+        <v>6767430</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4831,7 +4824,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På 5 tallstammar</t>
+          <t>På 3 tallstammar</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4859,37 +4852,43 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127613359</v>
+        <v>127608027</v>
       </c>
       <c r="B40" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4897,10 +4896,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>443350</v>
+        <v>443898</v>
       </c>
       <c r="R40" t="n">
-        <v>6767430</v>
+        <v>6766974</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4933,11 +4932,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På 3 tallstammar</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4965,37 +4959,43 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127608263</v>
+        <v>127618701</v>
       </c>
       <c r="B41" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5003,10 +5003,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>443820</v>
+        <v>443327</v>
       </c>
       <c r="R41" t="n">
-        <v>6767096</v>
+        <v>6767322</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5043,7 +5043,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På 3 tallstammar</t>
+          <t>1 låga och 3 torraka</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5071,10 +5071,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127618474</v>
+        <v>127608047</v>
       </c>
       <c r="B42" t="n">
-        <v>79018</v>
+        <v>78776</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5082,21 +5082,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5109,10 +5109,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>443254</v>
+        <v>443798</v>
       </c>
       <c r="R42" t="n">
-        <v>6767417</v>
+        <v>6767031</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5172,10 +5172,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127608047</v>
+        <v>127618474</v>
       </c>
       <c r="B43" t="n">
-        <v>78776</v>
+        <v>79018</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5183,21 +5183,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5210,10 +5210,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>443798</v>
+        <v>443254</v>
       </c>
       <c r="R43" t="n">
-        <v>6767031</v>
+        <v>6767417</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5491,7 +5491,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127618548</v>
+        <v>127618485</v>
       </c>
       <c r="B46" t="n">
         <v>79018</v>
@@ -5529,10 +5529,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>443265</v>
+        <v>443251</v>
       </c>
       <c r="R46" t="n">
-        <v>6767455</v>
+        <v>6767415</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5592,7 +5592,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127618485</v>
+        <v>127618548</v>
       </c>
       <c r="B47" t="n">
         <v>79018</v>
@@ -5630,10 +5630,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>443251</v>
+        <v>443265</v>
       </c>
       <c r="R47" t="n">
-        <v>6767415</v>
+        <v>6767455</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5693,7 +5693,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127621072</v>
+        <v>127618673</v>
       </c>
       <c r="B48" t="n">
         <v>79018</v>
@@ -5731,10 +5731,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>443404</v>
+        <v>443294</v>
       </c>
       <c r="R48" t="n">
-        <v>6766973</v>
+        <v>6767362</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5767,11 +5767,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På 3 tallstammar</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5799,7 +5794,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127621265</v>
+        <v>127613428</v>
       </c>
       <c r="B49" t="n">
         <v>79018</v>
@@ -5837,10 +5832,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>443543</v>
+        <v>443272</v>
       </c>
       <c r="R49" t="n">
-        <v>6766974</v>
+        <v>6767422</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5900,7 +5895,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127613428</v>
+        <v>127621265</v>
       </c>
       <c r="B50" t="n">
         <v>79018</v>
@@ -5938,10 +5933,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>443272</v>
+        <v>443543</v>
       </c>
       <c r="R50" t="n">
-        <v>6767422</v>
+        <v>6766974</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6001,10 +5996,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127618557</v>
+        <v>127621072</v>
       </c>
       <c r="B51" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6012,21 +6007,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6039,10 +6034,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>443265</v>
+        <v>443404</v>
       </c>
       <c r="R51" t="n">
-        <v>6767455</v>
+        <v>6766973</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6075,6 +6070,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På 3 tallstammar</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6203,10 +6203,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127618673</v>
+        <v>127618557</v>
       </c>
       <c r="B53" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6214,21 +6214,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6241,10 +6241,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>443294</v>
+        <v>443265</v>
       </c>
       <c r="R53" t="n">
-        <v>6767362</v>
+        <v>6767455</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6612,43 +6612,37 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127620831</v>
+        <v>127618534</v>
       </c>
       <c r="B57" t="n">
-        <v>43939</v>
+        <v>79018</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>101735</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6656,10 +6650,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>443380</v>
+        <v>443258</v>
       </c>
       <c r="R57" t="n">
-        <v>6767035</v>
+        <v>6767430</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6692,6 +6686,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>På 2 tallstammar</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6719,7 +6718,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127618707</v>
+        <v>127618512</v>
       </c>
       <c r="B58" t="n">
         <v>8450</v>
@@ -6763,10 +6762,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>443350</v>
+        <v>443254</v>
       </c>
       <c r="R58" t="n">
-        <v>6767334</v>
+        <v>6767421</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6799,11 +6798,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>På torraka</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6831,7 +6825,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127618512</v>
+        <v>127618707</v>
       </c>
       <c r="B59" t="n">
         <v>8450</v>
@@ -6875,10 +6869,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>443254</v>
+        <v>443350</v>
       </c>
       <c r="R59" t="n">
-        <v>6767421</v>
+        <v>6767334</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6911,6 +6905,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>På torraka</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6938,37 +6937,43 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127618534</v>
+        <v>127620831</v>
       </c>
       <c r="B60" t="n">
-        <v>79018</v>
+        <v>43939</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>101735</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6976,10 +6981,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>443258</v>
+        <v>443380</v>
       </c>
       <c r="R60" t="n">
-        <v>6767430</v>
+        <v>6767035</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7012,11 +7017,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>På 2 tallstammar</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7044,10 +7044,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127618554</v>
+        <v>127608048</v>
       </c>
       <c r="B61" t="n">
-        <v>78776</v>
+        <v>78777</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7055,21 +7055,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7082,10 +7082,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>443265</v>
+        <v>443798</v>
       </c>
       <c r="R61" t="n">
-        <v>6767455</v>
+        <v>6767031</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7145,10 +7145,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127608048</v>
+        <v>127621155</v>
       </c>
       <c r="B62" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7156,21 +7156,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7183,10 +7183,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>443798</v>
+        <v>443504</v>
       </c>
       <c r="R62" t="n">
-        <v>6767031</v>
+        <v>6766983</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7219,6 +7219,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7246,10 +7251,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127621155</v>
+        <v>127618554</v>
       </c>
       <c r="B63" t="n">
-        <v>79018</v>
+        <v>78776</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7257,21 +7262,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7284,10 +7289,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>443504</v>
+        <v>443265</v>
       </c>
       <c r="R63" t="n">
-        <v>6766983</v>
+        <v>6767455</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7320,11 +7325,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7352,43 +7352,37 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127606882</v>
+        <v>127621185</v>
       </c>
       <c r="B64" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7396,10 +7390,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>443860</v>
+        <v>443486</v>
       </c>
       <c r="R64" t="n">
-        <v>6766863</v>
+        <v>6766960</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7564,37 +7558,43 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127621185</v>
+        <v>127606882</v>
       </c>
       <c r="B66" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7602,10 +7602,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>443486</v>
+        <v>443860</v>
       </c>
       <c r="R66" t="n">
-        <v>6766960</v>
+        <v>6766863</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7984,10 +7984,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127619056</v>
+        <v>127608339</v>
       </c>
       <c r="B70" t="n">
-        <v>57658</v>
+        <v>91350</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7995,31 +7995,26 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8027,10 +8022,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>443270</v>
+        <v>443750</v>
       </c>
       <c r="R70" t="n">
-        <v>6767248</v>
+        <v>6767090</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8071,6 +8066,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8196,10 +8192,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127608339</v>
+        <v>127619056</v>
       </c>
       <c r="B72" t="n">
-        <v>91350</v>
+        <v>57658</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8207,26 +8203,31 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -8234,10 +8235,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>443750</v>
+        <v>443270</v>
       </c>
       <c r="R72" t="n">
-        <v>6767090</v>
+        <v>6767248</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8278,7 +8279,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8403,10 +8403,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127606796</v>
+        <v>127619016</v>
       </c>
       <c r="B74" t="n">
-        <v>79018</v>
+        <v>78776</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8414,21 +8414,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8441,10 +8441,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>443860</v>
+        <v>443270</v>
       </c>
       <c r="R74" t="n">
-        <v>6766854</v>
+        <v>6767260</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8504,10 +8504,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127619016</v>
+        <v>127606796</v>
       </c>
       <c r="B75" t="n">
-        <v>78776</v>
+        <v>79018</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8515,21 +8515,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8542,10 +8542,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>443270</v>
+        <v>443860</v>
       </c>
       <c r="R75" t="n">
-        <v>6767260</v>
+        <v>6766854</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8605,43 +8605,37 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127619038</v>
+        <v>127621131</v>
       </c>
       <c r="B76" t="n">
-        <v>4773</v>
+        <v>79018</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100299</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -8649,10 +8643,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>443270</v>
+        <v>443495</v>
       </c>
       <c r="R76" t="n">
-        <v>6767248</v>
+        <v>6766975</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8685,6 +8679,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>På tall och gran rikligt</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8712,37 +8711,43 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127621131</v>
+        <v>127619038</v>
       </c>
       <c r="B77" t="n">
-        <v>79018</v>
+        <v>4773</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>100299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -8750,10 +8755,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>443495</v>
+        <v>443270</v>
       </c>
       <c r="R77" t="n">
-        <v>6766975</v>
+        <v>6767248</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8786,11 +8791,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>På tall och gran rikligt</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8818,43 +8818,37 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127619183</v>
+        <v>127618895</v>
       </c>
       <c r="B78" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -8862,10 +8856,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>443347</v>
+        <v>443282</v>
       </c>
       <c r="R78" t="n">
-        <v>6767103</v>
+        <v>6767309</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8898,11 +8892,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>På låga</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9036,43 +9025,37 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127619158</v>
+        <v>127618498</v>
       </c>
       <c r="B80" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -9080,10 +9063,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>443344</v>
+        <v>443249</v>
       </c>
       <c r="R80" t="n">
-        <v>6767154</v>
+        <v>6767415</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9120,7 +9103,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>På raka</t>
+          <t>På 3 tallstammar</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9148,37 +9131,43 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127618895</v>
+        <v>127619183</v>
       </c>
       <c r="B81" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -9186,10 +9175,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>443282</v>
+        <v>443347</v>
       </c>
       <c r="R81" t="n">
-        <v>6767309</v>
+        <v>6767103</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9222,6 +9211,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>På låga</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9249,37 +9243,43 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127618498</v>
+        <v>127618615</v>
       </c>
       <c r="B82" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -9287,10 +9287,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>443249</v>
+        <v>443293</v>
       </c>
       <c r="R82" t="n">
-        <v>6767415</v>
+        <v>6767447</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9323,11 +9323,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>På 3 tallstammar</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9355,7 +9350,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127618615</v>
+        <v>127619158</v>
       </c>
       <c r="B83" t="n">
         <v>8450</v>
@@ -9399,10 +9394,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>443293</v>
+        <v>443344</v>
       </c>
       <c r="R83" t="n">
-        <v>6767447</v>
+        <v>6767154</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9435,6 +9430,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>På raka</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9462,38 +9462,37 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127618897</v>
+        <v>127621268</v>
       </c>
       <c r="B84" t="n">
-        <v>58031</v>
+        <v>78776</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>103015</v>
+        <v>6446</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -9501,10 +9500,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>443282</v>
+        <v>443543</v>
       </c>
       <c r="R84" t="n">
-        <v>6767309</v>
+        <v>6766974</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9545,6 +9544,7 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9664,7 +9664,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127621268</v>
+        <v>127621011</v>
       </c>
       <c r="B86" t="n">
         <v>78776</v>
@@ -9702,10 +9702,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>443543</v>
+        <v>443400</v>
       </c>
       <c r="R86" t="n">
-        <v>6766974</v>
+        <v>6766956</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9765,36 +9765,44 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127621011</v>
+        <v>127618762</v>
       </c>
       <c r="B87" t="n">
-        <v>78776</v>
+        <v>92620</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
@@ -9803,10 +9811,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>443400</v>
+        <v>443291</v>
       </c>
       <c r="R87" t="n">
-        <v>6766956</v>
+        <v>6767297</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9839,6 +9847,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Förra årets Fkr.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9866,10 +9879,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127618762</v>
+        <v>127618897</v>
       </c>
       <c r="B88" t="n">
-        <v>92620</v>
+        <v>58031</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9877,34 +9890,27 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4364</v>
+        <v>103015</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -9912,10 +9918,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>443291</v>
+        <v>443282</v>
       </c>
       <c r="R88" t="n">
-        <v>6767297</v>
+        <v>6767309</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9950,18 +9956,12 @@
           <t>2025-08-14</t>
         </is>
       </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Förra årets Fkr.</t>
-        </is>
-      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9980,7 +9980,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127618666</v>
+        <v>127619059</v>
       </c>
       <c r="B89" t="n">
         <v>79018</v>
@@ -10018,10 +10018,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>443292</v>
+        <v>443270</v>
       </c>
       <c r="R89" t="n">
-        <v>6767366</v>
+        <v>6767248</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10054,11 +10054,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>På 2 tallstammar</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10086,43 +10081,37 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127613349</v>
+        <v>127606939</v>
       </c>
       <c r="B90" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -10130,10 +10119,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>443363</v>
+        <v>443852</v>
       </c>
       <c r="R90" t="n">
-        <v>6767418</v>
+        <v>6766955</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10166,6 +10155,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>På 9 tallstammar</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10193,7 +10187,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127606939</v>
+        <v>127608341</v>
       </c>
       <c r="B91" t="n">
         <v>79018</v>
@@ -10231,10 +10225,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>443852</v>
+        <v>443750</v>
       </c>
       <c r="R91" t="n">
-        <v>6766955</v>
+        <v>6767090</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10267,11 +10261,6 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>På 9 tallstammar</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10299,7 +10288,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127608341</v>
+        <v>127608010</v>
       </c>
       <c r="B92" t="n">
         <v>79018</v>
@@ -10337,10 +10326,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>443750</v>
+        <v>443876</v>
       </c>
       <c r="R92" t="n">
-        <v>6767090</v>
+        <v>6766959</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10400,43 +10389,37 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127613395</v>
+        <v>127618666</v>
       </c>
       <c r="B93" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
@@ -10444,10 +10427,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>443299</v>
+        <v>443292</v>
       </c>
       <c r="R93" t="n">
-        <v>6767410</v>
+        <v>6767366</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10480,6 +10463,11 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>På 2 tallstammar</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10507,37 +10495,43 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127608010</v>
+        <v>127613349</v>
       </c>
       <c r="B94" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -10545,10 +10539,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>443876</v>
+        <v>443363</v>
       </c>
       <c r="R94" t="n">
-        <v>6766959</v>
+        <v>6767418</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10608,37 +10602,43 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127619059</v>
+        <v>127613395</v>
       </c>
       <c r="B95" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -10646,10 +10646,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>443270</v>
+        <v>443299</v>
       </c>
       <c r="R95" t="n">
-        <v>6767248</v>
+        <v>6767410</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>

--- a/artfynd/A 35482-2025 artfynd.xlsx
+++ b/artfynd/A 35482-2025 artfynd.xlsx
@@ -2731,10 +2731,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127620991</v>
+        <v>127618950</v>
       </c>
       <c r="B20" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2742,26 +2742,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2769,10 +2774,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>443391</v>
+        <v>443268</v>
       </c>
       <c r="R20" t="n">
-        <v>6766953</v>
+        <v>6767266</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2809,7 +2814,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2818,7 +2823,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2837,37 +2841,43 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127613169</v>
+        <v>127619035</v>
       </c>
       <c r="B21" t="n">
-        <v>79018</v>
+        <v>5177</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2875,10 +2885,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>443649</v>
+        <v>443270</v>
       </c>
       <c r="R21" t="n">
-        <v>6767135</v>
+        <v>6767248</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2911,11 +2921,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På 3 tallstammar</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2943,40 +2948,41 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127618950</v>
+        <v>127606899</v>
       </c>
       <c r="B22" t="n">
-        <v>57661</v>
+        <v>8450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2986,10 +2992,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>443268</v>
+        <v>443830</v>
       </c>
       <c r="R22" t="n">
-        <v>6767266</v>
+        <v>6766958</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3024,17 +3030,13 @@
           <t>2025-08-14</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3053,43 +3055,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127619035</v>
+        <v>127620991</v>
       </c>
       <c r="B23" t="n">
-        <v>5177</v>
+        <v>79018</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3097,10 +3093,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>443270</v>
+        <v>443391</v>
       </c>
       <c r="R23" t="n">
-        <v>6767248</v>
+        <v>6766953</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3133,6 +3129,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3160,43 +3161,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127606899</v>
+        <v>127613169</v>
       </c>
       <c r="B24" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3204,10 +3199,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>443830</v>
+        <v>443649</v>
       </c>
       <c r="R24" t="n">
-        <v>6766958</v>
+        <v>6767135</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3240,6 +3235,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På 3 tallstammar</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3267,10 +3267,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127619053</v>
+        <v>127618623</v>
       </c>
       <c r="B25" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3278,31 +3278,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3310,10 +3305,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>443270</v>
+        <v>443293</v>
       </c>
       <c r="R25" t="n">
-        <v>6767248</v>
+        <v>6767447</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3354,6 +3349,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3372,50 +3368,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127618987</v>
+        <v>127608276</v>
       </c>
       <c r="B26" t="n">
-        <v>56853</v>
+        <v>79018</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3423,10 +3406,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>443268</v>
+        <v>443801</v>
       </c>
       <c r="R26" t="n">
-        <v>6767266</v>
+        <v>6767090</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3461,12 +3444,18 @@
           <t>2025-08-14</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På 3 tallstammar</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3485,7 +3474,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127618623</v>
+        <v>127618438</v>
       </c>
       <c r="B27" t="n">
         <v>79018</v>
@@ -3523,10 +3512,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>443293</v>
+        <v>443259</v>
       </c>
       <c r="R27" t="n">
-        <v>6767447</v>
+        <v>6767420</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3586,7 +3575,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127608276</v>
+        <v>127618680</v>
       </c>
       <c r="B28" t="n">
         <v>79018</v>
@@ -3624,10 +3613,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>443801</v>
+        <v>443307</v>
       </c>
       <c r="R28" t="n">
-        <v>6767090</v>
+        <v>6767347</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3660,11 +3649,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På 3 tallstammar</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3692,10 +3676,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127618438</v>
+        <v>127619053</v>
       </c>
       <c r="B29" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3703,26 +3687,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3730,10 +3719,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>443259</v>
+        <v>443270</v>
       </c>
       <c r="R29" t="n">
-        <v>6767420</v>
+        <v>6767248</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3774,7 +3763,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3793,37 +3781,50 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127618680</v>
+        <v>127618987</v>
       </c>
       <c r="B30" t="n">
-        <v>79018</v>
+        <v>56853</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3831,10 +3832,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>443307</v>
+        <v>443268</v>
       </c>
       <c r="R30" t="n">
-        <v>6767347</v>
+        <v>6767266</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3875,7 +3876,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -5693,10 +5693,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127618673</v>
+        <v>127618557</v>
       </c>
       <c r="B48" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5704,21 +5704,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5731,10 +5731,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>443294</v>
+        <v>443265</v>
       </c>
       <c r="R48" t="n">
-        <v>6767362</v>
+        <v>6767455</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5794,7 +5794,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127613428</v>
+        <v>127618673</v>
       </c>
       <c r="B49" t="n">
         <v>79018</v>
@@ -5832,10 +5832,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>443272</v>
+        <v>443294</v>
       </c>
       <c r="R49" t="n">
-        <v>6767422</v>
+        <v>6767362</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5895,7 +5895,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127621265</v>
+        <v>127613428</v>
       </c>
       <c r="B50" t="n">
         <v>79018</v>
@@ -5933,10 +5933,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>443543</v>
+        <v>443272</v>
       </c>
       <c r="R50" t="n">
-        <v>6766974</v>
+        <v>6767422</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5996,7 +5996,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127621072</v>
+        <v>127621265</v>
       </c>
       <c r="B51" t="n">
         <v>79018</v>
@@ -6034,10 +6034,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>443404</v>
+        <v>443543</v>
       </c>
       <c r="R51" t="n">
-        <v>6766973</v>
+        <v>6766974</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6070,11 +6070,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På 3 tallstammar</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6102,7 +6097,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127608059</v>
+        <v>127621072</v>
       </c>
       <c r="B52" t="n">
         <v>79018</v>
@@ -6140,10 +6135,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>443812</v>
+        <v>443404</v>
       </c>
       <c r="R52" t="n">
-        <v>6767031</v>
+        <v>6766973</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6176,6 +6171,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>På 3 tallstammar</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6203,10 +6203,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127618557</v>
+        <v>127608059</v>
       </c>
       <c r="B53" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6214,21 +6214,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6241,10 +6241,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>443265</v>
+        <v>443812</v>
       </c>
       <c r="R53" t="n">
-        <v>6767455</v>
+        <v>6767031</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6718,10 +6718,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127618512</v>
+        <v>127620831</v>
       </c>
       <c r="B58" t="n">
-        <v>8450</v>
+        <v>43939</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6729,21 +6729,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106545</v>
+        <v>101735</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6762,10 +6762,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>443254</v>
+        <v>443380</v>
       </c>
       <c r="R58" t="n">
-        <v>6767421</v>
+        <v>6767035</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6825,7 +6825,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127618707</v>
+        <v>127618512</v>
       </c>
       <c r="B59" t="n">
         <v>8450</v>
@@ -6869,10 +6869,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>443350</v>
+        <v>443254</v>
       </c>
       <c r="R59" t="n">
-        <v>6767334</v>
+        <v>6767421</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6905,11 +6905,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>På torraka</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6937,10 +6932,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127620831</v>
+        <v>127618707</v>
       </c>
       <c r="B60" t="n">
-        <v>43939</v>
+        <v>8450</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6948,21 +6943,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>101735</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6981,10 +6976,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>443380</v>
+        <v>443350</v>
       </c>
       <c r="R60" t="n">
-        <v>6767035</v>
+        <v>6767334</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7017,6 +7012,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>På torraka</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7044,10 +7044,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127608048</v>
+        <v>127621155</v>
       </c>
       <c r="B61" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7055,21 +7055,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7082,10 +7082,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>443798</v>
+        <v>443504</v>
       </c>
       <c r="R61" t="n">
-        <v>6767031</v>
+        <v>6766983</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7118,6 +7118,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7145,10 +7150,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127621155</v>
+        <v>127618554</v>
       </c>
       <c r="B62" t="n">
-        <v>79018</v>
+        <v>78776</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7156,21 +7161,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7183,10 +7188,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>443504</v>
+        <v>443265</v>
       </c>
       <c r="R62" t="n">
-        <v>6766983</v>
+        <v>6767455</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7219,11 +7224,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7251,10 +7251,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127618554</v>
+        <v>127608048</v>
       </c>
       <c r="B63" t="n">
-        <v>78776</v>
+        <v>78777</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7262,21 +7262,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7289,10 +7289,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>443265</v>
+        <v>443798</v>
       </c>
       <c r="R63" t="n">
-        <v>6767455</v>
+        <v>6767031</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7352,37 +7352,43 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127621185</v>
+        <v>127606882</v>
       </c>
       <c r="B64" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7390,10 +7396,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>443486</v>
+        <v>443860</v>
       </c>
       <c r="R64" t="n">
-        <v>6766960</v>
+        <v>6766863</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7453,10 +7459,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127621194</v>
+        <v>127621185</v>
       </c>
       <c r="B65" t="n">
-        <v>57821</v>
+        <v>79018</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7464,31 +7470,26 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7540,6 +7541,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7558,41 +7560,40 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127606882</v>
+        <v>127621194</v>
       </c>
       <c r="B66" t="n">
-        <v>8450</v>
+        <v>57821</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -7602,10 +7603,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>443860</v>
+        <v>443486</v>
       </c>
       <c r="R66" t="n">
-        <v>6766863</v>
+        <v>6766960</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7646,7 +7647,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35482-2025 artfynd.xlsx
+++ b/artfynd/A 35482-2025 artfynd.xlsx
@@ -2731,10 +2731,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127618950</v>
+        <v>127620991</v>
       </c>
       <c r="B20" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2742,31 +2742,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2774,10 +2769,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>443268</v>
+        <v>443391</v>
       </c>
       <c r="R20" t="n">
-        <v>6767266</v>
+        <v>6766953</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2814,7 +2809,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2823,6 +2818,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2841,43 +2837,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127619035</v>
+        <v>127613169</v>
       </c>
       <c r="B21" t="n">
-        <v>5177</v>
+        <v>79018</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2885,10 +2875,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>443270</v>
+        <v>443649</v>
       </c>
       <c r="R21" t="n">
-        <v>6767248</v>
+        <v>6767135</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2921,6 +2911,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På 3 tallstammar</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2948,41 +2943,40 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127606899</v>
+        <v>127618950</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>57661</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2992,10 +2986,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>443830</v>
+        <v>443268</v>
       </c>
       <c r="R22" t="n">
-        <v>6766958</v>
+        <v>6767266</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3030,13 +3024,17 @@
           <t>2025-08-14</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3055,37 +3053,43 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127620991</v>
+        <v>127619035</v>
       </c>
       <c r="B23" t="n">
-        <v>79018</v>
+        <v>5177</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3093,10 +3097,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>443391</v>
+        <v>443270</v>
       </c>
       <c r="R23" t="n">
-        <v>6766953</v>
+        <v>6767248</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3129,11 +3133,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3161,37 +3160,43 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127613169</v>
+        <v>127606899</v>
       </c>
       <c r="B24" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3199,10 +3204,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>443649</v>
+        <v>443830</v>
       </c>
       <c r="R24" t="n">
-        <v>6767135</v>
+        <v>6766958</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3235,11 +3240,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På 3 tallstammar</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3267,10 +3267,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127618623</v>
+        <v>127619053</v>
       </c>
       <c r="B25" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3278,26 +3278,31 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3305,10 +3310,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>443293</v>
+        <v>443270</v>
       </c>
       <c r="R25" t="n">
-        <v>6767447</v>
+        <v>6767248</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3349,7 +3354,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3368,37 +3372,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127608276</v>
+        <v>127618987</v>
       </c>
       <c r="B26" t="n">
-        <v>79018</v>
+        <v>56853</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3406,10 +3423,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>443801</v>
+        <v>443268</v>
       </c>
       <c r="R26" t="n">
-        <v>6767090</v>
+        <v>6767266</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3444,18 +3461,12 @@
           <t>2025-08-14</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På 3 tallstammar</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3474,7 +3485,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127618438</v>
+        <v>127618623</v>
       </c>
       <c r="B27" t="n">
         <v>79018</v>
@@ -3512,10 +3523,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>443259</v>
+        <v>443293</v>
       </c>
       <c r="R27" t="n">
-        <v>6767420</v>
+        <v>6767447</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3575,7 +3586,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127618680</v>
+        <v>127608276</v>
       </c>
       <c r="B28" t="n">
         <v>79018</v>
@@ -3613,10 +3624,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>443307</v>
+        <v>443801</v>
       </c>
       <c r="R28" t="n">
-        <v>6767347</v>
+        <v>6767090</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3649,6 +3660,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På 3 tallstammar</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3676,10 +3692,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127619053</v>
+        <v>127618438</v>
       </c>
       <c r="B29" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3687,31 +3703,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3719,10 +3730,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>443270</v>
+        <v>443259</v>
       </c>
       <c r="R29" t="n">
-        <v>6767248</v>
+        <v>6767420</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3763,6 +3774,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3781,50 +3793,37 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127618987</v>
+        <v>127618680</v>
       </c>
       <c r="B30" t="n">
-        <v>56853</v>
+        <v>79018</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3832,10 +3831,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>443268</v>
+        <v>443307</v>
       </c>
       <c r="R30" t="n">
-        <v>6767266</v>
+        <v>6767347</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3876,6 +3875,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -5273,37 +5273,43 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127608039</v>
+        <v>127619167</v>
       </c>
       <c r="B44" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5311,10 +5317,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>443868</v>
+        <v>443339</v>
       </c>
       <c r="R44" t="n">
-        <v>6766980</v>
+        <v>6767141</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5351,7 +5357,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På 3 tallstammar</t>
+          <t>På raka</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5379,43 +5385,37 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127619167</v>
+        <v>127608039</v>
       </c>
       <c r="B45" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5423,10 +5423,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>443339</v>
+        <v>443868</v>
       </c>
       <c r="R45" t="n">
-        <v>6767141</v>
+        <v>6766980</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5463,7 +5463,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På raka</t>
+          <t>På 3 tallstammar</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6304,37 +6304,43 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127621090</v>
+        <v>127618512</v>
       </c>
       <c r="B54" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6342,10 +6348,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>443420</v>
+        <v>443254</v>
       </c>
       <c r="R54" t="n">
-        <v>6767000</v>
+        <v>6767421</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6378,11 +6384,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>På 3 tallstammar</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6410,37 +6411,43 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127620953</v>
+        <v>127618707</v>
       </c>
       <c r="B55" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6448,10 +6455,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>443383</v>
+        <v>443350</v>
       </c>
       <c r="R55" t="n">
-        <v>6766953</v>
+        <v>6767334</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6484,6 +6491,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>På torraka</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6511,7 +6523,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127618689</v>
+        <v>127621090</v>
       </c>
       <c r="B56" t="n">
         <v>79018</v>
@@ -6549,10 +6561,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>443307</v>
+        <v>443420</v>
       </c>
       <c r="R56" t="n">
-        <v>6767350</v>
+        <v>6767000</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6585,6 +6597,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>På 3 tallstammar</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6612,7 +6629,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127618534</v>
+        <v>127620953</v>
       </c>
       <c r="B57" t="n">
         <v>79018</v>
@@ -6650,10 +6667,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>443258</v>
+        <v>443383</v>
       </c>
       <c r="R57" t="n">
-        <v>6767430</v>
+        <v>6766953</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6686,11 +6703,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>På 2 tallstammar</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6718,43 +6730,37 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127620831</v>
+        <v>127618689</v>
       </c>
       <c r="B58" t="n">
-        <v>43939</v>
+        <v>79018</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>101735</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6762,10 +6768,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>443380</v>
+        <v>443307</v>
       </c>
       <c r="R58" t="n">
-        <v>6767035</v>
+        <v>6767350</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6825,43 +6831,37 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127618512</v>
+        <v>127618534</v>
       </c>
       <c r="B59" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6869,10 +6869,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>443254</v>
+        <v>443258</v>
       </c>
       <c r="R59" t="n">
-        <v>6767421</v>
+        <v>6767430</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6905,6 +6905,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>På 2 tallstammar</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6932,10 +6937,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127618707</v>
+        <v>127620831</v>
       </c>
       <c r="B60" t="n">
-        <v>8450</v>
+        <v>43939</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6943,21 +6948,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>101735</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6976,10 +6981,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>443350</v>
+        <v>443380</v>
       </c>
       <c r="R60" t="n">
-        <v>6767334</v>
+        <v>6767035</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7012,11 +7017,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>På torraka</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7352,43 +7352,37 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127606882</v>
+        <v>127621185</v>
       </c>
       <c r="B64" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7396,10 +7390,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>443860</v>
+        <v>443486</v>
       </c>
       <c r="R64" t="n">
-        <v>6766863</v>
+        <v>6766960</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7459,10 +7453,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127621185</v>
+        <v>127621194</v>
       </c>
       <c r="B65" t="n">
-        <v>79018</v>
+        <v>57821</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7470,26 +7464,31 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7541,7 +7540,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7560,40 +7558,41 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127621194</v>
+        <v>127606882</v>
       </c>
       <c r="B66" t="n">
-        <v>57821</v>
+        <v>8450</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -7603,10 +7602,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>443486</v>
+        <v>443860</v>
       </c>
       <c r="R66" t="n">
-        <v>6766960</v>
+        <v>6766863</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7647,6 +7646,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7665,37 +7665,43 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127620944</v>
+        <v>127618658</v>
       </c>
       <c r="B67" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7703,10 +7709,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>443383</v>
+        <v>443286</v>
       </c>
       <c r="R67" t="n">
-        <v>6766978</v>
+        <v>6767436</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7743,7 +7749,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>På 5 tallstammar</t>
+          <t>På tallraka</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7771,7 +7777,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127618716</v>
+        <v>127620944</v>
       </c>
       <c r="B68" t="n">
         <v>79018</v>
@@ -7809,10 +7815,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>443350</v>
+        <v>443383</v>
       </c>
       <c r="R68" t="n">
-        <v>6767334</v>
+        <v>6766978</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7845,6 +7851,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>På 5 tallstammar</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7872,43 +7883,37 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127618658</v>
+        <v>127618716</v>
       </c>
       <c r="B69" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -7916,10 +7921,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>443286</v>
+        <v>443350</v>
       </c>
       <c r="R69" t="n">
-        <v>6767436</v>
+        <v>6767334</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7952,11 +7957,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>På tallraka</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8818,37 +8818,43 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127618895</v>
+        <v>127619183</v>
       </c>
       <c r="B78" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -8856,10 +8862,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>443282</v>
+        <v>443347</v>
       </c>
       <c r="R78" t="n">
-        <v>6767309</v>
+        <v>6767103</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8892,6 +8898,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>På låga</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8919,37 +8930,43 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127619312</v>
+        <v>127618615</v>
       </c>
       <c r="B79" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -8957,10 +8974,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>443370</v>
+        <v>443293</v>
       </c>
       <c r="R79" t="n">
-        <v>6767060</v>
+        <v>6767447</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8993,11 +9010,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>På 3 tallstammar</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9025,37 +9037,43 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127618498</v>
+        <v>127619158</v>
       </c>
       <c r="B80" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -9063,10 +9081,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>443249</v>
+        <v>443344</v>
       </c>
       <c r="R80" t="n">
-        <v>6767415</v>
+        <v>6767154</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9103,7 +9121,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>På 3 tallstammar</t>
+          <t>På raka</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9131,43 +9149,37 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127619183</v>
+        <v>127618895</v>
       </c>
       <c r="B81" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -9175,10 +9187,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>443347</v>
+        <v>443282</v>
       </c>
       <c r="R81" t="n">
-        <v>6767103</v>
+        <v>6767309</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9211,11 +9223,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>På låga</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9243,43 +9250,37 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127618615</v>
+        <v>127619312</v>
       </c>
       <c r="B82" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -9287,10 +9288,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>443293</v>
+        <v>443370</v>
       </c>
       <c r="R82" t="n">
-        <v>6767447</v>
+        <v>6767060</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9323,6 +9324,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>På 3 tallstammar</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9350,43 +9356,37 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127619158</v>
+        <v>127618498</v>
       </c>
       <c r="B83" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -9394,10 +9394,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>443344</v>
+        <v>443249</v>
       </c>
       <c r="R83" t="n">
-        <v>6767154</v>
+        <v>6767415</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9434,7 +9434,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>På raka</t>
+          <t>På 3 tallstammar</t>
         </is>
       </c>
       <c r="AD83" t="b">

--- a/artfynd/A 35482-2025 artfynd.xlsx
+++ b/artfynd/A 35482-2025 artfynd.xlsx
@@ -1967,45 +1967,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127473637</v>
+        <v>127473199</v>
       </c>
       <c r="B13" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Oxeråsbäcken, Oxeråsbäcken, Dlr</t>
+          <t>Oxeråsen S om, Oxeråsen S om, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>444013</v>
+        <v>443957</v>
       </c>
       <c r="R13" t="n">
-        <v>6766733</v>
+        <v>6766708</v>
       </c>
       <c r="S13" t="n">
         <v>9</v>
@@ -2037,7 +2042,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2047,12 +2052,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:41</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På tallstammen flera</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2079,50 +2079,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127473199</v>
+        <v>127473637</v>
       </c>
       <c r="B14" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Oxeråsen S om, Oxeråsen S om, Dlr</t>
+          <t>Oxeråsbäcken, Oxeråsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>443957</v>
+        <v>444013</v>
       </c>
       <c r="R14" t="n">
-        <v>6766708</v>
+        <v>6766733</v>
       </c>
       <c r="S14" t="n">
         <v>9</v>
@@ -2154,7 +2149,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2164,7 +2159,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På tallstammen flera</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -3267,10 +3267,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127619053</v>
+        <v>127618623</v>
       </c>
       <c r="B25" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3278,31 +3278,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3310,10 +3305,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>443270</v>
+        <v>443293</v>
       </c>
       <c r="R25" t="n">
-        <v>6767248</v>
+        <v>6767447</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3354,6 +3349,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3372,50 +3368,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127618987</v>
+        <v>127608276</v>
       </c>
       <c r="B26" t="n">
-        <v>56853</v>
+        <v>79018</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3423,10 +3406,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>443268</v>
+        <v>443801</v>
       </c>
       <c r="R26" t="n">
-        <v>6767266</v>
+        <v>6767090</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3461,12 +3444,18 @@
           <t>2025-08-14</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På 3 tallstammar</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3485,7 +3474,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127618623</v>
+        <v>127618438</v>
       </c>
       <c r="B27" t="n">
         <v>79018</v>
@@ -3523,10 +3512,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>443293</v>
+        <v>443259</v>
       </c>
       <c r="R27" t="n">
-        <v>6767447</v>
+        <v>6767420</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3586,7 +3575,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127608276</v>
+        <v>127618680</v>
       </c>
       <c r="B28" t="n">
         <v>79018</v>
@@ -3624,10 +3613,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>443801</v>
+        <v>443307</v>
       </c>
       <c r="R28" t="n">
-        <v>6767090</v>
+        <v>6767347</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3660,11 +3649,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På 3 tallstammar</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3692,37 +3676,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127618438</v>
+        <v>127618987</v>
       </c>
       <c r="B29" t="n">
-        <v>79018</v>
+        <v>56853</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3730,10 +3727,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>443259</v>
+        <v>443268</v>
       </c>
       <c r="R29" t="n">
-        <v>6767420</v>
+        <v>6767266</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3774,7 +3771,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3793,10 +3789,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127618680</v>
+        <v>127619053</v>
       </c>
       <c r="B30" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3804,26 +3800,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3831,10 +3832,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>443307</v>
+        <v>443270</v>
       </c>
       <c r="R30" t="n">
-        <v>6767347</v>
+        <v>6767248</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3875,7 +3876,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -5273,43 +5273,37 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127619167</v>
+        <v>127608039</v>
       </c>
       <c r="B44" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5317,10 +5311,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>443339</v>
+        <v>443868</v>
       </c>
       <c r="R44" t="n">
-        <v>6767141</v>
+        <v>6766980</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5357,7 +5351,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På raka</t>
+          <t>På 3 tallstammar</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5385,37 +5379,43 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127608039</v>
+        <v>127619167</v>
       </c>
       <c r="B45" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5423,10 +5423,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>443868</v>
+        <v>443339</v>
       </c>
       <c r="R45" t="n">
-        <v>6766980</v>
+        <v>6767141</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5463,7 +5463,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På 3 tallstammar</t>
+          <t>På raka</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5693,10 +5693,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127618557</v>
+        <v>127621072</v>
       </c>
       <c r="B48" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5704,21 +5704,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5731,10 +5731,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>443265</v>
+        <v>443404</v>
       </c>
       <c r="R48" t="n">
-        <v>6767455</v>
+        <v>6766973</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5767,6 +5767,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På 3 tallstammar</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5794,10 +5799,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127618673</v>
+        <v>127618557</v>
       </c>
       <c r="B49" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5805,21 +5810,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5832,10 +5837,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>443294</v>
+        <v>443265</v>
       </c>
       <c r="R49" t="n">
-        <v>6767362</v>
+        <v>6767455</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5895,7 +5900,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127613428</v>
+        <v>127618673</v>
       </c>
       <c r="B50" t="n">
         <v>79018</v>
@@ -5933,10 +5938,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>443272</v>
+        <v>443294</v>
       </c>
       <c r="R50" t="n">
-        <v>6767422</v>
+        <v>6767362</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5996,7 +6001,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127621265</v>
+        <v>127613428</v>
       </c>
       <c r="B51" t="n">
         <v>79018</v>
@@ -6034,10 +6039,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>443543</v>
+        <v>443272</v>
       </c>
       <c r="R51" t="n">
-        <v>6766974</v>
+        <v>6767422</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6097,7 +6102,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127621072</v>
+        <v>127621265</v>
       </c>
       <c r="B52" t="n">
         <v>79018</v>
@@ -6135,10 +6140,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>443404</v>
+        <v>443543</v>
       </c>
       <c r="R52" t="n">
-        <v>6766973</v>
+        <v>6766974</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6171,11 +6176,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>På 3 tallstammar</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6304,43 +6304,37 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127618512</v>
+        <v>127621090</v>
       </c>
       <c r="B54" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6348,10 +6342,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>443254</v>
+        <v>443420</v>
       </c>
       <c r="R54" t="n">
-        <v>6767421</v>
+        <v>6767000</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6384,6 +6378,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>På 3 tallstammar</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6411,43 +6410,37 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127618707</v>
+        <v>127620953</v>
       </c>
       <c r="B55" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6455,10 +6448,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>443350</v>
+        <v>443383</v>
       </c>
       <c r="R55" t="n">
-        <v>6767334</v>
+        <v>6766953</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6491,11 +6484,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>På torraka</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6523,7 +6511,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127621090</v>
+        <v>127618689</v>
       </c>
       <c r="B56" t="n">
         <v>79018</v>
@@ -6561,10 +6549,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>443420</v>
+        <v>443307</v>
       </c>
       <c r="R56" t="n">
-        <v>6767000</v>
+        <v>6767350</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6597,11 +6585,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>På 3 tallstammar</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6629,7 +6612,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127620953</v>
+        <v>127618534</v>
       </c>
       <c r="B57" t="n">
         <v>79018</v>
@@ -6667,10 +6650,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>443383</v>
+        <v>443258</v>
       </c>
       <c r="R57" t="n">
-        <v>6766953</v>
+        <v>6767430</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6703,6 +6686,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>På 2 tallstammar</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6730,37 +6718,43 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127618689</v>
+        <v>127620831</v>
       </c>
       <c r="B58" t="n">
-        <v>79018</v>
+        <v>43939</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>101735</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6768,10 +6762,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>443307</v>
+        <v>443380</v>
       </c>
       <c r="R58" t="n">
-        <v>6767350</v>
+        <v>6767035</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6831,37 +6825,43 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127618534</v>
+        <v>127618512</v>
       </c>
       <c r="B59" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6869,10 +6869,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>443258</v>
+        <v>443254</v>
       </c>
       <c r="R59" t="n">
-        <v>6767430</v>
+        <v>6767421</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6905,11 +6905,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>På 2 tallstammar</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6937,10 +6932,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127620831</v>
+        <v>127618707</v>
       </c>
       <c r="B60" t="n">
-        <v>43939</v>
+        <v>8450</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6948,21 +6943,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>101735</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6981,10 +6976,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>443380</v>
+        <v>443350</v>
       </c>
       <c r="R60" t="n">
-        <v>6767035</v>
+        <v>6767334</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7017,6 +7012,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>På torraka</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7984,10 +7984,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127608339</v>
+        <v>127619056</v>
       </c>
       <c r="B70" t="n">
-        <v>91350</v>
+        <v>57658</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7995,26 +7995,31 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8022,10 +8027,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>443750</v>
+        <v>443270</v>
       </c>
       <c r="R70" t="n">
-        <v>6767090</v>
+        <v>6767248</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8066,7 +8071,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8192,10 +8196,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127619056</v>
+        <v>127608339</v>
       </c>
       <c r="B72" t="n">
-        <v>57658</v>
+        <v>91350</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8203,31 +8207,26 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -8235,10 +8234,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>443270</v>
+        <v>443750</v>
       </c>
       <c r="R72" t="n">
-        <v>6767248</v>
+        <v>6767090</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8279,6 +8278,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -9462,36 +9462,44 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127621268</v>
+        <v>127618762</v>
       </c>
       <c r="B84" t="n">
-        <v>78776</v>
+        <v>92620</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
@@ -9500,10 +9508,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>443543</v>
+        <v>443291</v>
       </c>
       <c r="R84" t="n">
-        <v>6766974</v>
+        <v>6767297</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9536,6 +9544,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Förra årets Fkr.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9563,7 +9576,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127620818</v>
+        <v>127621268</v>
       </c>
       <c r="B85" t="n">
         <v>78776</v>
@@ -9601,10 +9614,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>443357</v>
+        <v>443543</v>
       </c>
       <c r="R85" t="n">
-        <v>6767054</v>
+        <v>6766974</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9664,7 +9677,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127621011</v>
+        <v>127620818</v>
       </c>
       <c r="B86" t="n">
         <v>78776</v>
@@ -9702,10 +9715,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>443400</v>
+        <v>443357</v>
       </c>
       <c r="R86" t="n">
-        <v>6766956</v>
+        <v>6767054</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9765,44 +9778,36 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127618762</v>
+        <v>127621011</v>
       </c>
       <c r="B87" t="n">
-        <v>92620</v>
+        <v>78776</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
@@ -9811,10 +9816,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>443291</v>
+        <v>443400</v>
       </c>
       <c r="R87" t="n">
-        <v>6767297</v>
+        <v>6766956</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9847,11 +9852,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Förra årets Fkr.</t>
         </is>
       </c>
       <c r="AD87" t="b">

--- a/artfynd/A 35482-2025 artfynd.xlsx
+++ b/artfynd/A 35482-2025 artfynd.xlsx
@@ -2731,10 +2731,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127618950</v>
+        <v>127620991</v>
       </c>
       <c r="B20" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2742,31 +2742,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2774,10 +2769,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>443268</v>
+        <v>443391</v>
       </c>
       <c r="R20" t="n">
-        <v>6767266</v>
+        <v>6766953</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2814,7 +2809,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2823,6 +2818,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2841,43 +2837,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127619035</v>
+        <v>127613169</v>
       </c>
       <c r="B21" t="n">
-        <v>5177</v>
+        <v>79029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2885,10 +2875,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>443270</v>
+        <v>443649</v>
       </c>
       <c r="R21" t="n">
-        <v>6767248</v>
+        <v>6767135</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2921,6 +2911,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På 3 tallstammar</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2948,41 +2943,40 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127606899</v>
+        <v>127618950</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>57672</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2992,10 +2986,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>443830</v>
+        <v>443268</v>
       </c>
       <c r="R22" t="n">
-        <v>6766958</v>
+        <v>6767266</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3030,13 +3024,17 @@
           <t>2025-08-14</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3055,37 +3053,43 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127620991</v>
+        <v>127606899</v>
       </c>
       <c r="B23" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3093,10 +3097,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>443391</v>
+        <v>443830</v>
       </c>
       <c r="R23" t="n">
-        <v>6766953</v>
+        <v>6766958</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3129,11 +3133,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3161,37 +3160,43 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127613169</v>
+        <v>127619035</v>
       </c>
       <c r="B24" t="n">
-        <v>79029</v>
+        <v>5177</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3199,10 +3204,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>443649</v>
+        <v>443270</v>
       </c>
       <c r="R24" t="n">
-        <v>6767135</v>
+        <v>6767248</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3235,11 +3240,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På 3 tallstammar</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3894,10 +3894,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127621213</v>
+        <v>127619291</v>
       </c>
       <c r="B31" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3905,31 +3905,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3937,10 +3932,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>443486</v>
+        <v>443357</v>
       </c>
       <c r="R31" t="n">
-        <v>6766960</v>
+        <v>6767070</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3977,7 +3972,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På 5 tallstammar</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3986,6 +3981,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4004,7 +4000,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127618880</v>
+        <v>127621213</v>
       </c>
       <c r="B32" t="n">
         <v>57672</v>
@@ -4047,10 +4043,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>443282</v>
+        <v>443486</v>
       </c>
       <c r="R32" t="n">
-        <v>6767309</v>
+        <v>6766960</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4087,7 +4083,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Har ant. ätit dubbelögda bastborre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4114,10 +4110,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127608356</v>
+        <v>127618880</v>
       </c>
       <c r="B33" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4125,26 +4121,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4152,10 +4153,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>443663</v>
+        <v>443282</v>
       </c>
       <c r="R33" t="n">
-        <v>6767132</v>
+        <v>6767309</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4192,7 +4193,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På 3 tallstammar</t>
+          <t>Har ant. ätit dubbelögda bastborre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4201,7 +4202,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4220,7 +4220,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127619291</v>
+        <v>127608356</v>
       </c>
       <c r="B34" t="n">
         <v>79029</v>
@@ -4258,10 +4258,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>443357</v>
+        <v>443663</v>
       </c>
       <c r="R34" t="n">
-        <v>6767070</v>
+        <v>6767132</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4298,7 +4298,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På 5 tallstammar</t>
+          <t>På 3 tallstammar</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4433,43 +4433,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127608027</v>
+        <v>127618637</v>
       </c>
       <c r="B36" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4477,10 +4471,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>443898</v>
+        <v>443286</v>
       </c>
       <c r="R36" t="n">
-        <v>6766974</v>
+        <v>6767436</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4540,7 +4534,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127618701</v>
+        <v>127608027</v>
       </c>
       <c r="B37" t="n">
         <v>8450</v>
@@ -4584,10 +4578,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>443327</v>
+        <v>443898</v>
       </c>
       <c r="R37" t="n">
-        <v>6767322</v>
+        <v>6766974</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4620,11 +4614,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>1 låga och 3 torraka</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4652,37 +4641,43 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127618637</v>
+        <v>127618701</v>
       </c>
       <c r="B38" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4690,10 +4685,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>443286</v>
+        <v>443327</v>
       </c>
       <c r="R38" t="n">
-        <v>6767436</v>
+        <v>6767322</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4726,6 +4721,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>1 låga och 3 torraka</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -7665,43 +7665,37 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127618658</v>
+        <v>127620944</v>
       </c>
       <c r="B67" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7709,10 +7703,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>443286</v>
+        <v>443383</v>
       </c>
       <c r="R67" t="n">
-        <v>6767436</v>
+        <v>6766978</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7749,7 +7743,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>På tallraka</t>
+          <t>På 5 tallstammar</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7777,7 +7771,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127620944</v>
+        <v>127618716</v>
       </c>
       <c r="B68" t="n">
         <v>79029</v>
@@ -7815,10 +7809,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>443383</v>
+        <v>443350</v>
       </c>
       <c r="R68" t="n">
-        <v>6766978</v>
+        <v>6767334</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7851,11 +7845,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>På 5 tallstammar</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7883,37 +7872,43 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127618716</v>
+        <v>127618658</v>
       </c>
       <c r="B69" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -7921,10 +7916,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>443350</v>
+        <v>443286</v>
       </c>
       <c r="R69" t="n">
-        <v>6767334</v>
+        <v>6767436</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7957,6 +7952,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>På tallraka</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7984,43 +7984,37 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127608037</v>
+        <v>127608339</v>
       </c>
       <c r="B70" t="n">
-        <v>8450</v>
+        <v>91372</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8028,10 +8022,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>443868</v>
+        <v>443750</v>
       </c>
       <c r="R70" t="n">
-        <v>6766980</v>
+        <v>6767090</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8196,37 +8190,43 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127608339</v>
+        <v>127608037</v>
       </c>
       <c r="B72" t="n">
-        <v>91372</v>
+        <v>8450</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -8234,10 +8234,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>443750</v>
+        <v>443868</v>
       </c>
       <c r="R72" t="n">
-        <v>6767090</v>
+        <v>6766980</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -13507,10 +13507,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127729110</v>
+        <v>127723564</v>
       </c>
       <c r="B124" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13518,34 +13518,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>443859</v>
+        <v>443650</v>
       </c>
       <c r="R124" t="n">
-        <v>6766840</v>
+        <v>6767089</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13575,19 +13575,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>16:37</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>16:37</t>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>På kolad stubbe med fyra brandljud</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13596,29 +13591,28 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127723246</v>
+        <v>127723573</v>
       </c>
       <c r="B125" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13626,21 +13620,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13650,10 +13644,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>443273</v>
+        <v>443275</v>
       </c>
       <c r="R125" t="n">
-        <v>6767242</v>
+        <v>6767333</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13712,10 +13706,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127723564</v>
+        <v>127722849</v>
       </c>
       <c r="B126" t="n">
-        <v>78696</v>
+        <v>79061</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13723,21 +13717,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13747,10 +13741,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>443650</v>
+        <v>443940</v>
       </c>
       <c r="R126" t="n">
-        <v>6767089</v>
+        <v>6766951</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13783,11 +13777,6 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>På kolad stubbe med fyra brandljud</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13814,7 +13803,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127723573</v>
+        <v>127723591</v>
       </c>
       <c r="B127" t="n">
         <v>78696</v>
@@ -13849,10 +13838,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>443275</v>
+        <v>443645</v>
       </c>
       <c r="R127" t="n">
-        <v>6767333</v>
+        <v>6767179</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13911,10 +13900,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127722849</v>
+        <v>127723216</v>
       </c>
       <c r="B128" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13922,21 +13911,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13946,10 +13935,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>443940</v>
+        <v>443420</v>
       </c>
       <c r="R128" t="n">
-        <v>6766951</v>
+        <v>6766981</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14008,10 +13997,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127723591</v>
+        <v>127723337</v>
       </c>
       <c r="B129" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14019,21 +14008,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14043,10 +14032,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>443645</v>
+        <v>443685</v>
       </c>
       <c r="R129" t="n">
-        <v>6767179</v>
+        <v>6767010</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14105,7 +14094,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127723337</v>
+        <v>127729098</v>
       </c>
       <c r="B130" t="n">
         <v>79029</v>
@@ -14136,14 +14125,14 @@
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>443685</v>
+        <v>443594</v>
       </c>
       <c r="R130" t="n">
-        <v>6767010</v>
+        <v>6767150</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14173,36 +14162,47 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
       <c r="AD130" t="b">
         <v>0</v>
       </c>
       <c r="AE130" t="b">
         <v>0</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127729098</v>
+        <v>127729110</v>
       </c>
       <c r="B131" t="n">
         <v>79029</v>
@@ -14237,10 +14237,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>443594</v>
+        <v>443859</v>
       </c>
       <c r="R131" t="n">
-        <v>6767150</v>
+        <v>6766840</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14272,7 +14272,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14282,7 +14282,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14709,7 +14709,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127723079</v>
+        <v>127723246</v>
       </c>
       <c r="B136" t="n">
         <v>79029</v>
@@ -14744,10 +14744,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>443619</v>
+        <v>443273</v>
       </c>
       <c r="R136" t="n">
-        <v>6766829</v>
+        <v>6767242</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14806,7 +14806,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127729113</v>
+        <v>127723079</v>
       </c>
       <c r="B137" t="n">
         <v>79029</v>
@@ -14837,14 +14837,14 @@
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>443866</v>
+        <v>443619</v>
       </c>
       <c r="R137" t="n">
-        <v>6766815</v>
+        <v>6766829</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14874,47 +14874,36 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z137" t="inlineStr">
-        <is>
-          <t>16:34</t>
-        </is>
-      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB137" t="inlineStr">
-        <is>
-          <t>16:34</t>
-        </is>
-      </c>
       <c r="AD137" t="b">
         <v>0</v>
       </c>
       <c r="AE137" t="b">
         <v>0</v>
       </c>
-      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127729078</v>
+        <v>127729113</v>
       </c>
       <c r="B138" t="n">
         <v>79029</v>
@@ -14949,10 +14938,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>443610</v>
+        <v>443866</v>
       </c>
       <c r="R138" t="n">
-        <v>6767120</v>
+        <v>6766815</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14984,7 +14973,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -14994,7 +14983,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15022,7 +15011,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127723378</v>
+        <v>127729078</v>
       </c>
       <c r="B139" t="n">
         <v>79029</v>
@@ -15053,14 +15042,14 @@
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>443795</v>
+        <v>443610</v>
       </c>
       <c r="R139" t="n">
-        <v>6767058</v>
+        <v>6767120</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15090,36 +15079,47 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
       <c r="AD139" t="b">
         <v>0</v>
       </c>
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127723216</v>
+        <v>127723378</v>
       </c>
       <c r="B140" t="n">
         <v>79029</v>
@@ -15154,10 +15154,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>443420</v>
+        <v>443795</v>
       </c>
       <c r="R140" t="n">
-        <v>6766981</v>
+        <v>6767058</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15216,7 +15216,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127722938</v>
+        <v>127722986</v>
       </c>
       <c r="B141" t="n">
         <v>8450</v>
@@ -15256,10 +15256,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>443618</v>
+        <v>443580</v>
       </c>
       <c r="R141" t="n">
-        <v>6766829</v>
+        <v>6767102</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15318,7 +15318,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127722986</v>
+        <v>127722939</v>
       </c>
       <c r="B142" t="n">
         <v>8450</v>
@@ -15358,10 +15358,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>443580</v>
+        <v>443661</v>
       </c>
       <c r="R142" t="n">
-        <v>6767102</v>
+        <v>6766786</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15420,7 +15420,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127722939</v>
+        <v>127722938</v>
       </c>
       <c r="B143" t="n">
         <v>8450</v>
@@ -15460,10 +15460,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>443661</v>
+        <v>443618</v>
       </c>
       <c r="R143" t="n">
-        <v>6766786</v>
+        <v>6766829</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15522,7 +15522,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127723317</v>
+        <v>127723357</v>
       </c>
       <c r="B144" t="n">
         <v>79029</v>
@@ -15557,10 +15557,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>443589</v>
+        <v>443931</v>
       </c>
       <c r="R144" t="n">
-        <v>6767070</v>
+        <v>6766931</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15619,10 +15619,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>127723326</v>
+        <v>127723582</v>
       </c>
       <c r="B145" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15630,21 +15630,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15654,10 +15654,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>443655</v>
+        <v>443606</v>
       </c>
       <c r="R145" t="n">
-        <v>6767102</v>
+        <v>6767114</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15716,10 +15716,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>127723207</v>
+        <v>127723579</v>
       </c>
       <c r="B146" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15727,21 +15727,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15751,10 +15751,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>443526</v>
+        <v>443583</v>
       </c>
       <c r="R146" t="n">
-        <v>6766954</v>
+        <v>6767093</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15813,45 +15813,45 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>127723263</v>
+        <v>127729075</v>
       </c>
       <c r="B147" t="n">
-        <v>79029</v>
+        <v>92654</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>443279</v>
+        <v>443903</v>
       </c>
       <c r="R147" t="n">
-        <v>6767392</v>
+        <v>6766793</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15881,36 +15881,47 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
       <c r="AD147" t="b">
         <v>0</v>
       </c>
       <c r="AE147" t="b">
         <v>0</v>
       </c>
+      <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
       </c>
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>127723234</v>
+        <v>127729129</v>
       </c>
       <c r="B148" t="n">
         <v>79029</v>
@@ -15941,14 +15952,14 @@
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>443321</v>
+        <v>443947</v>
       </c>
       <c r="R148" t="n">
-        <v>6767103</v>
+        <v>6766584</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15978,39 +15989,50 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
       <c r="AD148" t="b">
         <v>0</v>
       </c>
       <c r="AE148" t="b">
         <v>0</v>
       </c>
+      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
       </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>127723582</v>
+        <v>127723248</v>
       </c>
       <c r="B149" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16018,21 +16040,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16042,10 +16064,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>443606</v>
+        <v>443275</v>
       </c>
       <c r="R149" t="n">
-        <v>6767114</v>
+        <v>6767256</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16104,10 +16126,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>127723579</v>
+        <v>127723236</v>
       </c>
       <c r="B150" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16115,21 +16137,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16139,10 +16161,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>443583</v>
+        <v>443310</v>
       </c>
       <c r="R150" t="n">
-        <v>6767093</v>
+        <v>6767138</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16201,32 +16223,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>127729075</v>
+        <v>127729106</v>
       </c>
       <c r="B151" t="n">
-        <v>92654</v>
+        <v>79029</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16236,10 +16258,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>443903</v>
+        <v>443777</v>
       </c>
       <c r="R151" t="n">
-        <v>6766793</v>
+        <v>6766919</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16271,7 +16293,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16281,7 +16303,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16309,7 +16331,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>127729129</v>
+        <v>127723213</v>
       </c>
       <c r="B152" t="n">
         <v>79029</v>
@@ -16340,14 +16362,14 @@
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>443947</v>
+        <v>443470</v>
       </c>
       <c r="R152" t="n">
-        <v>6766584</v>
+        <v>6766976</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16377,47 +16399,36 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z152" t="inlineStr">
-        <is>
-          <t>15:17</t>
-        </is>
-      </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB152" t="inlineStr">
-        <is>
-          <t>15:17</t>
-        </is>
-      </c>
       <c r="AD152" t="b">
         <v>0</v>
       </c>
       <c r="AE152" t="b">
         <v>0</v>
       </c>
-      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>127723248</v>
+        <v>127723199</v>
       </c>
       <c r="B153" t="n">
         <v>79029</v>
@@ -16452,10 +16463,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>443275</v>
+        <v>443540</v>
       </c>
       <c r="R153" t="n">
-        <v>6767256</v>
+        <v>6766894</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16514,7 +16525,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>127723357</v>
+        <v>127723370</v>
       </c>
       <c r="B154" t="n">
         <v>79029</v>
@@ -16549,10 +16560,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>443931</v>
+        <v>443826</v>
       </c>
       <c r="R154" t="n">
-        <v>6766931</v>
+        <v>6767008</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16611,7 +16622,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>127723236</v>
+        <v>127730382</v>
       </c>
       <c r="B155" t="n">
         <v>79029</v>
@@ -16640,16 +16651,19 @@
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S om, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>443310</v>
+        <v>443332</v>
       </c>
       <c r="R155" t="n">
-        <v>6767138</v>
+        <v>6767071</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16684,31 +16698,37 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>På 10 tallstammar</t>
+        </is>
+      </c>
       <c r="AD155" t="b">
         <v>0</v>
       </c>
       <c r="AE155" t="b">
         <v>0</v>
       </c>
+      <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="b">
         <v>0</v>
       </c>
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>127729106</v>
+        <v>127723317</v>
       </c>
       <c r="B156" t="n">
         <v>79029</v>
@@ -16739,14 +16759,14 @@
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>443777</v>
+        <v>443589</v>
       </c>
       <c r="R156" t="n">
-        <v>6766919</v>
+        <v>6767070</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16776,47 +16796,36 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z156" t="inlineStr">
-        <is>
-          <t>16:47</t>
-        </is>
-      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB156" t="inlineStr">
-        <is>
-          <t>16:47</t>
-        </is>
-      </c>
       <c r="AD156" t="b">
         <v>0</v>
       </c>
       <c r="AE156" t="b">
         <v>0</v>
       </c>
-      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>127723213</v>
+        <v>127723326</v>
       </c>
       <c r="B157" t="n">
         <v>79029</v>
@@ -16851,10 +16860,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>443470</v>
+        <v>443655</v>
       </c>
       <c r="R157" t="n">
-        <v>6766976</v>
+        <v>6767102</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16913,7 +16922,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>127723199</v>
+        <v>127723207</v>
       </c>
       <c r="B158" t="n">
         <v>79029</v>
@@ -16948,10 +16957,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>443540</v>
+        <v>443526</v>
       </c>
       <c r="R158" t="n">
-        <v>6766894</v>
+        <v>6766954</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17010,7 +17019,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>127723370</v>
+        <v>127723263</v>
       </c>
       <c r="B159" t="n">
         <v>79029</v>
@@ -17045,10 +17054,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>443826</v>
+        <v>443279</v>
       </c>
       <c r="R159" t="n">
-        <v>6767008</v>
+        <v>6767392</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17107,7 +17116,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>127730382</v>
+        <v>127723234</v>
       </c>
       <c r="B160" t="n">
         <v>79029</v>
@@ -17136,19 +17145,16 @@
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
-      <c r="J160" t="inlineStr"/>
-      <c r="K160" t="inlineStr"/>
-      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Oxeråsen S om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>443332</v>
+        <v>443321</v>
       </c>
       <c r="R160" t="n">
-        <v>6767071</v>
+        <v>6767103</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17183,30 +17189,24 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>På 10 tallstammar</t>
-        </is>
-      </c>
       <c r="AD160" t="b">
         <v>0</v>
       </c>
       <c r="AE160" t="b">
         <v>0</v>
       </c>
-      <c r="AF160" t="inlineStr"/>
       <c r="AG160" t="b">
         <v>0</v>
       </c>
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
@@ -17315,10 +17315,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>127722995</v>
+        <v>127722803</v>
       </c>
       <c r="B162" t="n">
-        <v>8450</v>
+        <v>5197</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17326,21 +17326,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17355,10 +17355,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>443979</v>
+        <v>443270</v>
       </c>
       <c r="R162" t="n">
-        <v>6766943</v>
+        <v>6767291</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17417,10 +17417,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>127722803</v>
+        <v>127722995</v>
       </c>
       <c r="B163" t="n">
-        <v>5197</v>
+        <v>8450</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17428,21 +17428,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>105930</v>
+        <v>106545</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17457,10 +17457,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>443270</v>
+        <v>443979</v>
       </c>
       <c r="R163" t="n">
-        <v>6767291</v>
+        <v>6766943</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17923,50 +17923,45 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>127723003</v>
+        <v>127723580</v>
       </c>
       <c r="B168" t="n">
-        <v>8450</v>
+        <v>78696</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P168" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>443826</v>
+        <v>443589</v>
       </c>
       <c r="R168" t="n">
-        <v>6767094</v>
+        <v>6767070</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18025,50 +18020,45 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>127723005</v>
+        <v>127723577</v>
       </c>
       <c r="B169" t="n">
-        <v>8450</v>
+        <v>78696</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
-      <c r="M169" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P169" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>443760</v>
+        <v>443607</v>
       </c>
       <c r="R169" t="n">
-        <v>6767115</v>
+        <v>6767160</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18127,50 +18117,45 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>127722964</v>
+        <v>127723238</v>
       </c>
       <c r="B170" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P170" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>443313</v>
+        <v>443333</v>
       </c>
       <c r="R170" t="n">
-        <v>6767122</v>
+        <v>6767173</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18229,54 +18214,45 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>127729088</v>
+        <v>127723390</v>
       </c>
       <c r="B171" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
-      <c r="J171" t="inlineStr"/>
-      <c r="K171" t="inlineStr"/>
-      <c r="L171" t="inlineStr"/>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>443854</v>
+        <v>443729</v>
       </c>
       <c r="R171" t="n">
-        <v>6766866</v>
+        <v>6767169</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18306,50 +18282,39 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z171" t="inlineStr">
-        <is>
-          <t>16:40</t>
-        </is>
-      </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB171" t="inlineStr">
-        <is>
-          <t>16:40</t>
-        </is>
-      </c>
       <c r="AD171" t="b">
         <v>0</v>
       </c>
       <c r="AE171" t="b">
         <v>0</v>
       </c>
-      <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="b">
         <v>0</v>
       </c>
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>127723580</v>
+        <v>127723209</v>
       </c>
       <c r="B172" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18357,21 +18322,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18381,10 +18346,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>443589</v>
+        <v>443502</v>
       </c>
       <c r="R172" t="n">
-        <v>6767070</v>
+        <v>6766972</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18443,10 +18408,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>127723577</v>
+        <v>127729116</v>
       </c>
       <c r="B173" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18454,34 +18419,34 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>443607</v>
+        <v>443899</v>
       </c>
       <c r="R173" t="n">
-        <v>6767160</v>
+        <v>6766758</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18511,39 +18476,50 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
       <c r="AA173" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB173" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
       <c r="AD173" t="b">
         <v>0</v>
       </c>
       <c r="AE173" t="b">
         <v>0</v>
       </c>
+      <c r="AF173" t="inlineStr"/>
       <c r="AG173" t="b">
         <v>0</v>
       </c>
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>127722907</v>
+        <v>127729080</v>
       </c>
       <c r="B174" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18551,39 +18527,34 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
-      <c r="M174" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>443485</v>
+        <v>443643</v>
       </c>
       <c r="R174" t="n">
-        <v>6766960</v>
+        <v>6767081</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18613,14 +18584,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z174" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
       <c r="AA174" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC174" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
+      <c r="AB174" t="inlineStr">
+        <is>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -18629,28 +18605,29 @@
       <c r="AE174" t="b">
         <v>0</v>
       </c>
+      <c r="AF174" t="inlineStr"/>
       <c r="AG174" t="b">
         <v>0</v>
       </c>
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>127723060</v>
+        <v>127723220</v>
       </c>
       <c r="B175" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18658,21 +18635,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18682,10 +18659,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>443583</v>
+        <v>443452</v>
       </c>
       <c r="R175" t="n">
-        <v>6767184</v>
+        <v>6767071</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18726,7 +18703,6 @@
       <c r="AE175" t="b">
         <v>0</v>
       </c>
-      <c r="AF175" t="inlineStr"/>
       <c r="AG175" t="b">
         <v>0</v>
       </c>
@@ -18745,50 +18721,45 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>127723613</v>
+        <v>127723256</v>
       </c>
       <c r="B176" t="n">
-        <v>5177</v>
+        <v>79029</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
-      <c r="M176" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P176" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>443517</v>
+        <v>443302</v>
       </c>
       <c r="R176" t="n">
-        <v>6766984</v>
+        <v>6767306</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18847,7 +18818,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>127723238</v>
+        <v>127723288</v>
       </c>
       <c r="B177" t="n">
         <v>79029</v>
@@ -18882,10 +18853,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>443333</v>
+        <v>443316</v>
       </c>
       <c r="R177" t="n">
-        <v>6767173</v>
+        <v>6767429</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18944,10 +18915,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>127723390</v>
+        <v>127723060</v>
       </c>
       <c r="B178" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18955,21 +18926,21 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -18979,10 +18950,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>443729</v>
+        <v>443583</v>
       </c>
       <c r="R178" t="n">
-        <v>6767169</v>
+        <v>6767184</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19023,6 +18994,7 @@
       <c r="AE178" t="b">
         <v>0</v>
       </c>
+      <c r="AF178" t="inlineStr"/>
       <c r="AG178" t="b">
         <v>0</v>
       </c>
@@ -19041,45 +19013,50 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>127723209</v>
+        <v>127723613</v>
       </c>
       <c r="B179" t="n">
-        <v>79029</v>
+        <v>5177</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P179" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>443502</v>
+        <v>443517</v>
       </c>
       <c r="R179" t="n">
-        <v>6766972</v>
+        <v>6766984</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19138,45 +19115,50 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>127729116</v>
+        <v>127723005</v>
       </c>
       <c r="B180" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>443899</v>
+        <v>443760</v>
       </c>
       <c r="R180" t="n">
-        <v>6766758</v>
+        <v>6767115</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19206,85 +19188,83 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z180" t="inlineStr">
-        <is>
-          <t>16:14</t>
-        </is>
-      </c>
       <c r="AA180" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB180" t="inlineStr">
-        <is>
-          <t>16:14</t>
-        </is>
-      </c>
       <c r="AD180" t="b">
         <v>0</v>
       </c>
       <c r="AE180" t="b">
         <v>0</v>
       </c>
-      <c r="AF180" t="inlineStr"/>
       <c r="AG180" t="b">
         <v>0</v>
       </c>
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>127729080</v>
+        <v>127729088</v>
       </c>
       <c r="B181" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
           <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>443643</v>
+        <v>443854</v>
       </c>
       <c r="R181" t="n">
-        <v>6767081</v>
+        <v>6766866</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19316,7 +19296,7 @@
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
@@ -19326,7 +19306,7 @@
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -19354,10 +19334,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>127723220</v>
+        <v>127722907</v>
       </c>
       <c r="B182" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19365,34 +19345,39 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P182" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>443452</v>
+        <v>443485</v>
       </c>
       <c r="R182" t="n">
-        <v>6767071</v>
+        <v>6766960</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19425,6 +19410,11 @@
       <c r="AA182" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC182" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -19451,45 +19441,50 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>127723256</v>
+        <v>127723003</v>
       </c>
       <c r="B183" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P183" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>443302</v>
+        <v>443826</v>
       </c>
       <c r="R183" t="n">
-        <v>6767306</v>
+        <v>6767094</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19548,45 +19543,50 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>127723288</v>
+        <v>127722964</v>
       </c>
       <c r="B184" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P184" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>443316</v>
+        <v>443313</v>
       </c>
       <c r="R184" t="n">
-        <v>6767429</v>
+        <v>6767122</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -29139,7 +29139,7 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>127723280</v>
+        <v>127723296</v>
       </c>
       <c r="B280" t="n">
         <v>79029</v>
@@ -29174,10 +29174,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>443281</v>
+        <v>443372</v>
       </c>
       <c r="R280" t="n">
-        <v>6767440</v>
+        <v>6767321</v>
       </c>
       <c r="S280" t="n">
         <v>10</v>
@@ -29236,10 +29236,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>127729117</v>
+        <v>127722911</v>
       </c>
       <c r="B281" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -29247,34 +29247,39 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P281" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>443904</v>
+        <v>443272</v>
       </c>
       <c r="R281" t="n">
-        <v>6766753</v>
+        <v>6767269</v>
       </c>
       <c r="S281" t="n">
         <v>10</v>
@@ -29304,19 +29309,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z281" t="inlineStr">
-        <is>
-          <t>16:13</t>
-        </is>
-      </c>
       <c r="AA281" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB281" t="inlineStr">
-        <is>
-          <t>16:13</t>
+      <c r="AC281" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD281" t="b">
@@ -29325,64 +29325,68 @@
       <c r="AE281" t="b">
         <v>0</v>
       </c>
-      <c r="AF281" t="inlineStr"/>
       <c r="AG281" t="b">
         <v>0</v>
       </c>
       <c r="AT281" t="inlineStr"/>
       <c r="AW281" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX281" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>127729130</v>
+        <v>127723006</v>
       </c>
       <c r="B282" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I282" t="inlineStr"/>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P282" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>443942</v>
+        <v>443749</v>
       </c>
       <c r="R282" t="n">
-        <v>6766584</v>
+        <v>6767151</v>
       </c>
       <c r="S282" t="n">
         <v>10</v>
@@ -29412,85 +29416,79 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z282" t="inlineStr">
-        <is>
-          <t>15:17</t>
-        </is>
-      </c>
       <c r="AA282" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB282" t="inlineStr">
-        <is>
-          <t>15:17</t>
-        </is>
-      </c>
       <c r="AD282" t="b">
         <v>0</v>
       </c>
       <c r="AE282" t="b">
         <v>0</v>
       </c>
-      <c r="AF282" t="inlineStr"/>
       <c r="AG282" t="b">
         <v>0</v>
       </c>
       <c r="AT282" t="inlineStr"/>
       <c r="AW282" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX282" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>127723249</v>
+        <v>127723009</v>
       </c>
       <c r="B283" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I283" t="inlineStr"/>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P283" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>443272</v>
+        <v>443652</v>
       </c>
       <c r="R283" t="n">
-        <v>6767269</v>
+        <v>6767168</v>
       </c>
       <c r="S283" t="n">
         <v>10</v>
@@ -29549,10 +29547,10 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>127722820</v>
+        <v>127723280</v>
       </c>
       <c r="B284" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -29560,21 +29558,21 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I284" t="inlineStr"/>
@@ -29584,10 +29582,10 @@
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>443903</v>
+        <v>443281</v>
       </c>
       <c r="R284" t="n">
-        <v>6766943</v>
+        <v>6767440</v>
       </c>
       <c r="S284" t="n">
         <v>10</v>
@@ -29646,10 +29644,10 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>127730386</v>
+        <v>127729117</v>
       </c>
       <c r="B285" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -29657,37 +29655,34 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I285" t="inlineStr"/>
-      <c r="J285" t="inlineStr"/>
-      <c r="K285" t="inlineStr"/>
-      <c r="N285" t="inlineStr"/>
       <c r="P285" t="inlineStr">
         <is>
-          <t>Oxeråsen S om, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>443335</v>
+        <v>443904</v>
       </c>
       <c r="R285" t="n">
-        <v>6767051</v>
+        <v>6766753</v>
       </c>
       <c r="S285" t="n">
         <v>10</v>
@@ -29717,9 +29712,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z285" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
       <c r="AA285" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB285" t="inlineStr">
+        <is>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD285" t="b">
@@ -29747,50 +29752,45 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>127723006</v>
+        <v>127729130</v>
       </c>
       <c r="B286" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E286" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I286" t="inlineStr"/>
-      <c r="M286" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P286" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>443749</v>
+        <v>443942</v>
       </c>
       <c r="R286" t="n">
-        <v>6767151</v>
+        <v>6766584</v>
       </c>
       <c r="S286" t="n">
         <v>10</v>
@@ -29820,79 +29820,85 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z286" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
       <c r="AA286" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB286" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
       <c r="AD286" t="b">
         <v>0</v>
       </c>
       <c r="AE286" t="b">
         <v>0</v>
       </c>
+      <c r="AF286" t="inlineStr"/>
       <c r="AG286" t="b">
         <v>0</v>
       </c>
       <c r="AT286" t="inlineStr"/>
       <c r="AW286" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX286" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>127723009</v>
+        <v>127723249</v>
       </c>
       <c r="B287" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E287" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I287" t="inlineStr"/>
-      <c r="M287" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P287" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>443652</v>
+        <v>443272</v>
       </c>
       <c r="R287" t="n">
-        <v>6767168</v>
+        <v>6767269</v>
       </c>
       <c r="S287" t="n">
         <v>10</v>
@@ -29951,10 +29957,10 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>127723296</v>
+        <v>127722820</v>
       </c>
       <c r="B288" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -29962,21 +29968,21 @@
         </is>
       </c>
       <c r="E288" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I288" t="inlineStr"/>
@@ -29986,10 +29992,10 @@
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>443372</v>
+        <v>443903</v>
       </c>
       <c r="R288" t="n">
-        <v>6767321</v>
+        <v>6766943</v>
       </c>
       <c r="S288" t="n">
         <v>10</v>
@@ -30048,10 +30054,10 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>127723253</v>
+        <v>127730386</v>
       </c>
       <c r="B289" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -30059,34 +30065,37 @@
         </is>
       </c>
       <c r="E289" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I289" t="inlineStr"/>
+      <c r="J289" t="inlineStr"/>
+      <c r="K289" t="inlineStr"/>
+      <c r="N289" t="inlineStr"/>
       <c r="P289" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S om, Dlr</t>
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>443258</v>
+        <v>443335</v>
       </c>
       <c r="R289" t="n">
-        <v>6767313</v>
+        <v>6767051</v>
       </c>
       <c r="S289" t="n">
         <v>10</v>
@@ -30127,25 +30136,26 @@
       <c r="AE289" t="b">
         <v>0</v>
       </c>
+      <c r="AF289" t="inlineStr"/>
       <c r="AG289" t="b">
         <v>0</v>
       </c>
       <c r="AT289" t="inlineStr"/>
       <c r="AW289" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX289" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>127723320</v>
+        <v>127723253</v>
       </c>
       <c r="B290" t="n">
         <v>79029</v>
@@ -30180,10 +30190,10 @@
         </is>
       </c>
       <c r="Q290" t="n">
-        <v>443616</v>
+        <v>443258</v>
       </c>
       <c r="R290" t="n">
-        <v>6767105</v>
+        <v>6767313</v>
       </c>
       <c r="S290" t="n">
         <v>10</v>
@@ -30242,10 +30252,10 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>127722911</v>
+        <v>127723320</v>
       </c>
       <c r="B291" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -30253,39 +30263,34 @@
         </is>
       </c>
       <c r="E291" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I291" t="inlineStr"/>
-      <c r="M291" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P291" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q291" t="n">
-        <v>443272</v>
+        <v>443616</v>
       </c>
       <c r="R291" t="n">
-        <v>6767269</v>
+        <v>6767105</v>
       </c>
       <c r="S291" t="n">
         <v>10</v>
@@ -30318,11 +30323,6 @@
       <c r="AA291" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC291" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD291" t="b">
@@ -35321,10 +35321,10 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>127730396</v>
+        <v>127729076</v>
       </c>
       <c r="B342" t="n">
-        <v>92642</v>
+        <v>92654</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -35332,45 +35332,34 @@
         </is>
       </c>
       <c r="E342" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I342" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J342" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K342" t="inlineStr"/>
-      <c r="N342" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr"/>
       <c r="P342" t="inlineStr">
         <is>
-          <t>Oxeråsen S om, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q342" t="n">
-        <v>443376</v>
+        <v>443894</v>
       </c>
       <c r="R342" t="n">
-        <v>6767009</v>
+        <v>6766720</v>
       </c>
       <c r="S342" t="n">
         <v>10</v>
@@ -35400,9 +35389,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z342" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
       <c r="AA342" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB342" t="inlineStr">
+        <is>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD342" t="b">
@@ -35430,45 +35429,45 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>127729076</v>
+        <v>127723211</v>
       </c>
       <c r="B343" t="n">
-        <v>92654</v>
+        <v>79029</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E343" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I343" t="inlineStr"/>
       <c r="P343" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q343" t="n">
-        <v>443894</v>
+        <v>443486</v>
       </c>
       <c r="R343" t="n">
-        <v>6766720</v>
+        <v>6766965</v>
       </c>
       <c r="S343" t="n">
         <v>10</v>
@@ -35498,47 +35497,36 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z343" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
       <c r="AA343" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB343" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
       <c r="AD343" t="b">
         <v>0</v>
       </c>
       <c r="AE343" t="b">
         <v>0</v>
       </c>
-      <c r="AF343" t="inlineStr"/>
       <c r="AG343" t="b">
         <v>0</v>
       </c>
       <c r="AT343" t="inlineStr"/>
       <c r="AW343" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX343" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>127723211</v>
+        <v>127723553</v>
       </c>
       <c r="B344" t="n">
         <v>79029</v>
@@ -35573,10 +35561,10 @@
         </is>
       </c>
       <c r="Q344" t="n">
-        <v>443486</v>
+        <v>443748</v>
       </c>
       <c r="R344" t="n">
-        <v>6766965</v>
+        <v>6767154</v>
       </c>
       <c r="S344" t="n">
         <v>10</v>
@@ -35635,7 +35623,7 @@
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>127723553</v>
+        <v>127729131</v>
       </c>
       <c r="B345" t="n">
         <v>79029</v>
@@ -35666,14 +35654,14 @@
       <c r="I345" t="inlineStr"/>
       <c r="P345" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q345" t="n">
-        <v>443748</v>
+        <v>443929</v>
       </c>
       <c r="R345" t="n">
-        <v>6767154</v>
+        <v>6766582</v>
       </c>
       <c r="S345" t="n">
         <v>10</v>
@@ -35703,36 +35691,47 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z345" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
       <c r="AA345" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB345" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
       <c r="AD345" t="b">
         <v>0</v>
       </c>
       <c r="AE345" t="b">
         <v>0</v>
       </c>
+      <c r="AF345" t="inlineStr"/>
       <c r="AG345" t="b">
         <v>0</v>
       </c>
       <c r="AT345" t="inlineStr"/>
       <c r="AW345" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX345" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>127729131</v>
+        <v>127723352</v>
       </c>
       <c r="B346" t="n">
         <v>79029</v>
@@ -35763,14 +35762,14 @@
       <c r="I346" t="inlineStr"/>
       <c r="P346" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q346" t="n">
-        <v>443929</v>
+        <v>443848</v>
       </c>
       <c r="R346" t="n">
-        <v>6766582</v>
+        <v>6766953</v>
       </c>
       <c r="S346" t="n">
         <v>10</v>
@@ -35800,47 +35799,36 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z346" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
       <c r="AA346" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB346" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
       <c r="AD346" t="b">
         <v>0</v>
       </c>
       <c r="AE346" t="b">
         <v>0</v>
       </c>
-      <c r="AF346" t="inlineStr"/>
       <c r="AG346" t="b">
         <v>0</v>
       </c>
       <c r="AT346" t="inlineStr"/>
       <c r="AW346" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX346" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>127723352</v>
+        <v>127723328</v>
       </c>
       <c r="B347" t="n">
         <v>79029</v>
@@ -35875,10 +35863,10 @@
         </is>
       </c>
       <c r="Q347" t="n">
-        <v>443848</v>
+        <v>443653</v>
       </c>
       <c r="R347" t="n">
-        <v>6766953</v>
+        <v>6767086</v>
       </c>
       <c r="S347" t="n">
         <v>10</v>
@@ -35937,7 +35925,7 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>127723328</v>
+        <v>127729097</v>
       </c>
       <c r="B348" t="n">
         <v>79029</v>
@@ -35968,14 +35956,14 @@
       <c r="I348" t="inlineStr"/>
       <c r="P348" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q348" t="n">
-        <v>443653</v>
+        <v>443579</v>
       </c>
       <c r="R348" t="n">
-        <v>6767086</v>
+        <v>6767150</v>
       </c>
       <c r="S348" t="n">
         <v>10</v>
@@ -36005,36 +35993,47 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z348" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
       <c r="AA348" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB348" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
       <c r="AD348" t="b">
         <v>0</v>
       </c>
       <c r="AE348" t="b">
         <v>0</v>
       </c>
+      <c r="AF348" t="inlineStr"/>
       <c r="AG348" t="b">
         <v>0</v>
       </c>
       <c r="AT348" t="inlineStr"/>
       <c r="AW348" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX348" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>127729097</v>
+        <v>127723348</v>
       </c>
       <c r="B349" t="n">
         <v>79029</v>
@@ -36065,14 +36064,14 @@
       <c r="I349" t="inlineStr"/>
       <c r="P349" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q349" t="n">
-        <v>443579</v>
+        <v>443814</v>
       </c>
       <c r="R349" t="n">
-        <v>6767150</v>
+        <v>6766946</v>
       </c>
       <c r="S349" t="n">
         <v>10</v>
@@ -36102,47 +36101,36 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z349" t="inlineStr">
-        <is>
-          <t>17:10</t>
-        </is>
-      </c>
       <c r="AA349" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB349" t="inlineStr">
-        <is>
-          <t>17:10</t>
-        </is>
-      </c>
       <c r="AD349" t="b">
         <v>0</v>
       </c>
       <c r="AE349" t="b">
         <v>0</v>
       </c>
-      <c r="AF349" t="inlineStr"/>
       <c r="AG349" t="b">
         <v>0</v>
       </c>
       <c r="AT349" t="inlineStr"/>
       <c r="AW349" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX349" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>127723348</v>
+        <v>127723313</v>
       </c>
       <c r="B350" t="n">
         <v>79029</v>
@@ -36177,10 +36165,10 @@
         </is>
       </c>
       <c r="Q350" t="n">
-        <v>443814</v>
+        <v>443612</v>
       </c>
       <c r="R350" t="n">
-        <v>6766946</v>
+        <v>6767149</v>
       </c>
       <c r="S350" t="n">
         <v>10</v>
@@ -36239,7 +36227,7 @@
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>127723313</v>
+        <v>127729120</v>
       </c>
       <c r="B351" t="n">
         <v>79029</v>
@@ -36270,14 +36258,14 @@
       <c r="I351" t="inlineStr"/>
       <c r="P351" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q351" t="n">
-        <v>443612</v>
+        <v>443935</v>
       </c>
       <c r="R351" t="n">
-        <v>6767149</v>
+        <v>6766723</v>
       </c>
       <c r="S351" t="n">
         <v>10</v>
@@ -36307,39 +36295,50 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z351" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
       <c r="AA351" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB351" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
       <c r="AD351" t="b">
         <v>0</v>
       </c>
       <c r="AE351" t="b">
         <v>0</v>
       </c>
+      <c r="AF351" t="inlineStr"/>
       <c r="AG351" t="b">
         <v>0</v>
       </c>
       <c r="AT351" t="inlineStr"/>
       <c r="AW351" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX351" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>127729120</v>
+        <v>127722812</v>
       </c>
       <c r="B352" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -36347,34 +36346,34 @@
         </is>
       </c>
       <c r="E352" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I352" t="inlineStr"/>
       <c r="P352" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q352" t="n">
-        <v>443935</v>
+        <v>443600</v>
       </c>
       <c r="R352" t="n">
-        <v>6766723</v>
+        <v>6767125</v>
       </c>
       <c r="S352" t="n">
         <v>10</v>
@@ -36404,50 +36403,39 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z352" t="inlineStr">
-        <is>
-          <t>16:10</t>
-        </is>
-      </c>
       <c r="AA352" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB352" t="inlineStr">
-        <is>
-          <t>16:10</t>
-        </is>
-      </c>
       <c r="AD352" t="b">
         <v>0</v>
       </c>
       <c r="AE352" t="b">
         <v>0</v>
       </c>
-      <c r="AF352" t="inlineStr"/>
       <c r="AG352" t="b">
         <v>0</v>
       </c>
       <c r="AT352" t="inlineStr"/>
       <c r="AW352" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX352" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>127722812</v>
+        <v>127723333</v>
       </c>
       <c r="B353" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -36455,21 +36443,21 @@
         </is>
       </c>
       <c r="E353" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I353" t="inlineStr"/>
@@ -36479,10 +36467,10 @@
         </is>
       </c>
       <c r="Q353" t="n">
-        <v>443600</v>
+        <v>443690</v>
       </c>
       <c r="R353" t="n">
-        <v>6767125</v>
+        <v>6767074</v>
       </c>
       <c r="S353" t="n">
         <v>10</v>
@@ -36541,7 +36529,7 @@
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>127723333</v>
+        <v>127723258</v>
       </c>
       <c r="B354" t="n">
         <v>79029</v>
@@ -36576,10 +36564,10 @@
         </is>
       </c>
       <c r="Q354" t="n">
-        <v>443690</v>
+        <v>443306</v>
       </c>
       <c r="R354" t="n">
-        <v>6767074</v>
+        <v>6767334</v>
       </c>
       <c r="S354" t="n">
         <v>10</v>
@@ -36638,7 +36626,7 @@
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>127723258</v>
+        <v>127723219</v>
       </c>
       <c r="B355" t="n">
         <v>79029</v>
@@ -36673,10 +36661,10 @@
         </is>
       </c>
       <c r="Q355" t="n">
-        <v>443306</v>
+        <v>443442</v>
       </c>
       <c r="R355" t="n">
-        <v>6767334</v>
+        <v>6767042</v>
       </c>
       <c r="S355" t="n">
         <v>10</v>
@@ -36735,45 +36723,56 @@
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>127723219</v>
+        <v>127730396</v>
       </c>
       <c r="B356" t="n">
-        <v>79029</v>
+        <v>92642</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E356" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I356" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr"/>
+      <c r="N356" t="inlineStr"/>
       <c r="P356" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S om, Dlr</t>
         </is>
       </c>
       <c r="Q356" t="n">
-        <v>443442</v>
+        <v>443376</v>
       </c>
       <c r="R356" t="n">
-        <v>6767042</v>
+        <v>6767009</v>
       </c>
       <c r="S356" t="n">
         <v>10</v>
@@ -36814,18 +36813,19 @@
       <c r="AE356" t="b">
         <v>0</v>
       </c>
+      <c r="AF356" t="inlineStr"/>
       <c r="AG356" t="b">
         <v>0</v>
       </c>
       <c r="AT356" t="inlineStr"/>
       <c r="AW356" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX356" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY356" t="inlineStr"/>
@@ -37146,45 +37146,50 @@
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>127723231</v>
+        <v>127722994</v>
       </c>
       <c r="B360" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E360" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I360" t="inlineStr"/>
+      <c r="M360" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P360" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q360" t="n">
-        <v>443313</v>
+        <v>443987</v>
       </c>
       <c r="R360" t="n">
-        <v>6767074</v>
+        <v>6766929</v>
       </c>
       <c r="S360" t="n">
         <v>10</v>
@@ -37243,45 +37248,50 @@
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>127723327</v>
+        <v>127722989</v>
       </c>
       <c r="B361" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E361" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I361" t="inlineStr"/>
+      <c r="M361" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P361" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q361" t="n">
-        <v>443650</v>
+        <v>443668</v>
       </c>
       <c r="R361" t="n">
-        <v>6767097</v>
+        <v>6767052</v>
       </c>
       <c r="S361" t="n">
         <v>10</v>
@@ -37340,50 +37350,45 @@
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>127722994</v>
+        <v>127723239</v>
       </c>
       <c r="B362" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E362" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I362" t="inlineStr"/>
-      <c r="M362" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P362" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q362" t="n">
-        <v>443987</v>
+        <v>443281</v>
       </c>
       <c r="R362" t="n">
-        <v>6766929</v>
+        <v>6767174</v>
       </c>
       <c r="S362" t="n">
         <v>10</v>
@@ -37442,50 +37447,45 @@
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>127722989</v>
+        <v>127722837</v>
       </c>
       <c r="B363" t="n">
-        <v>8450</v>
+        <v>75153</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E363" t="n">
-        <v>106545</v>
+        <v>6440</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I363" t="inlineStr"/>
-      <c r="M363" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P363" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q363" t="n">
-        <v>443668</v>
+        <v>443811</v>
       </c>
       <c r="R363" t="n">
-        <v>6767052</v>
+        <v>6767031</v>
       </c>
       <c r="S363" t="n">
         <v>10</v>
@@ -37518,6 +37518,11 @@
       <c r="AA363" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC363" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD363" t="b">
@@ -37544,10 +37549,10 @@
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>127723048</v>
+        <v>127723311</v>
       </c>
       <c r="B364" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -37555,21 +37560,21 @@
         </is>
       </c>
       <c r="E364" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I364" t="inlineStr"/>
@@ -37579,10 +37584,10 @@
         </is>
       </c>
       <c r="Q364" t="n">
-        <v>443796</v>
+        <v>443555</v>
       </c>
       <c r="R364" t="n">
-        <v>6767030</v>
+        <v>6767164</v>
       </c>
       <c r="S364" t="n">
         <v>10</v>
@@ -37641,10 +37646,10 @@
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>127723047</v>
+        <v>127723245</v>
       </c>
       <c r="B365" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -37652,21 +37657,21 @@
         </is>
       </c>
       <c r="E365" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I365" t="inlineStr"/>
@@ -37676,10 +37681,10 @@
         </is>
       </c>
       <c r="Q365" t="n">
-        <v>443681</v>
+        <v>443267</v>
       </c>
       <c r="R365" t="n">
-        <v>6766998</v>
+        <v>6767237</v>
       </c>
       <c r="S365" t="n">
         <v>10</v>
@@ -37738,10 +37743,10 @@
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>127723578</v>
+        <v>127723048</v>
       </c>
       <c r="B366" t="n">
-        <v>78696</v>
+        <v>78788</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -37749,21 +37754,21 @@
         </is>
       </c>
       <c r="E366" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I366" t="inlineStr"/>
@@ -37773,10 +37778,10 @@
         </is>
       </c>
       <c r="Q366" t="n">
-        <v>443600</v>
+        <v>443796</v>
       </c>
       <c r="R366" t="n">
-        <v>6767127</v>
+        <v>6767030</v>
       </c>
       <c r="S366" t="n">
         <v>10</v>
@@ -37835,10 +37840,10 @@
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>127723567</v>
+        <v>127723047</v>
       </c>
       <c r="B367" t="n">
-        <v>78696</v>
+        <v>78788</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -37846,21 +37851,21 @@
         </is>
       </c>
       <c r="E367" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I367" t="inlineStr"/>
@@ -37870,10 +37875,10 @@
         </is>
       </c>
       <c r="Q367" t="n">
-        <v>443664</v>
+        <v>443681</v>
       </c>
       <c r="R367" t="n">
-        <v>6766781</v>
+        <v>6766998</v>
       </c>
       <c r="S367" t="n">
         <v>10</v>
@@ -37932,7 +37937,7 @@
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>127723583</v>
+        <v>127723578</v>
       </c>
       <c r="B368" t="n">
         <v>78696</v>
@@ -37967,10 +37972,10 @@
         </is>
       </c>
       <c r="Q368" t="n">
-        <v>443617</v>
+        <v>443600</v>
       </c>
       <c r="R368" t="n">
-        <v>6767104</v>
+        <v>6767127</v>
       </c>
       <c r="S368" t="n">
         <v>10</v>
@@ -38029,7 +38034,7 @@
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>127723589</v>
+        <v>127723567</v>
       </c>
       <c r="B369" t="n">
         <v>78696</v>
@@ -38064,10 +38069,10 @@
         </is>
       </c>
       <c r="Q369" t="n">
-        <v>443860</v>
+        <v>443664</v>
       </c>
       <c r="R369" t="n">
-        <v>6766996</v>
+        <v>6766781</v>
       </c>
       <c r="S369" t="n">
         <v>10</v>
@@ -38126,7 +38131,7 @@
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>127723588</v>
+        <v>127723583</v>
       </c>
       <c r="B370" t="n">
         <v>78696</v>
@@ -38161,10 +38166,10 @@
         </is>
       </c>
       <c r="Q370" t="n">
-        <v>443885</v>
+        <v>443617</v>
       </c>
       <c r="R370" t="n">
-        <v>6766988</v>
+        <v>6767104</v>
       </c>
       <c r="S370" t="n">
         <v>10</v>
@@ -38223,10 +38228,10 @@
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>127729108</v>
+        <v>127723589</v>
       </c>
       <c r="B371" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -38234,34 +38239,34 @@
         </is>
       </c>
       <c r="E371" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I371" t="inlineStr"/>
       <c r="P371" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q371" t="n">
-        <v>443852</v>
+        <v>443860</v>
       </c>
       <c r="R371" t="n">
-        <v>6766872</v>
+        <v>6766996</v>
       </c>
       <c r="S371" t="n">
         <v>10</v>
@@ -38291,50 +38296,39 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z371" t="inlineStr">
-        <is>
-          <t>16:41</t>
-        </is>
-      </c>
       <c r="AA371" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB371" t="inlineStr">
-        <is>
-          <t>16:41</t>
-        </is>
-      </c>
       <c r="AD371" t="b">
         <v>0</v>
       </c>
       <c r="AE371" t="b">
         <v>0</v>
       </c>
-      <c r="AF371" t="inlineStr"/>
       <c r="AG371" t="b">
         <v>0</v>
       </c>
       <c r="AT371" t="inlineStr"/>
       <c r="AW371" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX371" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>127729123</v>
+        <v>127723588</v>
       </c>
       <c r="B372" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -38342,34 +38336,34 @@
         </is>
       </c>
       <c r="E372" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I372" t="inlineStr"/>
       <c r="P372" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q372" t="n">
-        <v>443920</v>
+        <v>443885</v>
       </c>
       <c r="R372" t="n">
-        <v>6766713</v>
+        <v>6766988</v>
       </c>
       <c r="S372" t="n">
         <v>10</v>
@@ -38399,47 +38393,36 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z372" t="inlineStr">
-        <is>
-          <t>16:09</t>
-        </is>
-      </c>
       <c r="AA372" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB372" t="inlineStr">
-        <is>
-          <t>16:09</t>
-        </is>
-      </c>
       <c r="AD372" t="b">
         <v>0</v>
       </c>
       <c r="AE372" t="b">
         <v>0</v>
       </c>
-      <c r="AF372" t="inlineStr"/>
       <c r="AG372" t="b">
         <v>0</v>
       </c>
       <c r="AT372" t="inlineStr"/>
       <c r="AW372" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX372" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>127723292</v>
+        <v>127723231</v>
       </c>
       <c r="B373" t="n">
         <v>79029</v>
@@ -38474,10 +38457,10 @@
         </is>
       </c>
       <c r="Q373" t="n">
-        <v>443359</v>
+        <v>443313</v>
       </c>
       <c r="R373" t="n">
-        <v>6767352</v>
+        <v>6767074</v>
       </c>
       <c r="S373" t="n">
         <v>10</v>
@@ -38536,7 +38519,7 @@
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>127729119</v>
+        <v>127723327</v>
       </c>
       <c r="B374" t="n">
         <v>79029</v>
@@ -38567,14 +38550,14 @@
       <c r="I374" t="inlineStr"/>
       <c r="P374" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q374" t="n">
-        <v>443916</v>
+        <v>443650</v>
       </c>
       <c r="R374" t="n">
-        <v>6766734</v>
+        <v>6767097</v>
       </c>
       <c r="S374" t="n">
         <v>10</v>
@@ -38604,47 +38587,36 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z374" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
       <c r="AA374" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB374" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
       <c r="AD374" t="b">
         <v>0</v>
       </c>
       <c r="AE374" t="b">
         <v>0</v>
       </c>
-      <c r="AF374" t="inlineStr"/>
       <c r="AG374" t="b">
         <v>0</v>
       </c>
       <c r="AT374" t="inlineStr"/>
       <c r="AW374" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX374" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>127729133</v>
+        <v>127729108</v>
       </c>
       <c r="B375" t="n">
         <v>79029</v>
@@ -38679,10 +38651,10 @@
         </is>
       </c>
       <c r="Q375" t="n">
-        <v>443914</v>
+        <v>443852</v>
       </c>
       <c r="R375" t="n">
-        <v>6766575</v>
+        <v>6766872</v>
       </c>
       <c r="S375" t="n">
         <v>10</v>
@@ -38714,7 +38686,7 @@
       </c>
       <c r="Z375" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA375" t="inlineStr">
@@ -38724,7 +38696,7 @@
       </c>
       <c r="AB375" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD375" t="b">
@@ -38752,7 +38724,7 @@
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>127729096</v>
+        <v>127729123</v>
       </c>
       <c r="B376" t="n">
         <v>79029</v>
@@ -38787,10 +38759,10 @@
         </is>
       </c>
       <c r="Q376" t="n">
-        <v>443573</v>
+        <v>443920</v>
       </c>
       <c r="R376" t="n">
-        <v>6767157</v>
+        <v>6766713</v>
       </c>
       <c r="S376" t="n">
         <v>10</v>
@@ -38822,7 +38794,7 @@
       </c>
       <c r="Z376" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA376" t="inlineStr">
@@ -38832,7 +38804,7 @@
       </c>
       <c r="AB376" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD376" t="b">
@@ -38860,7 +38832,7 @@
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>127723278</v>
+        <v>127723292</v>
       </c>
       <c r="B377" t="n">
         <v>79029</v>
@@ -38895,10 +38867,10 @@
         </is>
       </c>
       <c r="Q377" t="n">
-        <v>443289</v>
+        <v>443359</v>
       </c>
       <c r="R377" t="n">
-        <v>6767458</v>
+        <v>6767352</v>
       </c>
       <c r="S377" t="n">
         <v>10</v>
@@ -38957,7 +38929,7 @@
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>127729079</v>
+        <v>127729119</v>
       </c>
       <c r="B378" t="n">
         <v>79029</v>
@@ -38992,10 +38964,10 @@
         </is>
       </c>
       <c r="Q378" t="n">
-        <v>443633</v>
+        <v>443916</v>
       </c>
       <c r="R378" t="n">
-        <v>6767101</v>
+        <v>6766734</v>
       </c>
       <c r="S378" t="n">
         <v>10</v>
@@ -39027,7 +38999,7 @@
       </c>
       <c r="Z378" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA378" t="inlineStr">
@@ -39037,7 +39009,7 @@
       </c>
       <c r="AB378" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD378" t="b">
@@ -39065,7 +39037,7 @@
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>127723396</v>
+        <v>127729133</v>
       </c>
       <c r="B379" t="n">
         <v>79029</v>
@@ -39096,14 +39068,14 @@
       <c r="I379" t="inlineStr"/>
       <c r="P379" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q379" t="n">
-        <v>443649</v>
+        <v>443914</v>
       </c>
       <c r="R379" t="n">
-        <v>6767152</v>
+        <v>6766575</v>
       </c>
       <c r="S379" t="n">
         <v>10</v>
@@ -39133,36 +39105,47 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z379" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
       <c r="AA379" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB379" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
       <c r="AD379" t="b">
         <v>0</v>
       </c>
       <c r="AE379" t="b">
         <v>0</v>
       </c>
+      <c r="AF379" t="inlineStr"/>
       <c r="AG379" t="b">
         <v>0</v>
       </c>
       <c r="AT379" t="inlineStr"/>
       <c r="AW379" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX379" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>127723251</v>
+        <v>127729096</v>
       </c>
       <c r="B380" t="n">
         <v>79029</v>
@@ -39193,14 +39176,14 @@
       <c r="I380" t="inlineStr"/>
       <c r="P380" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q380" t="n">
-        <v>443282</v>
+        <v>443573</v>
       </c>
       <c r="R380" t="n">
-        <v>6767291</v>
+        <v>6767157</v>
       </c>
       <c r="S380" t="n">
         <v>10</v>
@@ -39230,39 +39213,50 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z380" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
       <c r="AA380" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB380" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
       <c r="AD380" t="b">
         <v>0</v>
       </c>
       <c r="AE380" t="b">
         <v>0</v>
       </c>
+      <c r="AF380" t="inlineStr"/>
       <c r="AG380" t="b">
         <v>0</v>
       </c>
       <c r="AT380" t="inlineStr"/>
       <c r="AW380" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX380" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>127730376</v>
+        <v>127723278</v>
       </c>
       <c r="B381" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -39270,37 +39264,34 @@
         </is>
       </c>
       <c r="E381" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I381" t="inlineStr"/>
-      <c r="J381" t="inlineStr"/>
-      <c r="K381" t="inlineStr"/>
-      <c r="N381" t="inlineStr"/>
       <c r="P381" t="inlineStr">
         <is>
-          <t>Oxeråsen S om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q381" t="n">
-        <v>443332</v>
+        <v>443289</v>
       </c>
       <c r="R381" t="n">
-        <v>6767103</v>
+        <v>6767458</v>
       </c>
       <c r="S381" t="n">
         <v>10</v>
@@ -39341,29 +39332,28 @@
       <c r="AE381" t="b">
         <v>0</v>
       </c>
-      <c r="AF381" t="inlineStr"/>
       <c r="AG381" t="b">
         <v>0</v>
       </c>
       <c r="AT381" t="inlineStr"/>
       <c r="AW381" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX381" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>127722817</v>
+        <v>127729079</v>
       </c>
       <c r="B382" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -39371,34 +39361,34 @@
         </is>
       </c>
       <c r="E382" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I382" t="inlineStr"/>
       <c r="P382" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q382" t="n">
-        <v>443590</v>
+        <v>443633</v>
       </c>
       <c r="R382" t="n">
-        <v>6767070</v>
+        <v>6767101</v>
       </c>
       <c r="S382" t="n">
         <v>10</v>
@@ -39428,39 +39418,50 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z382" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
       <c r="AA382" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB382" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
       <c r="AD382" t="b">
         <v>0</v>
       </c>
       <c r="AE382" t="b">
         <v>0</v>
       </c>
+      <c r="AF382" t="inlineStr"/>
       <c r="AG382" t="b">
         <v>0</v>
       </c>
       <c r="AT382" t="inlineStr"/>
       <c r="AW382" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX382" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>127722823</v>
+        <v>127723396</v>
       </c>
       <c r="B383" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -39468,21 +39469,21 @@
         </is>
       </c>
       <c r="E383" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I383" t="inlineStr"/>
@@ -39492,10 +39493,10 @@
         </is>
       </c>
       <c r="Q383" t="n">
-        <v>443781</v>
+        <v>443649</v>
       </c>
       <c r="R383" t="n">
-        <v>6767103</v>
+        <v>6767152</v>
       </c>
       <c r="S383" t="n">
         <v>10</v>
@@ -39554,7 +39555,7 @@
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>127723239</v>
+        <v>127723251</v>
       </c>
       <c r="B384" t="n">
         <v>79029</v>
@@ -39589,10 +39590,10 @@
         </is>
       </c>
       <c r="Q384" t="n">
-        <v>443281</v>
+        <v>443282</v>
       </c>
       <c r="R384" t="n">
-        <v>6767174</v>
+        <v>6767291</v>
       </c>
       <c r="S384" t="n">
         <v>10</v>
@@ -39651,10 +39652,10 @@
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>127722837</v>
+        <v>127730376</v>
       </c>
       <c r="B385" t="n">
-        <v>75153</v>
+        <v>79647</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -39662,34 +39663,37 @@
         </is>
       </c>
       <c r="E385" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I385" t="inlineStr"/>
+      <c r="J385" t="inlineStr"/>
+      <c r="K385" t="inlineStr"/>
+      <c r="N385" t="inlineStr"/>
       <c r="P385" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S om, Dlr</t>
         </is>
       </c>
       <c r="Q385" t="n">
-        <v>443811</v>
+        <v>443332</v>
       </c>
       <c r="R385" t="n">
-        <v>6767031</v>
+        <v>6767103</v>
       </c>
       <c r="S385" t="n">
         <v>10</v>
@@ -39724,39 +39728,35 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC385" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD385" t="b">
         <v>0</v>
       </c>
       <c r="AE385" t="b">
         <v>0</v>
       </c>
+      <c r="AF385" t="inlineStr"/>
       <c r="AG385" t="b">
         <v>0</v>
       </c>
       <c r="AT385" t="inlineStr"/>
       <c r="AW385" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX385" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>127723311</v>
+        <v>127722817</v>
       </c>
       <c r="B386" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -39764,21 +39764,21 @@
         </is>
       </c>
       <c r="E386" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I386" t="inlineStr"/>
@@ -39788,10 +39788,10 @@
         </is>
       </c>
       <c r="Q386" t="n">
-        <v>443555</v>
+        <v>443590</v>
       </c>
       <c r="R386" t="n">
-        <v>6767164</v>
+        <v>6767070</v>
       </c>
       <c r="S386" t="n">
         <v>10</v>
@@ -39850,10 +39850,10 @@
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>127723245</v>
+        <v>127722823</v>
       </c>
       <c r="B387" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -39861,21 +39861,21 @@
         </is>
       </c>
       <c r="E387" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I387" t="inlineStr"/>
@@ -39885,10 +39885,10 @@
         </is>
       </c>
       <c r="Q387" t="n">
-        <v>443267</v>
+        <v>443781</v>
       </c>
       <c r="R387" t="n">
-        <v>6767237</v>
+        <v>6767103</v>
       </c>
       <c r="S387" t="n">
         <v>10</v>
@@ -39947,7 +39947,7 @@
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>127723087</v>
+        <v>127723346</v>
       </c>
       <c r="B388" t="n">
         <v>79029</v>
@@ -39982,10 +39982,10 @@
         </is>
       </c>
       <c r="Q388" t="n">
-        <v>443713</v>
+        <v>443773</v>
       </c>
       <c r="R388" t="n">
-        <v>6766723</v>
+        <v>6766946</v>
       </c>
       <c r="S388" t="n">
         <v>10</v>
@@ -40044,10 +40044,10 @@
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>127723353</v>
+        <v>127722905</v>
       </c>
       <c r="B389" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -40055,21 +40055,21 @@
         </is>
       </c>
       <c r="E389" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I389" t="inlineStr"/>
@@ -40079,10 +40079,10 @@
         </is>
       </c>
       <c r="Q389" t="n">
-        <v>443860</v>
+        <v>443743</v>
       </c>
       <c r="R389" t="n">
-        <v>6766958</v>
+        <v>6767161</v>
       </c>
       <c r="S389" t="n">
         <v>10</v>
@@ -40115,6 +40115,11 @@
       <c r="AA389" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC389" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD389" t="b">
@@ -40141,45 +40146,50 @@
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>127723379</v>
+        <v>127722967</v>
       </c>
       <c r="B390" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E390" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I390" t="inlineStr"/>
+      <c r="M390" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P390" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q390" t="n">
-        <v>443820</v>
+        <v>443274</v>
       </c>
       <c r="R390" t="n">
-        <v>6767075</v>
+        <v>6767205</v>
       </c>
       <c r="S390" t="n">
         <v>10</v>
@@ -40238,45 +40248,54 @@
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>127729132</v>
+        <v>127729089</v>
       </c>
       <c r="B391" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E391" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I391" t="inlineStr"/>
+      <c r="J391" t="inlineStr"/>
+      <c r="K391" t="inlineStr"/>
+      <c r="L391" t="inlineStr"/>
+      <c r="M391" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N391" t="inlineStr"/>
       <c r="P391" t="inlineStr">
         <is>
           <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q391" t="n">
-        <v>443918</v>
+        <v>443908</v>
       </c>
       <c r="R391" t="n">
-        <v>6766588</v>
+        <v>6766751</v>
       </c>
       <c r="S391" t="n">
         <v>10</v>
@@ -40308,7 +40327,7 @@
       </c>
       <c r="Z391" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA391" t="inlineStr">
@@ -40318,7 +40337,7 @@
       </c>
       <c r="AB391" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD391" t="b">
@@ -40346,10 +40365,10 @@
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>127723082</v>
+        <v>127729144</v>
       </c>
       <c r="B392" t="n">
-        <v>79029</v>
+        <v>92636</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -40357,34 +40376,45 @@
         </is>
       </c>
       <c r="E392" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I392" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K392" t="inlineStr"/>
+      <c r="N392" t="inlineStr"/>
       <c r="P392" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q392" t="n">
-        <v>443674</v>
+        <v>443900</v>
       </c>
       <c r="R392" t="n">
-        <v>6766780</v>
+        <v>6766718</v>
       </c>
       <c r="S392" t="n">
         <v>10</v>
@@ -40414,36 +40444,47 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z392" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
       <c r="AA392" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB392" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
       <c r="AD392" t="b">
         <v>0</v>
       </c>
       <c r="AE392" t="b">
         <v>0</v>
       </c>
+      <c r="AF392" t="inlineStr"/>
       <c r="AG392" t="b">
         <v>0</v>
       </c>
       <c r="AT392" t="inlineStr"/>
       <c r="AW392" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX392" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>127723285</v>
+        <v>127723379</v>
       </c>
       <c r="B393" t="n">
         <v>79029</v>
@@ -40478,10 +40519,10 @@
         </is>
       </c>
       <c r="Q393" t="n">
-        <v>443311</v>
+        <v>443820</v>
       </c>
       <c r="R393" t="n">
-        <v>6767434</v>
+        <v>6767075</v>
       </c>
       <c r="S393" t="n">
         <v>10</v>
@@ -40540,7 +40581,7 @@
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>127723341</v>
+        <v>127723218</v>
       </c>
       <c r="B394" t="n">
         <v>79029</v>
@@ -40575,10 +40616,10 @@
         </is>
       </c>
       <c r="Q394" t="n">
-        <v>443695</v>
+        <v>443425</v>
       </c>
       <c r="R394" t="n">
-        <v>6766960</v>
+        <v>6767031</v>
       </c>
       <c r="S394" t="n">
         <v>10</v>
@@ -40637,7 +40678,7 @@
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>127723332</v>
+        <v>127729132</v>
       </c>
       <c r="B395" t="n">
         <v>79029</v>
@@ -40668,14 +40709,14 @@
       <c r="I395" t="inlineStr"/>
       <c r="P395" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q395" t="n">
-        <v>443690</v>
+        <v>443918</v>
       </c>
       <c r="R395" t="n">
-        <v>6767067</v>
+        <v>6766588</v>
       </c>
       <c r="S395" t="n">
         <v>10</v>
@@ -40705,36 +40746,47 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z395" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
       <c r="AA395" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB395" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
       <c r="AD395" t="b">
         <v>0</v>
       </c>
       <c r="AE395" t="b">
         <v>0</v>
       </c>
+      <c r="AF395" t="inlineStr"/>
       <c r="AG395" t="b">
         <v>0</v>
       </c>
       <c r="AT395" t="inlineStr"/>
       <c r="AW395" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX395" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>127729107</v>
+        <v>127723082</v>
       </c>
       <c r="B396" t="n">
         <v>79029</v>
@@ -40765,14 +40817,14 @@
       <c r="I396" t="inlineStr"/>
       <c r="P396" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q396" t="n">
-        <v>443847</v>
+        <v>443674</v>
       </c>
       <c r="R396" t="n">
-        <v>6766880</v>
+        <v>6766780</v>
       </c>
       <c r="S396" t="n">
         <v>10</v>
@@ -40802,47 +40854,36 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z396" t="inlineStr">
-        <is>
-          <t>16:42</t>
-        </is>
-      </c>
       <c r="AA396" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB396" t="inlineStr">
-        <is>
-          <t>16:42</t>
-        </is>
-      </c>
       <c r="AD396" t="b">
         <v>0</v>
       </c>
       <c r="AE396" t="b">
         <v>0</v>
       </c>
-      <c r="AF396" t="inlineStr"/>
       <c r="AG396" t="b">
         <v>0</v>
       </c>
       <c r="AT396" t="inlineStr"/>
       <c r="AW396" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX396" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>127723283</v>
+        <v>127723285</v>
       </c>
       <c r="B397" t="n">
         <v>79029</v>
@@ -40877,10 +40918,10 @@
         </is>
       </c>
       <c r="Q397" t="n">
-        <v>443290</v>
+        <v>443311</v>
       </c>
       <c r="R397" t="n">
-        <v>6767430</v>
+        <v>6767434</v>
       </c>
       <c r="S397" t="n">
         <v>10</v>
@@ -40939,10 +40980,10 @@
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>127722818</v>
+        <v>127723341</v>
       </c>
       <c r="B398" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -40950,21 +40991,21 @@
         </is>
       </c>
       <c r="E398" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I398" t="inlineStr"/>
@@ -40974,10 +41015,10 @@
         </is>
       </c>
       <c r="Q398" t="n">
-        <v>443606</v>
+        <v>443695</v>
       </c>
       <c r="R398" t="n">
-        <v>6767114</v>
+        <v>6766960</v>
       </c>
       <c r="S398" t="n">
         <v>10</v>
@@ -41036,10 +41077,10 @@
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>127729144</v>
+        <v>127723332</v>
       </c>
       <c r="B399" t="n">
-        <v>92636</v>
+        <v>79029</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -41047,45 +41088,34 @@
         </is>
       </c>
       <c r="E399" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I399" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J399" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K399" t="inlineStr"/>
-      <c r="N399" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr"/>
       <c r="P399" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q399" t="n">
-        <v>443900</v>
+        <v>443690</v>
       </c>
       <c r="R399" t="n">
-        <v>6766718</v>
+        <v>6767067</v>
       </c>
       <c r="S399" t="n">
         <v>10</v>
@@ -41115,47 +41145,36 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z399" t="inlineStr">
-        <is>
-          <t>16:17</t>
-        </is>
-      </c>
       <c r="AA399" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB399" t="inlineStr">
-        <is>
-          <t>16:17</t>
-        </is>
-      </c>
       <c r="AD399" t="b">
         <v>0</v>
       </c>
       <c r="AE399" t="b">
         <v>0</v>
       </c>
-      <c r="AF399" t="inlineStr"/>
       <c r="AG399" t="b">
         <v>0</v>
       </c>
       <c r="AT399" t="inlineStr"/>
       <c r="AW399" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX399" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>127723218</v>
+        <v>127729107</v>
       </c>
       <c r="B400" t="n">
         <v>79029</v>
@@ -41186,14 +41205,14 @@
       <c r="I400" t="inlineStr"/>
       <c r="P400" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q400" t="n">
-        <v>443425</v>
+        <v>443847</v>
       </c>
       <c r="R400" t="n">
-        <v>6767031</v>
+        <v>6766880</v>
       </c>
       <c r="S400" t="n">
         <v>10</v>
@@ -41223,39 +41242,50 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z400" t="inlineStr">
+        <is>
+          <t>16:42</t>
+        </is>
+      </c>
       <c r="AA400" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB400" t="inlineStr">
+        <is>
+          <t>16:42</t>
+        </is>
+      </c>
       <c r="AD400" t="b">
         <v>0</v>
       </c>
       <c r="AE400" t="b">
         <v>0</v>
       </c>
+      <c r="AF400" t="inlineStr"/>
       <c r="AG400" t="b">
         <v>0</v>
       </c>
       <c r="AT400" t="inlineStr"/>
       <c r="AW400" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX400" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>127723346</v>
+        <v>127722818</v>
       </c>
       <c r="B401" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -41263,21 +41293,21 @@
         </is>
       </c>
       <c r="E401" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I401" t="inlineStr"/>
@@ -41287,10 +41317,10 @@
         </is>
       </c>
       <c r="Q401" t="n">
-        <v>443773</v>
+        <v>443606</v>
       </c>
       <c r="R401" t="n">
-        <v>6766946</v>
+        <v>6767114</v>
       </c>
       <c r="S401" t="n">
         <v>10</v>
@@ -41349,10 +41379,10 @@
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>127722905</v>
+        <v>127723087</v>
       </c>
       <c r="B402" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -41360,21 +41390,21 @@
         </is>
       </c>
       <c r="E402" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I402" t="inlineStr"/>
@@ -41384,10 +41414,10 @@
         </is>
       </c>
       <c r="Q402" t="n">
-        <v>443743</v>
+        <v>443713</v>
       </c>
       <c r="R402" t="n">
-        <v>6767161</v>
+        <v>6766723</v>
       </c>
       <c r="S402" t="n">
         <v>10</v>
@@ -41420,11 +41450,6 @@
       <c r="AA402" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC402" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD402" t="b">
@@ -41451,50 +41476,45 @@
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>127722967</v>
+        <v>127723353</v>
       </c>
       <c r="B403" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E403" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I403" t="inlineStr"/>
-      <c r="M403" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P403" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q403" t="n">
-        <v>443274</v>
+        <v>443860</v>
       </c>
       <c r="R403" t="n">
-        <v>6767205</v>
+        <v>6766958</v>
       </c>
       <c r="S403" t="n">
         <v>10</v>
@@ -41553,54 +41573,45 @@
     </row>
     <row r="404">
       <c r="A404" t="n">
-        <v>127729089</v>
+        <v>127723283</v>
       </c>
       <c r="B404" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E404" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I404" t="inlineStr"/>
-      <c r="J404" t="inlineStr"/>
-      <c r="K404" t="inlineStr"/>
-      <c r="L404" t="inlineStr"/>
-      <c r="M404" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N404" t="inlineStr"/>
       <c r="P404" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q404" t="n">
-        <v>443908</v>
+        <v>443290</v>
       </c>
       <c r="R404" t="n">
-        <v>6766751</v>
+        <v>6767430</v>
       </c>
       <c r="S404" t="n">
         <v>10</v>
@@ -41630,40 +41641,29 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z404" t="inlineStr">
-        <is>
-          <t>16:26</t>
-        </is>
-      </c>
       <c r="AA404" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB404" t="inlineStr">
-        <is>
-          <t>16:26</t>
-        </is>
-      </c>
       <c r="AD404" t="b">
         <v>0</v>
       </c>
       <c r="AE404" t="b">
         <v>0</v>
       </c>
-      <c r="AF404" t="inlineStr"/>
       <c r="AG404" t="b">
         <v>0</v>
       </c>
       <c r="AT404" t="inlineStr"/>
       <c r="AW404" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX404" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY404" t="inlineStr"/>
@@ -41772,7 +41772,7 @@
     </row>
     <row r="406">
       <c r="A406" t="n">
-        <v>127723225</v>
+        <v>127723393</v>
       </c>
       <c r="B406" t="n">
         <v>79029</v>
@@ -41807,10 +41807,10 @@
         </is>
       </c>
       <c r="Q406" t="n">
-        <v>443404</v>
+        <v>443672</v>
       </c>
       <c r="R406" t="n">
-        <v>6767071</v>
+        <v>6767146</v>
       </c>
       <c r="S406" t="n">
         <v>10</v>
@@ -41869,7 +41869,7 @@
     </row>
     <row r="407">
       <c r="A407" t="n">
-        <v>127723273</v>
+        <v>127723225</v>
       </c>
       <c r="B407" t="n">
         <v>79029</v>
@@ -41904,10 +41904,10 @@
         </is>
       </c>
       <c r="Q407" t="n">
-        <v>443264</v>
+        <v>443404</v>
       </c>
       <c r="R407" t="n">
-        <v>6767454</v>
+        <v>6767071</v>
       </c>
       <c r="S407" t="n">
         <v>10</v>
@@ -41966,50 +41966,45 @@
     </row>
     <row r="408">
       <c r="A408" t="n">
-        <v>127722959</v>
+        <v>127723273</v>
       </c>
       <c r="B408" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E408" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I408" t="inlineStr"/>
-      <c r="M408" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P408" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q408" t="n">
-        <v>443559</v>
+        <v>443264</v>
       </c>
       <c r="R408" t="n">
-        <v>6766954</v>
+        <v>6767454</v>
       </c>
       <c r="S408" t="n">
         <v>10</v>
@@ -42068,10 +42063,10 @@
     </row>
     <row r="409">
       <c r="A409" t="n">
-        <v>127723393</v>
+        <v>127729090</v>
       </c>
       <c r="B409" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -42079,34 +42074,34 @@
         </is>
       </c>
       <c r="E409" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I409" t="inlineStr"/>
       <c r="P409" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q409" t="n">
-        <v>443672</v>
+        <v>443550</v>
       </c>
       <c r="R409" t="n">
-        <v>6767146</v>
+        <v>6767191</v>
       </c>
       <c r="S409" t="n">
         <v>10</v>
@@ -42136,39 +42131,50 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z409" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
       <c r="AA409" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB409" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
       <c r="AD409" t="b">
         <v>0</v>
       </c>
       <c r="AE409" t="b">
         <v>0</v>
       </c>
+      <c r="AF409" t="inlineStr"/>
       <c r="AG409" t="b">
         <v>0</v>
       </c>
       <c r="AT409" t="inlineStr"/>
       <c r="AW409" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX409" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY409" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" t="n">
-        <v>127729090</v>
+        <v>127723377</v>
       </c>
       <c r="B410" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -42176,34 +42182,34 @@
         </is>
       </c>
       <c r="E410" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I410" t="inlineStr"/>
       <c r="P410" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q410" t="n">
-        <v>443550</v>
+        <v>443794</v>
       </c>
       <c r="R410" t="n">
-        <v>6767191</v>
+        <v>6767054</v>
       </c>
       <c r="S410" t="n">
         <v>10</v>
@@ -42233,47 +42239,36 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z410" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
       <c r="AA410" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB410" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
       <c r="AD410" t="b">
         <v>0</v>
       </c>
       <c r="AE410" t="b">
         <v>0</v>
       </c>
-      <c r="AF410" t="inlineStr"/>
       <c r="AG410" t="b">
         <v>0</v>
       </c>
       <c r="AT410" t="inlineStr"/>
       <c r="AW410" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX410" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" t="n">
-        <v>127723377</v>
+        <v>127723331</v>
       </c>
       <c r="B411" t="n">
         <v>79029</v>
@@ -42308,10 +42303,10 @@
         </is>
       </c>
       <c r="Q411" t="n">
-        <v>443794</v>
+        <v>443670</v>
       </c>
       <c r="R411" t="n">
-        <v>6767054</v>
+        <v>6767066</v>
       </c>
       <c r="S411" t="n">
         <v>10</v>
@@ -42370,45 +42365,50 @@
     </row>
     <row r="412">
       <c r="A412" t="n">
-        <v>127723331</v>
+        <v>127723010</v>
       </c>
       <c r="B412" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E412" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I412" t="inlineStr"/>
+      <c r="M412" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P412" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q412" t="n">
-        <v>443670</v>
+        <v>443591</v>
       </c>
       <c r="R412" t="n">
-        <v>6767066</v>
+        <v>6767183</v>
       </c>
       <c r="S412" t="n">
         <v>10</v>
@@ -42467,7 +42467,7 @@
     </row>
     <row r="413">
       <c r="A413" t="n">
-        <v>127723010</v>
+        <v>127722959</v>
       </c>
       <c r="B413" t="n">
         <v>8450</v>
@@ -42507,10 +42507,10 @@
         </is>
       </c>
       <c r="Q413" t="n">
-        <v>443591</v>
+        <v>443559</v>
       </c>
       <c r="R413" t="n">
-        <v>6767183</v>
+        <v>6766954</v>
       </c>
       <c r="S413" t="n">
         <v>10</v>
@@ -51029,37 +51029,39 @@
     </row>
     <row r="497">
       <c r="A497" t="n">
-        <v>127795217</v>
+        <v>127795366</v>
       </c>
       <c r="B497" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E497" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I497" t="inlineStr"/>
       <c r="J497" t="inlineStr"/>
       <c r="K497" t="inlineStr"/>
+      <c r="L497" t="inlineStr"/>
+      <c r="M497" t="inlineStr"/>
       <c r="N497" t="inlineStr"/>
       <c r="P497" t="inlineStr">
         <is>
@@ -51067,10 +51069,10 @@
         </is>
       </c>
       <c r="Q497" t="n">
-        <v>443305</v>
+        <v>443860</v>
       </c>
       <c r="R497" t="n">
-        <v>6766979</v>
+        <v>6766585</v>
       </c>
       <c r="S497" t="n">
         <v>50</v>
@@ -51130,39 +51132,37 @@
     </row>
     <row r="498">
       <c r="A498" t="n">
-        <v>127795366</v>
+        <v>127795217</v>
       </c>
       <c r="B498" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E498" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I498" t="inlineStr"/>
       <c r="J498" t="inlineStr"/>
       <c r="K498" t="inlineStr"/>
-      <c r="L498" t="inlineStr"/>
-      <c r="M498" t="inlineStr"/>
       <c r="N498" t="inlineStr"/>
       <c r="P498" t="inlineStr">
         <is>
@@ -51170,10 +51170,10 @@
         </is>
       </c>
       <c r="Q498" t="n">
-        <v>443860</v>
+        <v>443305</v>
       </c>
       <c r="R498" t="n">
-        <v>6766585</v>
+        <v>6766979</v>
       </c>
       <c r="S498" t="n">
         <v>50</v>

--- a/artfynd/A 35482-2025 artfynd.xlsx
+++ b/artfynd/A 35482-2025 artfynd.xlsx
@@ -4433,37 +4433,43 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127618637</v>
+        <v>127608027</v>
       </c>
       <c r="B36" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4471,10 +4477,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>443286</v>
+        <v>443898</v>
       </c>
       <c r="R36" t="n">
-        <v>6767436</v>
+        <v>6766974</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4534,7 +4540,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127608027</v>
+        <v>127618701</v>
       </c>
       <c r="B37" t="n">
         <v>8450</v>
@@ -4578,10 +4584,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>443898</v>
+        <v>443327</v>
       </c>
       <c r="R37" t="n">
-        <v>6766974</v>
+        <v>6767322</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4614,6 +4620,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>1 låga och 3 torraka</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4641,43 +4652,37 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127618701</v>
+        <v>127618637</v>
       </c>
       <c r="B38" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4685,10 +4690,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>443327</v>
+        <v>443286</v>
       </c>
       <c r="R38" t="n">
-        <v>6767322</v>
+        <v>6767436</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4721,11 +4726,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>1 låga och 3 torraka</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5273,37 +5273,43 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127608039</v>
+        <v>127619167</v>
       </c>
       <c r="B44" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5311,10 +5317,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>443868</v>
+        <v>443339</v>
       </c>
       <c r="R44" t="n">
-        <v>6766980</v>
+        <v>6767141</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5351,7 +5357,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På 3 tallstammar</t>
+          <t>På raka</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5379,43 +5385,37 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127619167</v>
+        <v>127608039</v>
       </c>
       <c r="B45" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5423,10 +5423,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>443339</v>
+        <v>443868</v>
       </c>
       <c r="R45" t="n">
-        <v>6767141</v>
+        <v>6766980</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5463,7 +5463,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På raka</t>
+          <t>På 3 tallstammar</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -7984,43 +7984,37 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127608037</v>
+        <v>127608339</v>
       </c>
       <c r="B70" t="n">
-        <v>8450</v>
+        <v>91372</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8028,10 +8022,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>443868</v>
+        <v>443750</v>
       </c>
       <c r="R70" t="n">
-        <v>6766980</v>
+        <v>6767090</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8196,37 +8190,43 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127608339</v>
+        <v>127608037</v>
       </c>
       <c r="B72" t="n">
-        <v>91372</v>
+        <v>8450</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -8234,10 +8234,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>443750</v>
+        <v>443868</v>
       </c>
       <c r="R72" t="n">
-        <v>6767090</v>
+        <v>6766980</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8297,37 +8297,43 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127606796</v>
+        <v>127619038</v>
       </c>
       <c r="B73" t="n">
-        <v>79029</v>
+        <v>4773</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -8335,10 +8341,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>443860</v>
+        <v>443270</v>
       </c>
       <c r="R73" t="n">
-        <v>6766854</v>
+        <v>6767248</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8398,7 +8404,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127606827</v>
+        <v>127606796</v>
       </c>
       <c r="B74" t="n">
         <v>79029</v>
@@ -8436,10 +8442,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>443866</v>
+        <v>443860</v>
       </c>
       <c r="R74" t="n">
-        <v>6766858</v>
+        <v>6766854</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8472,11 +8478,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8504,10 +8505,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127619016</v>
+        <v>127606827</v>
       </c>
       <c r="B75" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8515,21 +8516,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8542,10 +8543,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>443270</v>
+        <v>443866</v>
       </c>
       <c r="R75" t="n">
-        <v>6767260</v>
+        <v>6766858</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8578,6 +8579,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8605,10 +8611,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127621131</v>
+        <v>127619016</v>
       </c>
       <c r="B76" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8616,21 +8622,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8643,10 +8649,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>443495</v>
+        <v>443270</v>
       </c>
       <c r="R76" t="n">
-        <v>6766975</v>
+        <v>6767260</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8679,11 +8685,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>På tall och gran rikligt</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8711,43 +8712,37 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127619038</v>
+        <v>127621131</v>
       </c>
       <c r="B77" t="n">
-        <v>4773</v>
+        <v>79029</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100299</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -8755,10 +8750,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>443270</v>
+        <v>443495</v>
       </c>
       <c r="R77" t="n">
-        <v>6767248</v>
+        <v>6766975</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8791,6 +8786,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>På tall och gran rikligt</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9131,7 +9131,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127619183</v>
+        <v>127618615</v>
       </c>
       <c r="B81" t="n">
         <v>8450</v>
@@ -9175,10 +9175,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>443347</v>
+        <v>443293</v>
       </c>
       <c r="R81" t="n">
-        <v>6767103</v>
+        <v>6767447</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9211,11 +9211,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>På låga</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9243,7 +9238,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127618615</v>
+        <v>127619158</v>
       </c>
       <c r="B82" t="n">
         <v>8450</v>
@@ -9287,10 +9282,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>443293</v>
+        <v>443344</v>
       </c>
       <c r="R82" t="n">
-        <v>6767447</v>
+        <v>6767154</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9323,6 +9318,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>På raka</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9350,7 +9350,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127619158</v>
+        <v>127619183</v>
       </c>
       <c r="B83" t="n">
         <v>8450</v>
@@ -9394,10 +9394,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>443344</v>
+        <v>443347</v>
       </c>
       <c r="R83" t="n">
-        <v>6767154</v>
+        <v>6767103</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9434,7 +9434,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>På raka</t>
+          <t>På låga</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -15522,10 +15522,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127723582</v>
+        <v>127723317</v>
       </c>
       <c r="B144" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15533,21 +15533,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15557,10 +15557,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>443606</v>
+        <v>443589</v>
       </c>
       <c r="R144" t="n">
-        <v>6767114</v>
+        <v>6767070</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15619,10 +15619,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>127723579</v>
+        <v>127723326</v>
       </c>
       <c r="B145" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15630,21 +15630,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15654,10 +15654,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>443583</v>
+        <v>443655</v>
       </c>
       <c r="R145" t="n">
-        <v>6767093</v>
+        <v>6767102</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15716,45 +15716,45 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>127729075</v>
+        <v>127723207</v>
       </c>
       <c r="B146" t="n">
-        <v>92654</v>
+        <v>79029</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>443903</v>
+        <v>443526</v>
       </c>
       <c r="R146" t="n">
-        <v>6766793</v>
+        <v>6766954</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15784,47 +15784,36 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z146" t="inlineStr">
-        <is>
-          <t>16:29</t>
-        </is>
-      </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB146" t="inlineStr">
-        <is>
-          <t>16:29</t>
-        </is>
-      </c>
       <c r="AD146" t="b">
         <v>0</v>
       </c>
       <c r="AE146" t="b">
         <v>0</v>
       </c>
-      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
       </c>
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>127729129</v>
+        <v>127723263</v>
       </c>
       <c r="B147" t="n">
         <v>79029</v>
@@ -15855,14 +15844,14 @@
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>443947</v>
+        <v>443279</v>
       </c>
       <c r="R147" t="n">
-        <v>6766584</v>
+        <v>6767392</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15892,47 +15881,36 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z147" t="inlineStr">
-        <is>
-          <t>15:17</t>
-        </is>
-      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB147" t="inlineStr">
-        <is>
-          <t>15:17</t>
-        </is>
-      </c>
       <c r="AD147" t="b">
         <v>0</v>
       </c>
       <c r="AE147" t="b">
         <v>0</v>
       </c>
-      <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
       </c>
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>127723248</v>
+        <v>127723234</v>
       </c>
       <c r="B148" t="n">
         <v>79029</v>
@@ -15967,10 +15945,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>443275</v>
+        <v>443321</v>
       </c>
       <c r="R148" t="n">
-        <v>6767256</v>
+        <v>6767103</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16029,10 +16007,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>127723236</v>
+        <v>127723582</v>
       </c>
       <c r="B149" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16040,21 +16018,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16064,10 +16042,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>443310</v>
+        <v>443606</v>
       </c>
       <c r="R149" t="n">
-        <v>6767138</v>
+        <v>6767114</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16126,10 +16104,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>127729106</v>
+        <v>127723579</v>
       </c>
       <c r="B150" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16137,34 +16115,34 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>443777</v>
+        <v>443583</v>
       </c>
       <c r="R150" t="n">
-        <v>6766919</v>
+        <v>6767093</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16194,85 +16172,74 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z150" t="inlineStr">
-        <is>
-          <t>16:47</t>
-        </is>
-      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB150" t="inlineStr">
-        <is>
-          <t>16:47</t>
-        </is>
-      </c>
       <c r="AD150" t="b">
         <v>0</v>
       </c>
       <c r="AE150" t="b">
         <v>0</v>
       </c>
-      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>127723213</v>
+        <v>127729075</v>
       </c>
       <c r="B151" t="n">
-        <v>79029</v>
+        <v>92654</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>443470</v>
+        <v>443903</v>
       </c>
       <c r="R151" t="n">
-        <v>6766976</v>
+        <v>6766793</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16302,36 +16269,47 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
       <c r="AD151" t="b">
         <v>0</v>
       </c>
       <c r="AE151" t="b">
         <v>0</v>
       </c>
+      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>127723199</v>
+        <v>127729129</v>
       </c>
       <c r="B152" t="n">
         <v>79029</v>
@@ -16362,14 +16340,14 @@
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>443540</v>
+        <v>443947</v>
       </c>
       <c r="R152" t="n">
-        <v>6766894</v>
+        <v>6766584</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16399,36 +16377,47 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
       <c r="AD152" t="b">
         <v>0</v>
       </c>
       <c r="AE152" t="b">
         <v>0</v>
       </c>
+      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>127723370</v>
+        <v>127723248</v>
       </c>
       <c r="B153" t="n">
         <v>79029</v>
@@ -16463,10 +16452,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>443826</v>
+        <v>443275</v>
       </c>
       <c r="R153" t="n">
-        <v>6767008</v>
+        <v>6767256</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16525,7 +16514,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>127730382</v>
+        <v>127723357</v>
       </c>
       <c r="B154" t="n">
         <v>79029</v>
@@ -16554,19 +16543,16 @@
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
-      <c r="J154" t="inlineStr"/>
-      <c r="K154" t="inlineStr"/>
-      <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Oxeråsen S om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>443332</v>
+        <v>443931</v>
       </c>
       <c r="R154" t="n">
-        <v>6767071</v>
+        <v>6766931</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16601,37 +16587,31 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>På 10 tallstammar</t>
-        </is>
-      </c>
       <c r="AD154" t="b">
         <v>0</v>
       </c>
       <c r="AE154" t="b">
         <v>0</v>
       </c>
-      <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
         <v>0</v>
       </c>
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>127723317</v>
+        <v>127723236</v>
       </c>
       <c r="B155" t="n">
         <v>79029</v>
@@ -16666,10 +16646,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>443589</v>
+        <v>443310</v>
       </c>
       <c r="R155" t="n">
-        <v>6767070</v>
+        <v>6767138</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16728,7 +16708,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>127723326</v>
+        <v>127729106</v>
       </c>
       <c r="B156" t="n">
         <v>79029</v>
@@ -16759,14 +16739,14 @@
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>443655</v>
+        <v>443777</v>
       </c>
       <c r="R156" t="n">
-        <v>6767102</v>
+        <v>6766919</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16796,36 +16776,47 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
       <c r="AD156" t="b">
         <v>0</v>
       </c>
       <c r="AE156" t="b">
         <v>0</v>
       </c>
+      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>127723207</v>
+        <v>127723213</v>
       </c>
       <c r="B157" t="n">
         <v>79029</v>
@@ -16860,10 +16851,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>443526</v>
+        <v>443470</v>
       </c>
       <c r="R157" t="n">
-        <v>6766954</v>
+        <v>6766976</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16922,7 +16913,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>127723263</v>
+        <v>127723199</v>
       </c>
       <c r="B158" t="n">
         <v>79029</v>
@@ -16957,10 +16948,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>443279</v>
+        <v>443540</v>
       </c>
       <c r="R158" t="n">
-        <v>6767392</v>
+        <v>6766894</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17019,7 +17010,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>127723234</v>
+        <v>127723370</v>
       </c>
       <c r="B159" t="n">
         <v>79029</v>
@@ -17054,10 +17045,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>443321</v>
+        <v>443826</v>
       </c>
       <c r="R159" t="n">
-        <v>6767103</v>
+        <v>6767008</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17116,10 +17107,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>127723550</v>
+        <v>127730382</v>
       </c>
       <c r="B160" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17127,39 +17118,37 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S om, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>443283</v>
+        <v>443332</v>
       </c>
       <c r="R160" t="n">
-        <v>6767277</v>
+        <v>6767071</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17194,34 +17183,40 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>På 10 tallstammar</t>
+        </is>
+      </c>
       <c r="AD160" t="b">
         <v>0</v>
       </c>
       <c r="AE160" t="b">
         <v>0</v>
       </c>
+      <c r="AF160" t="inlineStr"/>
       <c r="AG160" t="b">
         <v>0</v>
       </c>
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>127723357</v>
+        <v>127723550</v>
       </c>
       <c r="B161" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17229,34 +17224,39 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P161" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>443931</v>
+        <v>443283</v>
       </c>
       <c r="R161" t="n">
-        <v>6766931</v>
+        <v>6767277</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17315,10 +17315,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>127722803</v>
+        <v>127722995</v>
       </c>
       <c r="B162" t="n">
-        <v>5197</v>
+        <v>8450</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17326,21 +17326,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>105930</v>
+        <v>106545</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17355,10 +17355,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>443270</v>
+        <v>443979</v>
       </c>
       <c r="R162" t="n">
-        <v>6767291</v>
+        <v>6766943</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17417,10 +17417,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>127722995</v>
+        <v>127722803</v>
       </c>
       <c r="B163" t="n">
-        <v>8450</v>
+        <v>5197</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17428,21 +17428,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17457,10 +17457,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>443979</v>
+        <v>443270</v>
       </c>
       <c r="R163" t="n">
-        <v>6766943</v>
+        <v>6767291</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -23058,10 +23058,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>127730406</v>
+        <v>127722857</v>
       </c>
       <c r="B219" t="n">
-        <v>57672</v>
+        <v>79618</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -23069,42 +23069,34 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
-      <c r="K219" t="inlineStr"/>
-      <c r="L219" t="inlineStr"/>
-      <c r="M219" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Oxeråsen S om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>443450</v>
+        <v>443698</v>
       </c>
       <c r="R219" t="n">
-        <v>6766975</v>
+        <v>6767038</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -23139,11 +23131,6 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC219" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD219" t="b">
         <v>0</v>
       </c>
@@ -23156,22 +23143,22 @@
       <c r="AT219" t="inlineStr"/>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>127723574</v>
+        <v>127723384</v>
       </c>
       <c r="B220" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -23179,21 +23166,21 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -23203,10 +23190,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>443316</v>
+        <v>443778</v>
       </c>
       <c r="R220" t="n">
-        <v>6767322</v>
+        <v>6767109</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -23265,10 +23252,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>127723590</v>
+        <v>127723261</v>
       </c>
       <c r="B221" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -23276,21 +23263,21 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -23300,10 +23287,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>443762</v>
+        <v>443289</v>
       </c>
       <c r="R221" t="n">
-        <v>6767123</v>
+        <v>6767380</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -23362,7 +23349,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>127723384</v>
+        <v>127723275</v>
       </c>
       <c r="B222" t="n">
         <v>79029</v>
@@ -23397,10 +23384,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>443778</v>
+        <v>443267</v>
       </c>
       <c r="R222" t="n">
-        <v>6767109</v>
+        <v>6767460</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -23459,7 +23446,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>127723261</v>
+        <v>127723316</v>
       </c>
       <c r="B223" t="n">
         <v>79029</v>
@@ -23494,10 +23481,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>443289</v>
+        <v>443580</v>
       </c>
       <c r="R223" t="n">
-        <v>6767380</v>
+        <v>6767058</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -23556,7 +23543,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>127723275</v>
+        <v>127723281</v>
       </c>
       <c r="B224" t="n">
         <v>79029</v>
@@ -23591,10 +23578,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>443267</v>
+        <v>443279</v>
       </c>
       <c r="R224" t="n">
-        <v>6767460</v>
+        <v>6767429</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -23653,7 +23640,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>127723316</v>
+        <v>127723373</v>
       </c>
       <c r="B225" t="n">
         <v>79029</v>
@@ -23688,10 +23675,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>443580</v>
+        <v>443799</v>
       </c>
       <c r="R225" t="n">
-        <v>6767058</v>
+        <v>6767022</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23750,7 +23737,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>127723281</v>
+        <v>127723350</v>
       </c>
       <c r="B226" t="n">
         <v>79029</v>
@@ -23785,10 +23772,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>443279</v>
+        <v>443834</v>
       </c>
       <c r="R226" t="n">
-        <v>6767429</v>
+        <v>6766955</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -23847,7 +23834,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>127723373</v>
+        <v>127723085</v>
       </c>
       <c r="B227" t="n">
         <v>79029</v>
@@ -23882,10 +23869,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>443799</v>
+        <v>443713</v>
       </c>
       <c r="R227" t="n">
-        <v>6767022</v>
+        <v>6766756</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -23944,7 +23931,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>127723350</v>
+        <v>127723383</v>
       </c>
       <c r="B228" t="n">
         <v>79029</v>
@@ -23979,10 +23966,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>443834</v>
+        <v>443801</v>
       </c>
       <c r="R228" t="n">
-        <v>6766955</v>
+        <v>6767104</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -24041,7 +24028,7 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>127723085</v>
+        <v>127723298</v>
       </c>
       <c r="B229" t="n">
         <v>79029</v>
@@ -24076,10 +24063,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>443713</v>
+        <v>443379</v>
       </c>
       <c r="R229" t="n">
-        <v>6766756</v>
+        <v>6767340</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -24138,10 +24125,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>127723383</v>
+        <v>127730406</v>
       </c>
       <c r="B230" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -24149,34 +24136,42 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
+      <c r="K230" t="inlineStr"/>
+      <c r="L230" t="inlineStr"/>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr"/>
       <c r="P230" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S om, Dlr</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>443801</v>
+        <v>443450</v>
       </c>
       <c r="R230" t="n">
-        <v>6767104</v>
+        <v>6766975</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -24211,6 +24206,11 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AC230" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD230" t="b">
         <v>0</v>
       </c>
@@ -24223,22 +24223,22 @@
       <c r="AT230" t="inlineStr"/>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>127723298</v>
+        <v>127723574</v>
       </c>
       <c r="B231" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -24246,21 +24246,21 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
@@ -24270,10 +24270,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>443379</v>
+        <v>443316</v>
       </c>
       <c r="R231" t="n">
-        <v>6767340</v>
+        <v>6767322</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -24332,10 +24332,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>127722808</v>
+        <v>127723590</v>
       </c>
       <c r="B232" t="n">
-        <v>79647</v>
+        <v>78696</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -24343,21 +24343,21 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -24367,10 +24367,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>443273</v>
+        <v>443762</v>
       </c>
       <c r="R232" t="n">
-        <v>6767233</v>
+        <v>6767123</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -24429,10 +24429,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>127723400</v>
+        <v>127722808</v>
       </c>
       <c r="B233" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -24440,21 +24440,21 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -24464,10 +24464,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>443583</v>
+        <v>443273</v>
       </c>
       <c r="R233" t="n">
-        <v>6767200</v>
+        <v>6767233</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -24526,7 +24526,7 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>127723208</v>
+        <v>127723400</v>
       </c>
       <c r="B234" t="n">
         <v>79029</v>
@@ -24561,10 +24561,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>443534</v>
+        <v>443583</v>
       </c>
       <c r="R234" t="n">
-        <v>6766982</v>
+        <v>6767200</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -24623,7 +24623,7 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>127723391</v>
+        <v>127723208</v>
       </c>
       <c r="B235" t="n">
         <v>79029</v>
@@ -24658,10 +24658,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>443677</v>
+        <v>443534</v>
       </c>
       <c r="R235" t="n">
-        <v>6767163</v>
+        <v>6766982</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -24720,50 +24720,45 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>127722937</v>
+        <v>127723391</v>
       </c>
       <c r="B236" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
-      <c r="M236" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P236" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>443632</v>
+        <v>443677</v>
       </c>
       <c r="R236" t="n">
-        <v>6766845</v>
+        <v>6767163</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -24822,7 +24817,7 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>127722970</v>
+        <v>127722937</v>
       </c>
       <c r="B237" t="n">
         <v>8450</v>
@@ -24862,10 +24857,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>443315</v>
+        <v>443632</v>
       </c>
       <c r="R237" t="n">
-        <v>6767311</v>
+        <v>6766845</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -24924,7 +24919,7 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>127722969</v>
+        <v>127722970</v>
       </c>
       <c r="B238" t="n">
         <v>8450</v>
@@ -24964,10 +24959,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>443285</v>
+        <v>443315</v>
       </c>
       <c r="R238" t="n">
-        <v>6767253</v>
+        <v>6767311</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -25026,45 +25021,50 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>127722857</v>
+        <v>127722969</v>
       </c>
       <c r="B239" t="n">
-        <v>79618</v>
+        <v>8450</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P239" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>443698</v>
+        <v>443285</v>
       </c>
       <c r="R239" t="n">
-        <v>6767038</v>
+        <v>6767253</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -32925,10 +32925,10 @@
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>127723572</v>
+        <v>127723073</v>
       </c>
       <c r="B318" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -32936,21 +32936,21 @@
         </is>
       </c>
       <c r="E318" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I318" t="inlineStr"/>
@@ -32960,10 +32960,10 @@
         </is>
       </c>
       <c r="Q318" t="n">
-        <v>443311</v>
+        <v>443369</v>
       </c>
       <c r="R318" t="n">
-        <v>6767073</v>
+        <v>6767383</v>
       </c>
       <c r="S318" t="n">
         <v>10</v>
@@ -33022,7 +33022,7 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>127723073</v>
+        <v>127723369</v>
       </c>
       <c r="B319" t="n">
         <v>79029</v>
@@ -33057,10 +33057,10 @@
         </is>
       </c>
       <c r="Q319" t="n">
-        <v>443369</v>
+        <v>443850</v>
       </c>
       <c r="R319" t="n">
-        <v>6767383</v>
+        <v>6766997</v>
       </c>
       <c r="S319" t="n">
         <v>10</v>
@@ -33119,7 +33119,7 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>127723369</v>
+        <v>127723380</v>
       </c>
       <c r="B320" t="n">
         <v>79029</v>
@@ -33154,10 +33154,10 @@
         </is>
       </c>
       <c r="Q320" t="n">
-        <v>443850</v>
+        <v>443818</v>
       </c>
       <c r="R320" t="n">
-        <v>6766997</v>
+        <v>6767091</v>
       </c>
       <c r="S320" t="n">
         <v>10</v>
@@ -33216,7 +33216,7 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>127723380</v>
+        <v>127729111</v>
       </c>
       <c r="B321" t="n">
         <v>79029</v>
@@ -33247,14 +33247,14 @@
       <c r="I321" t="inlineStr"/>
       <c r="P321" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q321" t="n">
-        <v>443818</v>
+        <v>443868</v>
       </c>
       <c r="R321" t="n">
-        <v>6767091</v>
+        <v>6766835</v>
       </c>
       <c r="S321" t="n">
         <v>10</v>
@@ -33284,36 +33284,47 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z321" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
       <c r="AA321" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB321" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
       <c r="AD321" t="b">
         <v>0</v>
       </c>
       <c r="AE321" t="b">
         <v>0</v>
       </c>
+      <c r="AF321" t="inlineStr"/>
       <c r="AG321" t="b">
         <v>0</v>
       </c>
       <c r="AT321" t="inlineStr"/>
       <c r="AW321" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX321" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>127729111</v>
+        <v>127723264</v>
       </c>
       <c r="B322" t="n">
         <v>79029</v>
@@ -33344,14 +33355,14 @@
       <c r="I322" t="inlineStr"/>
       <c r="P322" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q322" t="n">
-        <v>443868</v>
+        <v>443266</v>
       </c>
       <c r="R322" t="n">
-        <v>6766835</v>
+        <v>6767409</v>
       </c>
       <c r="S322" t="n">
         <v>10</v>
@@ -33381,47 +33392,36 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z322" t="inlineStr">
-        <is>
-          <t>16:36</t>
-        </is>
-      </c>
       <c r="AA322" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB322" t="inlineStr">
-        <is>
-          <t>16:36</t>
-        </is>
-      </c>
       <c r="AD322" t="b">
         <v>0</v>
       </c>
       <c r="AE322" t="b">
         <v>0</v>
       </c>
-      <c r="AF322" t="inlineStr"/>
       <c r="AG322" t="b">
         <v>0</v>
       </c>
       <c r="AT322" t="inlineStr"/>
       <c r="AW322" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX322" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>127723264</v>
+        <v>127723076</v>
       </c>
       <c r="B323" t="n">
         <v>79029</v>
@@ -33456,10 +33456,10 @@
         </is>
       </c>
       <c r="Q323" t="n">
-        <v>443266</v>
+        <v>443378</v>
       </c>
       <c r="R323" t="n">
-        <v>6767409</v>
+        <v>6767040</v>
       </c>
       <c r="S323" t="n">
         <v>10</v>
@@ -33518,7 +33518,7 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>127723076</v>
+        <v>127723372</v>
       </c>
       <c r="B324" t="n">
         <v>79029</v>
@@ -33553,10 +33553,10 @@
         </is>
       </c>
       <c r="Q324" t="n">
-        <v>443378</v>
+        <v>443812</v>
       </c>
       <c r="R324" t="n">
-        <v>6767040</v>
+        <v>6767016</v>
       </c>
       <c r="S324" t="n">
         <v>10</v>
@@ -33615,7 +33615,7 @@
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>127723372</v>
+        <v>127723376</v>
       </c>
       <c r="B325" t="n">
         <v>79029</v>
@@ -33650,10 +33650,10 @@
         </is>
       </c>
       <c r="Q325" t="n">
-        <v>443812</v>
+        <v>443810</v>
       </c>
       <c r="R325" t="n">
-        <v>6767016</v>
+        <v>6767041</v>
       </c>
       <c r="S325" t="n">
         <v>10</v>
@@ -33712,7 +33712,7 @@
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>127723376</v>
+        <v>127723221</v>
       </c>
       <c r="B326" t="n">
         <v>79029</v>
@@ -33747,10 +33747,10 @@
         </is>
       </c>
       <c r="Q326" t="n">
-        <v>443810</v>
+        <v>443444</v>
       </c>
       <c r="R326" t="n">
-        <v>6767041</v>
+        <v>6767069</v>
       </c>
       <c r="S326" t="n">
         <v>10</v>
@@ -33809,7 +33809,7 @@
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>127723221</v>
+        <v>127723277</v>
       </c>
       <c r="B327" t="n">
         <v>79029</v>
@@ -33844,10 +33844,10 @@
         </is>
       </c>
       <c r="Q327" t="n">
-        <v>443444</v>
+        <v>443284</v>
       </c>
       <c r="R327" t="n">
-        <v>6767069</v>
+        <v>6767460</v>
       </c>
       <c r="S327" t="n">
         <v>10</v>
@@ -33906,7 +33906,7 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>127723277</v>
+        <v>127723217</v>
       </c>
       <c r="B328" t="n">
         <v>79029</v>
@@ -33941,10 +33941,10 @@
         </is>
       </c>
       <c r="Q328" t="n">
-        <v>443284</v>
+        <v>443420</v>
       </c>
       <c r="R328" t="n">
-        <v>6767460</v>
+        <v>6767003</v>
       </c>
       <c r="S328" t="n">
         <v>10</v>
@@ -34003,10 +34003,10 @@
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>127723217</v>
+        <v>127723572</v>
       </c>
       <c r="B329" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -34014,21 +34014,21 @@
         </is>
       </c>
       <c r="E329" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I329" t="inlineStr"/>
@@ -34038,10 +34038,10 @@
         </is>
       </c>
       <c r="Q329" t="n">
-        <v>443420</v>
+        <v>443311</v>
       </c>
       <c r="R329" t="n">
-        <v>6767003</v>
+        <v>6767073</v>
       </c>
       <c r="S329" t="n">
         <v>10</v>
@@ -34100,10 +34100,10 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>127723548</v>
+        <v>127722807</v>
       </c>
       <c r="B330" t="n">
-        <v>57672</v>
+        <v>79647</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -34111,39 +34111,34 @@
         </is>
       </c>
       <c r="E330" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I330" t="inlineStr"/>
-      <c r="M330" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P330" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q330" t="n">
-        <v>443276</v>
+        <v>443325</v>
       </c>
       <c r="R330" t="n">
-        <v>6767251</v>
+        <v>6767147</v>
       </c>
       <c r="S330" t="n">
         <v>10</v>
@@ -34202,10 +34197,10 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>127723620</v>
+        <v>127723057</v>
       </c>
       <c r="B331" t="n">
-        <v>57672</v>
+        <v>78787</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -34213,39 +34208,34 @@
         </is>
       </c>
       <c r="E331" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I331" t="inlineStr"/>
-      <c r="M331" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P331" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q331" t="n">
-        <v>443652</v>
+        <v>443796</v>
       </c>
       <c r="R331" t="n">
-        <v>6766866</v>
+        <v>6767030</v>
       </c>
       <c r="S331" t="n">
         <v>10</v>
@@ -34280,17 +34270,13 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC331" t="inlineStr">
-        <is>
-          <t>I toppbruten tall</t>
-        </is>
-      </c>
       <c r="AD331" t="b">
         <v>0</v>
       </c>
       <c r="AE331" t="b">
         <v>0</v>
       </c>
+      <c r="AF331" t="inlineStr"/>
       <c r="AG331" t="b">
         <v>0</v>
       </c>
@@ -34309,38 +34295,38 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>127722987</v>
+        <v>127723548</v>
       </c>
       <c r="B332" t="n">
-        <v>8450</v>
+        <v>57672</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E332" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I332" t="inlineStr"/>
       <c r="M332" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P332" t="inlineStr">
@@ -34349,10 +34335,10 @@
         </is>
       </c>
       <c r="Q332" t="n">
-        <v>443641</v>
+        <v>443276</v>
       </c>
       <c r="R332" t="n">
-        <v>6767127</v>
+        <v>6767251</v>
       </c>
       <c r="S332" t="n">
         <v>10</v>
@@ -34411,38 +34397,38 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>127722998</v>
+        <v>127723620</v>
       </c>
       <c r="B333" t="n">
-        <v>8450</v>
+        <v>57672</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E333" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I333" t="inlineStr"/>
       <c r="M333" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P333" t="inlineStr">
@@ -34451,10 +34437,10 @@
         </is>
       </c>
       <c r="Q333" t="n">
-        <v>443898</v>
+        <v>443652</v>
       </c>
       <c r="R333" t="n">
-        <v>6766976</v>
+        <v>6766866</v>
       </c>
       <c r="S333" t="n">
         <v>10</v>
@@ -34487,6 +34473,11 @@
       <c r="AA333" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC333" t="inlineStr">
+        <is>
+          <t>I toppbruten tall</t>
         </is>
       </c>
       <c r="AD333" t="b">
@@ -34513,7 +34504,7 @@
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>127722999</v>
+        <v>127722987</v>
       </c>
       <c r="B334" t="n">
         <v>8450</v>
@@ -34553,10 +34544,10 @@
         </is>
       </c>
       <c r="Q334" t="n">
-        <v>443887</v>
+        <v>443641</v>
       </c>
       <c r="R334" t="n">
-        <v>6766991</v>
+        <v>6767127</v>
       </c>
       <c r="S334" t="n">
         <v>10</v>
@@ -34615,7 +34606,7 @@
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>127722968</v>
+        <v>127722998</v>
       </c>
       <c r="B335" t="n">
         <v>8450</v>
@@ -34655,10 +34646,10 @@
         </is>
       </c>
       <c r="Q335" t="n">
-        <v>443270</v>
+        <v>443898</v>
       </c>
       <c r="R335" t="n">
-        <v>6767224</v>
+        <v>6766976</v>
       </c>
       <c r="S335" t="n">
         <v>10</v>
@@ -34717,7 +34708,7 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>127722996</v>
+        <v>127722999</v>
       </c>
       <c r="B336" t="n">
         <v>8450</v>
@@ -34757,10 +34748,10 @@
         </is>
       </c>
       <c r="Q336" t="n">
-        <v>443936</v>
+        <v>443887</v>
       </c>
       <c r="R336" t="n">
-        <v>6766937</v>
+        <v>6766991</v>
       </c>
       <c r="S336" t="n">
         <v>10</v>
@@ -34819,7 +34810,7 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>127722936</v>
+        <v>127722968</v>
       </c>
       <c r="B337" t="n">
         <v>8450</v>
@@ -34859,10 +34850,10 @@
         </is>
       </c>
       <c r="Q337" t="n">
-        <v>443333</v>
+        <v>443270</v>
       </c>
       <c r="R337" t="n">
-        <v>6767302</v>
+        <v>6767224</v>
       </c>
       <c r="S337" t="n">
         <v>10</v>
@@ -34921,7 +34912,7 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>127729077</v>
+        <v>127722996</v>
       </c>
       <c r="B338" t="n">
         <v>8450</v>
@@ -34950,16 +34941,21 @@
         </is>
       </c>
       <c r="I338" t="inlineStr"/>
+      <c r="M338" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P338" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q338" t="n">
-        <v>443872</v>
+        <v>443936</v>
       </c>
       <c r="R338" t="n">
-        <v>6766601</v>
+        <v>6766937</v>
       </c>
       <c r="S338" t="n">
         <v>10</v>
@@ -34989,85 +34985,79 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z338" t="inlineStr">
-        <is>
-          <t>14:58</t>
-        </is>
-      </c>
       <c r="AA338" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB338" t="inlineStr">
-        <is>
-          <t>14:58</t>
-        </is>
-      </c>
       <c r="AD338" t="b">
         <v>0</v>
       </c>
       <c r="AE338" t="b">
         <v>0</v>
       </c>
-      <c r="AF338" t="inlineStr"/>
       <c r="AG338" t="b">
         <v>0</v>
       </c>
       <c r="AT338" t="inlineStr"/>
       <c r="AW338" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX338" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>127723042</v>
+        <v>127722936</v>
       </c>
       <c r="B339" t="n">
-        <v>78788</v>
+        <v>8450</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E339" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I339" t="inlineStr"/>
+      <c r="M339" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P339" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q339" t="n">
-        <v>443538</v>
+        <v>443333</v>
       </c>
       <c r="R339" t="n">
-        <v>6766912</v>
+        <v>6767302</v>
       </c>
       <c r="S339" t="n">
         <v>10</v>
@@ -35126,45 +35116,45 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>127722807</v>
+        <v>127729077</v>
       </c>
       <c r="B340" t="n">
-        <v>79647</v>
+        <v>8450</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E340" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I340" t="inlineStr"/>
       <c r="P340" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q340" t="n">
-        <v>443325</v>
+        <v>443872</v>
       </c>
       <c r="R340" t="n">
-        <v>6767147</v>
+        <v>6766601</v>
       </c>
       <c r="S340" t="n">
         <v>10</v>
@@ -35194,39 +35184,50 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z340" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
       <c r="AA340" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB340" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
       <c r="AD340" t="b">
         <v>0</v>
       </c>
       <c r="AE340" t="b">
         <v>0</v>
       </c>
+      <c r="AF340" t="inlineStr"/>
       <c r="AG340" t="b">
         <v>0</v>
       </c>
       <c r="AT340" t="inlineStr"/>
       <c r="AW340" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX340" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>127723057</v>
+        <v>127723042</v>
       </c>
       <c r="B341" t="n">
-        <v>78787</v>
+        <v>78788</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -35234,21 +35235,21 @@
         </is>
       </c>
       <c r="E341" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I341" t="inlineStr"/>
@@ -35258,10 +35259,10 @@
         </is>
       </c>
       <c r="Q341" t="n">
-        <v>443796</v>
+        <v>443538</v>
       </c>
       <c r="R341" t="n">
-        <v>6767030</v>
+        <v>6766912</v>
       </c>
       <c r="S341" t="n">
         <v>10</v>
@@ -35302,7 +35303,6 @@
       <c r="AE341" t="b">
         <v>0</v>
       </c>
-      <c r="AF341" t="inlineStr"/>
       <c r="AG341" t="b">
         <v>0</v>
       </c>
@@ -35430,53 +35430,45 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>127730270</v>
+        <v>127729076</v>
       </c>
       <c r="B343" t="n">
-        <v>57672</v>
+        <v>92654</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E343" t="n">
-        <v>100109</v>
+        <v>4366</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I343" t="inlineStr"/>
-      <c r="K343" t="inlineStr"/>
-      <c r="L343" t="inlineStr"/>
-      <c r="M343" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N343" t="inlineStr"/>
       <c r="P343" t="inlineStr">
         <is>
-          <t>Oxeråsen S om, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q343" t="n">
-        <v>443273</v>
+        <v>443894</v>
       </c>
       <c r="R343" t="n">
-        <v>6767233</v>
+        <v>6766720</v>
       </c>
       <c r="S343" t="n">
         <v>10</v>
@@ -35506,14 +35498,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z343" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
       <c r="AA343" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC343" t="inlineStr">
-        <is>
-          <t>Ringhack gamla</t>
+      <c r="AB343" t="inlineStr">
+        <is>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD343" t="b">
@@ -35522,6 +35519,7 @@
       <c r="AE343" t="b">
         <v>0</v>
       </c>
+      <c r="AF343" t="inlineStr"/>
       <c r="AG343" t="b">
         <v>0</v>
       </c>
@@ -35540,45 +35538,45 @@
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>127729076</v>
+        <v>127723211</v>
       </c>
       <c r="B344" t="n">
-        <v>92654</v>
+        <v>79029</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E344" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I344" t="inlineStr"/>
       <c r="P344" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q344" t="n">
-        <v>443894</v>
+        <v>443486</v>
       </c>
       <c r="R344" t="n">
-        <v>6766720</v>
+        <v>6766965</v>
       </c>
       <c r="S344" t="n">
         <v>10</v>
@@ -35608,47 +35606,36 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z344" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
       <c r="AA344" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB344" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
       <c r="AD344" t="b">
         <v>0</v>
       </c>
       <c r="AE344" t="b">
         <v>0</v>
       </c>
-      <c r="AF344" t="inlineStr"/>
       <c r="AG344" t="b">
         <v>0</v>
       </c>
       <c r="AT344" t="inlineStr"/>
       <c r="AW344" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX344" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>127723211</v>
+        <v>127723553</v>
       </c>
       <c r="B345" t="n">
         <v>79029</v>
@@ -35683,10 +35670,10 @@
         </is>
       </c>
       <c r="Q345" t="n">
-        <v>443486</v>
+        <v>443748</v>
       </c>
       <c r="R345" t="n">
-        <v>6766965</v>
+        <v>6767154</v>
       </c>
       <c r="S345" t="n">
         <v>10</v>
@@ -35745,7 +35732,7 @@
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>127723553</v>
+        <v>127729131</v>
       </c>
       <c r="B346" t="n">
         <v>79029</v>
@@ -35776,14 +35763,14 @@
       <c r="I346" t="inlineStr"/>
       <c r="P346" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q346" t="n">
-        <v>443748</v>
+        <v>443929</v>
       </c>
       <c r="R346" t="n">
-        <v>6767154</v>
+        <v>6766582</v>
       </c>
       <c r="S346" t="n">
         <v>10</v>
@@ -35813,36 +35800,47 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z346" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
       <c r="AA346" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB346" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
       <c r="AD346" t="b">
         <v>0</v>
       </c>
       <c r="AE346" t="b">
         <v>0</v>
       </c>
+      <c r="AF346" t="inlineStr"/>
       <c r="AG346" t="b">
         <v>0</v>
       </c>
       <c r="AT346" t="inlineStr"/>
       <c r="AW346" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX346" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>127729131</v>
+        <v>127723352</v>
       </c>
       <c r="B347" t="n">
         <v>79029</v>
@@ -35873,14 +35871,14 @@
       <c r="I347" t="inlineStr"/>
       <c r="P347" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q347" t="n">
-        <v>443929</v>
+        <v>443848</v>
       </c>
       <c r="R347" t="n">
-        <v>6766582</v>
+        <v>6766953</v>
       </c>
       <c r="S347" t="n">
         <v>10</v>
@@ -35910,47 +35908,36 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z347" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
       <c r="AA347" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB347" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
       <c r="AD347" t="b">
         <v>0</v>
       </c>
       <c r="AE347" t="b">
         <v>0</v>
       </c>
-      <c r="AF347" t="inlineStr"/>
       <c r="AG347" t="b">
         <v>0</v>
       </c>
       <c r="AT347" t="inlineStr"/>
       <c r="AW347" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX347" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>127723352</v>
+        <v>127723328</v>
       </c>
       <c r="B348" t="n">
         <v>79029</v>
@@ -35985,10 +35972,10 @@
         </is>
       </c>
       <c r="Q348" t="n">
-        <v>443848</v>
+        <v>443653</v>
       </c>
       <c r="R348" t="n">
-        <v>6766953</v>
+        <v>6767086</v>
       </c>
       <c r="S348" t="n">
         <v>10</v>
@@ -36047,7 +36034,7 @@
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>127723328</v>
+        <v>127729097</v>
       </c>
       <c r="B349" t="n">
         <v>79029</v>
@@ -36078,14 +36065,14 @@
       <c r="I349" t="inlineStr"/>
       <c r="P349" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q349" t="n">
-        <v>443653</v>
+        <v>443579</v>
       </c>
       <c r="R349" t="n">
-        <v>6767086</v>
+        <v>6767150</v>
       </c>
       <c r="S349" t="n">
         <v>10</v>
@@ -36115,36 +36102,47 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z349" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
       <c r="AA349" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB349" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
       <c r="AD349" t="b">
         <v>0</v>
       </c>
       <c r="AE349" t="b">
         <v>0</v>
       </c>
+      <c r="AF349" t="inlineStr"/>
       <c r="AG349" t="b">
         <v>0</v>
       </c>
       <c r="AT349" t="inlineStr"/>
       <c r="AW349" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX349" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>127729097</v>
+        <v>127723348</v>
       </c>
       <c r="B350" t="n">
         <v>79029</v>
@@ -36175,14 +36173,14 @@
       <c r="I350" t="inlineStr"/>
       <c r="P350" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q350" t="n">
-        <v>443579</v>
+        <v>443814</v>
       </c>
       <c r="R350" t="n">
-        <v>6767150</v>
+        <v>6766946</v>
       </c>
       <c r="S350" t="n">
         <v>10</v>
@@ -36212,47 +36210,36 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z350" t="inlineStr">
-        <is>
-          <t>17:10</t>
-        </is>
-      </c>
       <c r="AA350" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB350" t="inlineStr">
-        <is>
-          <t>17:10</t>
-        </is>
-      </c>
       <c r="AD350" t="b">
         <v>0</v>
       </c>
       <c r="AE350" t="b">
         <v>0</v>
       </c>
-      <c r="AF350" t="inlineStr"/>
       <c r="AG350" t="b">
         <v>0</v>
       </c>
       <c r="AT350" t="inlineStr"/>
       <c r="AW350" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX350" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>127723348</v>
+        <v>127723313</v>
       </c>
       <c r="B351" t="n">
         <v>79029</v>
@@ -36287,10 +36274,10 @@
         </is>
       </c>
       <c r="Q351" t="n">
-        <v>443814</v>
+        <v>443612</v>
       </c>
       <c r="R351" t="n">
-        <v>6766946</v>
+        <v>6767149</v>
       </c>
       <c r="S351" t="n">
         <v>10</v>
@@ -36349,7 +36336,7 @@
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>127723313</v>
+        <v>127729120</v>
       </c>
       <c r="B352" t="n">
         <v>79029</v>
@@ -36380,14 +36367,14 @@
       <c r="I352" t="inlineStr"/>
       <c r="P352" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q352" t="n">
-        <v>443612</v>
+        <v>443935</v>
       </c>
       <c r="R352" t="n">
-        <v>6767149</v>
+        <v>6766723</v>
       </c>
       <c r="S352" t="n">
         <v>10</v>
@@ -36417,39 +36404,50 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z352" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
       <c r="AA352" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB352" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
       <c r="AD352" t="b">
         <v>0</v>
       </c>
       <c r="AE352" t="b">
         <v>0</v>
       </c>
+      <c r="AF352" t="inlineStr"/>
       <c r="AG352" t="b">
         <v>0</v>
       </c>
       <c r="AT352" t="inlineStr"/>
       <c r="AW352" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX352" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>127729120</v>
+        <v>127722812</v>
       </c>
       <c r="B353" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -36457,34 +36455,34 @@
         </is>
       </c>
       <c r="E353" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I353" t="inlineStr"/>
       <c r="P353" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q353" t="n">
-        <v>443935</v>
+        <v>443600</v>
       </c>
       <c r="R353" t="n">
-        <v>6766723</v>
+        <v>6767125</v>
       </c>
       <c r="S353" t="n">
         <v>10</v>
@@ -36514,50 +36512,39 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z353" t="inlineStr">
-        <is>
-          <t>16:10</t>
-        </is>
-      </c>
       <c r="AA353" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB353" t="inlineStr">
-        <is>
-          <t>16:10</t>
-        </is>
-      </c>
       <c r="AD353" t="b">
         <v>0</v>
       </c>
       <c r="AE353" t="b">
         <v>0</v>
       </c>
-      <c r="AF353" t="inlineStr"/>
       <c r="AG353" t="b">
         <v>0</v>
       </c>
       <c r="AT353" t="inlineStr"/>
       <c r="AW353" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX353" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>127722812</v>
+        <v>127723333</v>
       </c>
       <c r="B354" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -36565,21 +36552,21 @@
         </is>
       </c>
       <c r="E354" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I354" t="inlineStr"/>
@@ -36589,10 +36576,10 @@
         </is>
       </c>
       <c r="Q354" t="n">
-        <v>443600</v>
+        <v>443690</v>
       </c>
       <c r="R354" t="n">
-        <v>6767125</v>
+        <v>6767074</v>
       </c>
       <c r="S354" t="n">
         <v>10</v>
@@ -36651,7 +36638,7 @@
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>127723333</v>
+        <v>127723258</v>
       </c>
       <c r="B355" t="n">
         <v>79029</v>
@@ -36686,10 +36673,10 @@
         </is>
       </c>
       <c r="Q355" t="n">
-        <v>443690</v>
+        <v>443306</v>
       </c>
       <c r="R355" t="n">
-        <v>6767074</v>
+        <v>6767334</v>
       </c>
       <c r="S355" t="n">
         <v>10</v>
@@ -36748,7 +36735,7 @@
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>127723258</v>
+        <v>127723219</v>
       </c>
       <c r="B356" t="n">
         <v>79029</v>
@@ -36783,10 +36770,10 @@
         </is>
       </c>
       <c r="Q356" t="n">
-        <v>443306</v>
+        <v>443442</v>
       </c>
       <c r="R356" t="n">
-        <v>6767334</v>
+        <v>6767042</v>
       </c>
       <c r="S356" t="n">
         <v>10</v>
@@ -36845,10 +36832,10 @@
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>127723219</v>
+        <v>127730270</v>
       </c>
       <c r="B357" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -36856,34 +36843,42 @@
         </is>
       </c>
       <c r="E357" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I357" t="inlineStr"/>
+      <c r="K357" t="inlineStr"/>
+      <c r="L357" t="inlineStr"/>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N357" t="inlineStr"/>
       <c r="P357" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S om, Dlr</t>
         </is>
       </c>
       <c r="Q357" t="n">
-        <v>443442</v>
+        <v>443273</v>
       </c>
       <c r="R357" t="n">
-        <v>6767042</v>
+        <v>6767233</v>
       </c>
       <c r="S357" t="n">
         <v>10</v>
@@ -36918,6 +36913,11 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AC357" t="inlineStr">
+        <is>
+          <t>Ringhack gamla</t>
+        </is>
+      </c>
       <c r="AD357" t="b">
         <v>0</v>
       </c>
@@ -36930,12 +36930,12 @@
       <c r="AT357" t="inlineStr"/>
       <c r="AW357" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX357" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY357" t="inlineStr"/>
@@ -41772,7 +41772,7 @@
     </row>
     <row r="406">
       <c r="A406" t="n">
-        <v>127723393</v>
+        <v>127723225</v>
       </c>
       <c r="B406" t="n">
         <v>79029</v>
@@ -41807,10 +41807,10 @@
         </is>
       </c>
       <c r="Q406" t="n">
-        <v>443672</v>
+        <v>443404</v>
       </c>
       <c r="R406" t="n">
-        <v>6767146</v>
+        <v>6767071</v>
       </c>
       <c r="S406" t="n">
         <v>10</v>
@@ -41869,7 +41869,7 @@
     </row>
     <row r="407">
       <c r="A407" t="n">
-        <v>127723225</v>
+        <v>127723273</v>
       </c>
       <c r="B407" t="n">
         <v>79029</v>
@@ -41904,10 +41904,10 @@
         </is>
       </c>
       <c r="Q407" t="n">
-        <v>443404</v>
+        <v>443264</v>
       </c>
       <c r="R407" t="n">
-        <v>6767071</v>
+        <v>6767454</v>
       </c>
       <c r="S407" t="n">
         <v>10</v>
@@ -41966,45 +41966,50 @@
     </row>
     <row r="408">
       <c r="A408" t="n">
-        <v>127723273</v>
+        <v>127722959</v>
       </c>
       <c r="B408" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E408" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I408" t="inlineStr"/>
+      <c r="M408" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P408" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q408" t="n">
-        <v>443264</v>
+        <v>443559</v>
       </c>
       <c r="R408" t="n">
-        <v>6767454</v>
+        <v>6766954</v>
       </c>
       <c r="S408" t="n">
         <v>10</v>
@@ -42063,10 +42068,10 @@
     </row>
     <row r="409">
       <c r="A409" t="n">
-        <v>127729090</v>
+        <v>127723393</v>
       </c>
       <c r="B409" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -42074,34 +42079,34 @@
         </is>
       </c>
       <c r="E409" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I409" t="inlineStr"/>
       <c r="P409" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q409" t="n">
-        <v>443550</v>
+        <v>443672</v>
       </c>
       <c r="R409" t="n">
-        <v>6767191</v>
+        <v>6767146</v>
       </c>
       <c r="S409" t="n">
         <v>10</v>
@@ -42131,50 +42136,39 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z409" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
       <c r="AA409" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB409" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
       <c r="AD409" t="b">
         <v>0</v>
       </c>
       <c r="AE409" t="b">
         <v>0</v>
       </c>
-      <c r="AF409" t="inlineStr"/>
       <c r="AG409" t="b">
         <v>0</v>
       </c>
       <c r="AT409" t="inlineStr"/>
       <c r="AW409" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX409" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY409" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" t="n">
-        <v>127723377</v>
+        <v>127729090</v>
       </c>
       <c r="B410" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -42182,34 +42176,34 @@
         </is>
       </c>
       <c r="E410" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I410" t="inlineStr"/>
       <c r="P410" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q410" t="n">
-        <v>443794</v>
+        <v>443550</v>
       </c>
       <c r="R410" t="n">
-        <v>6767054</v>
+        <v>6767191</v>
       </c>
       <c r="S410" t="n">
         <v>10</v>
@@ -42239,36 +42233,47 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z410" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
       <c r="AA410" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB410" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
       <c r="AD410" t="b">
         <v>0</v>
       </c>
       <c r="AE410" t="b">
         <v>0</v>
       </c>
+      <c r="AF410" t="inlineStr"/>
       <c r="AG410" t="b">
         <v>0</v>
       </c>
       <c r="AT410" t="inlineStr"/>
       <c r="AW410" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX410" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" t="n">
-        <v>127723331</v>
+        <v>127723377</v>
       </c>
       <c r="B411" t="n">
         <v>79029</v>
@@ -42303,10 +42308,10 @@
         </is>
       </c>
       <c r="Q411" t="n">
-        <v>443670</v>
+        <v>443794</v>
       </c>
       <c r="R411" t="n">
-        <v>6767066</v>
+        <v>6767054</v>
       </c>
       <c r="S411" t="n">
         <v>10</v>
@@ -42365,50 +42370,45 @@
     </row>
     <row r="412">
       <c r="A412" t="n">
-        <v>127723010</v>
+        <v>127723331</v>
       </c>
       <c r="B412" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E412" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I412" t="inlineStr"/>
-      <c r="M412" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P412" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q412" t="n">
-        <v>443591</v>
+        <v>443670</v>
       </c>
       <c r="R412" t="n">
-        <v>6767183</v>
+        <v>6767066</v>
       </c>
       <c r="S412" t="n">
         <v>10</v>
@@ -42467,7 +42467,7 @@
     </row>
     <row r="413">
       <c r="A413" t="n">
-        <v>127722959</v>
+        <v>127723010</v>
       </c>
       <c r="B413" t="n">
         <v>8450</v>
@@ -42507,10 +42507,10 @@
         </is>
       </c>
       <c r="Q413" t="n">
-        <v>443559</v>
+        <v>443591</v>
       </c>
       <c r="R413" t="n">
-        <v>6766954</v>
+        <v>6767183</v>
       </c>
       <c r="S413" t="n">
         <v>10</v>
@@ -44657,45 +44657,45 @@
     </row>
     <row r="435">
       <c r="A435" t="n">
-        <v>127722893</v>
+        <v>127729085</v>
       </c>
       <c r="B435" t="n">
-        <v>98491</v>
+        <v>78788</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E435" t="n">
-        <v>221952</v>
+        <v>228912</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I435" t="inlineStr"/>
       <c r="P435" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q435" t="n">
-        <v>443380</v>
+        <v>443909</v>
       </c>
       <c r="R435" t="n">
-        <v>6767331</v>
+        <v>6766780</v>
       </c>
       <c r="S435" t="n">
         <v>10</v>
@@ -44725,74 +44725,85 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z435" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
       <c r="AA435" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB435" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
       <c r="AD435" t="b">
         <v>0</v>
       </c>
       <c r="AE435" t="b">
         <v>0</v>
       </c>
+      <c r="AF435" t="inlineStr"/>
       <c r="AG435" t="b">
         <v>0</v>
       </c>
       <c r="AT435" t="inlineStr"/>
       <c r="AW435" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX435" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY435" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" t="n">
-        <v>127729085</v>
+        <v>127722893</v>
       </c>
       <c r="B436" t="n">
-        <v>78788</v>
+        <v>98491</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E436" t="n">
-        <v>228912</v>
+        <v>221952</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I436" t="inlineStr"/>
       <c r="P436" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q436" t="n">
-        <v>443909</v>
+        <v>443380</v>
       </c>
       <c r="R436" t="n">
-        <v>6766780</v>
+        <v>6767331</v>
       </c>
       <c r="S436" t="n">
         <v>10</v>
@@ -44822,40 +44833,29 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z436" t="inlineStr">
-        <is>
-          <t>16:27</t>
-        </is>
-      </c>
       <c r="AA436" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB436" t="inlineStr">
-        <is>
-          <t>16:27</t>
-        </is>
-      </c>
       <c r="AD436" t="b">
         <v>0</v>
       </c>
       <c r="AE436" t="b">
         <v>0</v>
       </c>
-      <c r="AF436" t="inlineStr"/>
       <c r="AG436" t="b">
         <v>0</v>
       </c>
       <c r="AT436" t="inlineStr"/>
       <c r="AW436" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX436" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY436" t="inlineStr"/>
@@ -45066,7 +45066,7 @@
     </row>
     <row r="439">
       <c r="A439" t="n">
-        <v>127729101</v>
+        <v>127723252</v>
       </c>
       <c r="B439" t="n">
         <v>79029</v>
@@ -45097,14 +45097,14 @@
       <c r="I439" t="inlineStr"/>
       <c r="P439" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q439" t="n">
-        <v>443699</v>
+        <v>443264</v>
       </c>
       <c r="R439" t="n">
-        <v>6766987</v>
+        <v>6767298</v>
       </c>
       <c r="S439" t="n">
         <v>10</v>
@@ -45134,47 +45134,36 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z439" t="inlineStr">
-        <is>
-          <t>16:53</t>
-        </is>
-      </c>
       <c r="AA439" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB439" t="inlineStr">
-        <is>
-          <t>16:53</t>
-        </is>
-      </c>
       <c r="AD439" t="b">
         <v>0</v>
       </c>
       <c r="AE439" t="b">
         <v>0</v>
       </c>
-      <c r="AF439" t="inlineStr"/>
       <c r="AG439" t="b">
         <v>0</v>
       </c>
       <c r="AT439" t="inlineStr"/>
       <c r="AW439" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX439" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY439" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" t="n">
-        <v>127723241</v>
+        <v>127729101</v>
       </c>
       <c r="B440" t="n">
         <v>79029</v>
@@ -45205,14 +45194,14 @@
       <c r="I440" t="inlineStr"/>
       <c r="P440" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q440" t="n">
-        <v>443271</v>
+        <v>443699</v>
       </c>
       <c r="R440" t="n">
-        <v>6767202</v>
+        <v>6766987</v>
       </c>
       <c r="S440" t="n">
         <v>10</v>
@@ -45242,36 +45231,47 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z440" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
       <c r="AA440" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB440" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
       <c r="AD440" t="b">
         <v>0</v>
       </c>
       <c r="AE440" t="b">
         <v>0</v>
       </c>
+      <c r="AF440" t="inlineStr"/>
       <c r="AG440" t="b">
         <v>0</v>
       </c>
       <c r="AT440" t="inlineStr"/>
       <c r="AW440" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX440" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY440" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" t="n">
-        <v>127723202</v>
+        <v>127723241</v>
       </c>
       <c r="B441" t="n">
         <v>79029</v>
@@ -45306,10 +45306,10 @@
         </is>
       </c>
       <c r="Q441" t="n">
-        <v>443546</v>
+        <v>443271</v>
       </c>
       <c r="R441" t="n">
-        <v>6766933</v>
+        <v>6767202</v>
       </c>
       <c r="S441" t="n">
         <v>10</v>
@@ -45368,7 +45368,7 @@
     </row>
     <row r="442">
       <c r="A442" t="n">
-        <v>127723314</v>
+        <v>127723202</v>
       </c>
       <c r="B442" t="n">
         <v>79029</v>
@@ -45403,10 +45403,10 @@
         </is>
       </c>
       <c r="Q442" t="n">
-        <v>443600</v>
+        <v>443546</v>
       </c>
       <c r="R442" t="n">
-        <v>6767128</v>
+        <v>6766933</v>
       </c>
       <c r="S442" t="n">
         <v>10</v>
@@ -45465,7 +45465,7 @@
     </row>
     <row r="443">
       <c r="A443" t="n">
-        <v>127723318</v>
+        <v>127723314</v>
       </c>
       <c r="B443" t="n">
         <v>79029</v>
@@ -45500,10 +45500,10 @@
         </is>
       </c>
       <c r="Q443" t="n">
-        <v>443601</v>
+        <v>443600</v>
       </c>
       <c r="R443" t="n">
-        <v>6767100</v>
+        <v>6767128</v>
       </c>
       <c r="S443" t="n">
         <v>10</v>
@@ -45562,10 +45562,10 @@
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>127722871</v>
+        <v>127723318</v>
       </c>
       <c r="B444" t="n">
-        <v>57832</v>
+        <v>79029</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -45573,39 +45573,34 @@
         </is>
       </c>
       <c r="E444" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I444" t="inlineStr"/>
-      <c r="M444" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P444" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q444" t="n">
-        <v>443317</v>
+        <v>443601</v>
       </c>
       <c r="R444" t="n">
-        <v>6767117</v>
+        <v>6767100</v>
       </c>
       <c r="S444" t="n">
         <v>10</v>
@@ -45664,7 +45659,7 @@
     </row>
     <row r="445">
       <c r="A445" t="n">
-        <v>127723252</v>
+        <v>127723237</v>
       </c>
       <c r="B445" t="n">
         <v>79029</v>
@@ -45699,10 +45694,10 @@
         </is>
       </c>
       <c r="Q445" t="n">
-        <v>443264</v>
+        <v>443326</v>
       </c>
       <c r="R445" t="n">
-        <v>6767298</v>
+        <v>6767155</v>
       </c>
       <c r="S445" t="n">
         <v>10</v>
@@ -45761,10 +45756,10 @@
     </row>
     <row r="446">
       <c r="A446" t="n">
-        <v>127722822</v>
+        <v>127722871</v>
       </c>
       <c r="B446" t="n">
-        <v>79647</v>
+        <v>57832</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -45772,34 +45767,39 @@
         </is>
       </c>
       <c r="E446" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I446" t="inlineStr"/>
+      <c r="M446" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P446" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q446" t="n">
-        <v>443850</v>
+        <v>443317</v>
       </c>
       <c r="R446" t="n">
-        <v>6766994</v>
+        <v>6767117</v>
       </c>
       <c r="S446" t="n">
         <v>10</v>
@@ -45858,45 +45858,50 @@
     </row>
     <row r="447">
       <c r="A447" t="n">
-        <v>127723237</v>
+        <v>127722963</v>
       </c>
       <c r="B447" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E447" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I447" t="inlineStr"/>
+      <c r="M447" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P447" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q447" t="n">
-        <v>443326</v>
+        <v>443342</v>
       </c>
       <c r="R447" t="n">
-        <v>6767155</v>
+        <v>6767084</v>
       </c>
       <c r="S447" t="n">
         <v>10</v>
@@ -45955,10 +45960,10 @@
     </row>
     <row r="448">
       <c r="A448" t="n">
-        <v>127723551</v>
+        <v>127722822</v>
       </c>
       <c r="B448" t="n">
-        <v>57672</v>
+        <v>79647</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -45966,39 +45971,34 @@
         </is>
       </c>
       <c r="E448" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H448" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I448" t="inlineStr"/>
-      <c r="M448" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P448" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q448" t="n">
-        <v>443267</v>
+        <v>443850</v>
       </c>
       <c r="R448" t="n">
-        <v>6767460</v>
+        <v>6766994</v>
       </c>
       <c r="S448" t="n">
         <v>10</v>
@@ -46057,38 +46057,38 @@
     </row>
     <row r="449">
       <c r="A449" t="n">
-        <v>127722963</v>
+        <v>127723551</v>
       </c>
       <c r="B449" t="n">
-        <v>8450</v>
+        <v>57672</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E449" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I449" t="inlineStr"/>
       <c r="M449" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P449" t="inlineStr">
@@ -46097,10 +46097,10 @@
         </is>
       </c>
       <c r="Q449" t="n">
-        <v>443342</v>
+        <v>443267</v>
       </c>
       <c r="R449" t="n">
-        <v>6767084</v>
+        <v>6767460</v>
       </c>
       <c r="S449" t="n">
         <v>10</v>
@@ -46159,10 +46159,10 @@
     </row>
     <row r="450">
       <c r="A450" t="n">
-        <v>127722848</v>
+        <v>127723286</v>
       </c>
       <c r="B450" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -46170,21 +46170,21 @@
         </is>
       </c>
       <c r="E450" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I450" t="inlineStr"/>
@@ -46194,7 +46194,7 @@
         </is>
       </c>
       <c r="Q450" t="n">
-        <v>443293</v>
+        <v>443314</v>
       </c>
       <c r="R450" t="n">
         <v>6767432</v>
@@ -46256,10 +46256,10 @@
     </row>
     <row r="451">
       <c r="A451" t="n">
-        <v>127722810</v>
+        <v>127723324</v>
       </c>
       <c r="B451" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -46267,21 +46267,21 @@
         </is>
       </c>
       <c r="E451" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I451" t="inlineStr"/>
@@ -46291,10 +46291,10 @@
         </is>
       </c>
       <c r="Q451" t="n">
-        <v>443317</v>
+        <v>443650</v>
       </c>
       <c r="R451" t="n">
-        <v>6767425</v>
+        <v>6767135</v>
       </c>
       <c r="S451" t="n">
         <v>10</v>
@@ -46353,10 +46353,10 @@
     </row>
     <row r="452">
       <c r="A452" t="n">
-        <v>127722813</v>
+        <v>127723201</v>
       </c>
       <c r="B452" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -46364,21 +46364,21 @@
         </is>
       </c>
       <c r="E452" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I452" t="inlineStr"/>
@@ -46388,10 +46388,10 @@
         </is>
       </c>
       <c r="Q452" t="n">
-        <v>443589</v>
+        <v>443535</v>
       </c>
       <c r="R452" t="n">
-        <v>6767104</v>
+        <v>6766905</v>
       </c>
       <c r="S452" t="n">
         <v>10</v>
@@ -46450,7 +46450,7 @@
     </row>
     <row r="453">
       <c r="A453" t="n">
-        <v>127723255</v>
+        <v>127723226</v>
       </c>
       <c r="B453" t="n">
         <v>79029</v>
@@ -46485,10 +46485,10 @@
         </is>
       </c>
       <c r="Q453" t="n">
-        <v>443283</v>
+        <v>443385</v>
       </c>
       <c r="R453" t="n">
-        <v>6767309</v>
+        <v>6767068</v>
       </c>
       <c r="S453" t="n">
         <v>10</v>
@@ -46547,7 +46547,7 @@
     </row>
     <row r="454">
       <c r="A454" t="n">
-        <v>127723242</v>
+        <v>127723215</v>
       </c>
       <c r="B454" t="n">
         <v>79029</v>
@@ -46582,10 +46582,10 @@
         </is>
       </c>
       <c r="Q454" t="n">
-        <v>443270</v>
+        <v>443428</v>
       </c>
       <c r="R454" t="n">
-        <v>6767213</v>
+        <v>6766973</v>
       </c>
       <c r="S454" t="n">
         <v>10</v>
@@ -46644,50 +46644,45 @@
     </row>
     <row r="455">
       <c r="A455" t="n">
-        <v>127723007</v>
+        <v>127723358</v>
       </c>
       <c r="B455" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E455" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I455" t="inlineStr"/>
-      <c r="M455" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P455" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q455" t="n">
-        <v>443724</v>
+        <v>443949</v>
       </c>
       <c r="R455" t="n">
-        <v>6767163</v>
+        <v>6766926</v>
       </c>
       <c r="S455" t="n">
         <v>10</v>
@@ -46746,50 +46741,45 @@
     </row>
     <row r="456">
       <c r="A456" t="n">
-        <v>127722985</v>
+        <v>127723228</v>
       </c>
       <c r="B456" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E456" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I456" t="inlineStr"/>
-      <c r="M456" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P456" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q456" t="n">
-        <v>443604</v>
+        <v>443370</v>
       </c>
       <c r="R456" t="n">
-        <v>6767161</v>
+        <v>6767061</v>
       </c>
       <c r="S456" t="n">
         <v>10</v>
@@ -46848,50 +46838,45 @@
     </row>
     <row r="457">
       <c r="A457" t="n">
-        <v>127722958</v>
+        <v>127723084</v>
       </c>
       <c r="B457" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E457" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I457" t="inlineStr"/>
-      <c r="M457" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P457" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q457" t="n">
-        <v>443565</v>
+        <v>443703</v>
       </c>
       <c r="R457" t="n">
-        <v>6766939</v>
+        <v>6766768</v>
       </c>
       <c r="S457" t="n">
         <v>10</v>
@@ -46950,7 +46935,7 @@
     </row>
     <row r="458">
       <c r="A458" t="n">
-        <v>127723286</v>
+        <v>127723255</v>
       </c>
       <c r="B458" t="n">
         <v>79029</v>
@@ -46985,10 +46970,10 @@
         </is>
       </c>
       <c r="Q458" t="n">
-        <v>443314</v>
+        <v>443283</v>
       </c>
       <c r="R458" t="n">
-        <v>6767432</v>
+        <v>6767309</v>
       </c>
       <c r="S458" t="n">
         <v>10</v>
@@ -47047,7 +47032,7 @@
     </row>
     <row r="459">
       <c r="A459" t="n">
-        <v>127723324</v>
+        <v>127723242</v>
       </c>
       <c r="B459" t="n">
         <v>79029</v>
@@ -47082,10 +47067,10 @@
         </is>
       </c>
       <c r="Q459" t="n">
-        <v>443650</v>
+        <v>443270</v>
       </c>
       <c r="R459" t="n">
-        <v>6767135</v>
+        <v>6767213</v>
       </c>
       <c r="S459" t="n">
         <v>10</v>
@@ -47144,10 +47129,10 @@
     </row>
     <row r="460">
       <c r="A460" t="n">
-        <v>127723201</v>
+        <v>127722848</v>
       </c>
       <c r="B460" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -47155,21 +47140,21 @@
         </is>
       </c>
       <c r="E460" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I460" t="inlineStr"/>
@@ -47179,10 +47164,10 @@
         </is>
       </c>
       <c r="Q460" t="n">
-        <v>443535</v>
+        <v>443293</v>
       </c>
       <c r="R460" t="n">
-        <v>6766905</v>
+        <v>6767432</v>
       </c>
       <c r="S460" t="n">
         <v>10</v>
@@ -47241,10 +47226,10 @@
     </row>
     <row r="461">
       <c r="A461" t="n">
-        <v>127723226</v>
+        <v>127722810</v>
       </c>
       <c r="B461" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -47252,21 +47237,21 @@
         </is>
       </c>
       <c r="E461" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I461" t="inlineStr"/>
@@ -47276,10 +47261,10 @@
         </is>
       </c>
       <c r="Q461" t="n">
-        <v>443385</v>
+        <v>443317</v>
       </c>
       <c r="R461" t="n">
-        <v>6767068</v>
+        <v>6767425</v>
       </c>
       <c r="S461" t="n">
         <v>10</v>
@@ -47338,10 +47323,10 @@
     </row>
     <row r="462">
       <c r="A462" t="n">
-        <v>127723215</v>
+        <v>127722813</v>
       </c>
       <c r="B462" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -47349,21 +47334,21 @@
         </is>
       </c>
       <c r="E462" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I462" t="inlineStr"/>
@@ -47373,10 +47358,10 @@
         </is>
       </c>
       <c r="Q462" t="n">
-        <v>443428</v>
+        <v>443589</v>
       </c>
       <c r="R462" t="n">
-        <v>6766973</v>
+        <v>6767104</v>
       </c>
       <c r="S462" t="n">
         <v>10</v>
@@ -47435,10 +47420,10 @@
     </row>
     <row r="463">
       <c r="A463" t="n">
-        <v>127723358</v>
+        <v>127723044</v>
       </c>
       <c r="B463" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -47446,21 +47431,21 @@
         </is>
       </c>
       <c r="E463" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H463" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I463" t="inlineStr"/>
@@ -47470,10 +47455,10 @@
         </is>
       </c>
       <c r="Q463" t="n">
-        <v>443949</v>
+        <v>443548</v>
       </c>
       <c r="R463" t="n">
-        <v>6766926</v>
+        <v>6767184</v>
       </c>
       <c r="S463" t="n">
         <v>10</v>
@@ -47532,45 +47517,50 @@
     </row>
     <row r="464">
       <c r="A464" t="n">
-        <v>127723228</v>
+        <v>127723007</v>
       </c>
       <c r="B464" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E464" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I464" t="inlineStr"/>
+      <c r="M464" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P464" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q464" t="n">
-        <v>443370</v>
+        <v>443724</v>
       </c>
       <c r="R464" t="n">
-        <v>6767061</v>
+        <v>6767163</v>
       </c>
       <c r="S464" t="n">
         <v>10</v>
@@ -47629,45 +47619,50 @@
     </row>
     <row r="465">
       <c r="A465" t="n">
-        <v>127723084</v>
+        <v>127722985</v>
       </c>
       <c r="B465" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E465" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I465" t="inlineStr"/>
+      <c r="M465" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P465" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q465" t="n">
-        <v>443703</v>
+        <v>443604</v>
       </c>
       <c r="R465" t="n">
-        <v>6766768</v>
+        <v>6767161</v>
       </c>
       <c r="S465" t="n">
         <v>10</v>
@@ -47726,45 +47721,50 @@
     </row>
     <row r="466">
       <c r="A466" t="n">
-        <v>127723044</v>
+        <v>127722958</v>
       </c>
       <c r="B466" t="n">
-        <v>78788</v>
+        <v>8450</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E466" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H466" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I466" t="inlineStr"/>
+      <c r="M466" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P466" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q466" t="n">
-        <v>443548</v>
+        <v>443565</v>
       </c>
       <c r="R466" t="n">
-        <v>6767184</v>
+        <v>6766939</v>
       </c>
       <c r="S466" t="n">
         <v>10</v>
@@ -48466,32 +48466,32 @@
     </row>
     <row r="473">
       <c r="A473" t="n">
-        <v>127736022</v>
+        <v>127736037</v>
       </c>
       <c r="B473" t="n">
-        <v>79029</v>
+        <v>92642</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E473" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I473" t="inlineStr"/>
@@ -48501,10 +48501,10 @@
         </is>
       </c>
       <c r="Q473" t="n">
-        <v>443434</v>
+        <v>443903</v>
       </c>
       <c r="R473" t="n">
-        <v>6767108</v>
+        <v>6766595</v>
       </c>
       <c r="S473" t="n">
         <v>10</v>
@@ -48536,7 +48536,7 @@
       </c>
       <c r="Z473" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA473" t="inlineStr">
@@ -48546,7 +48546,7 @@
       </c>
       <c r="AB473" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD473" t="b">
@@ -48573,32 +48573,32 @@
     </row>
     <row r="474">
       <c r="A474" t="n">
-        <v>127736037</v>
+        <v>127736022</v>
       </c>
       <c r="B474" t="n">
-        <v>92642</v>
+        <v>79029</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E474" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I474" t="inlineStr"/>
@@ -48608,10 +48608,10 @@
         </is>
       </c>
       <c r="Q474" t="n">
-        <v>443903</v>
+        <v>443434</v>
       </c>
       <c r="R474" t="n">
-        <v>6766595</v>
+        <v>6767108</v>
       </c>
       <c r="S474" t="n">
         <v>10</v>
@@ -48643,7 +48643,7 @@
       </c>
       <c r="Z474" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA474" t="inlineStr">
@@ -48653,7 +48653,7 @@
       </c>
       <c r="AB474" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD474" t="b">
@@ -49323,10 +49323,10 @@
     </row>
     <row r="481">
       <c r="A481" t="n">
-        <v>127736307</v>
+        <v>127736018</v>
       </c>
       <c r="B481" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -49334,45 +49334,37 @@
         </is>
       </c>
       <c r="E481" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H481" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I481" t="inlineStr"/>
-      <c r="K481" t="inlineStr"/>
-      <c r="L481" t="inlineStr"/>
-      <c r="M481" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N481" t="inlineStr"/>
       <c r="P481" t="inlineStr">
         <is>
           <t>Oxeråsen S, Dlr</t>
         </is>
       </c>
       <c r="Q481" t="n">
-        <v>443401</v>
+        <v>443867</v>
       </c>
       <c r="R481" t="n">
-        <v>6767402</v>
+        <v>6766578</v>
       </c>
       <c r="S481" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T481" t="inlineStr">
         <is>
@@ -49399,14 +49391,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z481" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
       <c r="AA481" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC481" t="inlineStr">
-        <is>
-          <t>Ringhack tall.</t>
+      <c r="AB481" t="inlineStr">
+        <is>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD481" t="b">
@@ -49433,10 +49430,10 @@
     </row>
     <row r="482">
       <c r="A482" t="n">
-        <v>127736018</v>
+        <v>127736307</v>
       </c>
       <c r="B482" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -49444,37 +49441,45 @@
         </is>
       </c>
       <c r="E482" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I482" t="inlineStr"/>
+      <c r="K482" t="inlineStr"/>
+      <c r="L482" t="inlineStr"/>
+      <c r="M482" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N482" t="inlineStr"/>
       <c r="P482" t="inlineStr">
         <is>
           <t>Oxeråsen S, Dlr</t>
         </is>
       </c>
       <c r="Q482" t="n">
-        <v>443867</v>
+        <v>443401</v>
       </c>
       <c r="R482" t="n">
-        <v>6766578</v>
+        <v>6767402</v>
       </c>
       <c r="S482" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T482" t="inlineStr">
         <is>
@@ -49501,19 +49506,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z482" t="inlineStr">
-        <is>
-          <t>14:54</t>
-        </is>
-      </c>
       <c r="AA482" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB482" t="inlineStr">
-        <is>
-          <t>14:54</t>
+      <c r="AC482" t="inlineStr">
+        <is>
+          <t>Ringhack tall.</t>
         </is>
       </c>
       <c r="AD482" t="b">
@@ -50621,10 +50621,10 @@
     </row>
     <row r="493">
       <c r="A493" t="n">
-        <v>127795807</v>
+        <v>127795436</v>
       </c>
       <c r="B493" t="n">
-        <v>88624</v>
+        <v>79029</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -50632,28 +50632,24 @@
         </is>
       </c>
       <c r="E493" t="n">
-        <v>4412</v>
+        <v>6425</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H493" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
-        </is>
-      </c>
-      <c r="I493" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I493" t="inlineStr"/>
       <c r="J493" t="inlineStr"/>
       <c r="K493" t="inlineStr"/>
       <c r="N493" t="inlineStr"/>
@@ -50663,10 +50659,10 @@
         </is>
       </c>
       <c r="Q493" t="n">
-        <v>443370</v>
+        <v>443900</v>
       </c>
       <c r="R493" t="n">
-        <v>6767363</v>
+        <v>6766619</v>
       </c>
       <c r="S493" t="n">
         <v>50</v>
@@ -50726,10 +50722,10 @@
     </row>
     <row r="494">
       <c r="A494" t="n">
-        <v>127795436</v>
+        <v>127795451</v>
       </c>
       <c r="B494" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -50737,21 +50733,21 @@
         </is>
       </c>
       <c r="E494" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G494" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I494" t="inlineStr"/>
@@ -50764,10 +50760,10 @@
         </is>
       </c>
       <c r="Q494" t="n">
-        <v>443900</v>
+        <v>443863</v>
       </c>
       <c r="R494" t="n">
-        <v>6766619</v>
+        <v>6766645</v>
       </c>
       <c r="S494" t="n">
         <v>50</v>
@@ -50827,10 +50823,10 @@
     </row>
     <row r="495">
       <c r="A495" t="n">
-        <v>127795451</v>
+        <v>127795740</v>
       </c>
       <c r="B495" t="n">
-        <v>78787</v>
+        <v>79030</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -50838,21 +50834,21 @@
         </is>
       </c>
       <c r="E495" t="n">
-        <v>6446</v>
+        <v>230405</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I495" t="inlineStr"/>
@@ -50865,10 +50861,10 @@
         </is>
       </c>
       <c r="Q495" t="n">
-        <v>443863</v>
+        <v>443687</v>
       </c>
       <c r="R495" t="n">
-        <v>6766645</v>
+        <v>6767163</v>
       </c>
       <c r="S495" t="n">
         <v>50</v>
@@ -50928,10 +50924,10 @@
     </row>
     <row r="496">
       <c r="A496" t="n">
-        <v>127795740</v>
+        <v>127795807</v>
       </c>
       <c r="B496" t="n">
-        <v>79030</v>
+        <v>88624</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -50939,24 +50935,28 @@
         </is>
       </c>
       <c r="E496" t="n">
-        <v>230405</v>
+        <v>4412</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I496" t="inlineStr"/>
+          <t>Sacc. &amp; Cub.</t>
+        </is>
+      </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J496" t="inlineStr"/>
       <c r="K496" t="inlineStr"/>
       <c r="N496" t="inlineStr"/>
@@ -50966,10 +50966,10 @@
         </is>
       </c>
       <c r="Q496" t="n">
-        <v>443687</v>
+        <v>443370</v>
       </c>
       <c r="R496" t="n">
-        <v>6767163</v>
+        <v>6767363</v>
       </c>
       <c r="S496" t="n">
         <v>50</v>
@@ -51029,37 +51029,39 @@
     </row>
     <row r="497">
       <c r="A497" t="n">
-        <v>127795217</v>
+        <v>127795366</v>
       </c>
       <c r="B497" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E497" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I497" t="inlineStr"/>
       <c r="J497" t="inlineStr"/>
       <c r="K497" t="inlineStr"/>
+      <c r="L497" t="inlineStr"/>
+      <c r="M497" t="inlineStr"/>
       <c r="N497" t="inlineStr"/>
       <c r="P497" t="inlineStr">
         <is>
@@ -51067,10 +51069,10 @@
         </is>
       </c>
       <c r="Q497" t="n">
-        <v>443305</v>
+        <v>443860</v>
       </c>
       <c r="R497" t="n">
-        <v>6766979</v>
+        <v>6766585</v>
       </c>
       <c r="S497" t="n">
         <v>50</v>
@@ -51130,39 +51132,37 @@
     </row>
     <row r="498">
       <c r="A498" t="n">
-        <v>127795366</v>
+        <v>127795217</v>
       </c>
       <c r="B498" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E498" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I498" t="inlineStr"/>
       <c r="J498" t="inlineStr"/>
       <c r="K498" t="inlineStr"/>
-      <c r="L498" t="inlineStr"/>
-      <c r="M498" t="inlineStr"/>
       <c r="N498" t="inlineStr"/>
       <c r="P498" t="inlineStr">
         <is>
@@ -51170,10 +51170,10 @@
         </is>
       </c>
       <c r="Q498" t="n">
-        <v>443860</v>
+        <v>443305</v>
       </c>
       <c r="R498" t="n">
-        <v>6766585</v>
+        <v>6766979</v>
       </c>
       <c r="S498" t="n">
         <v>50</v>

--- a/artfynd/A 35482-2025 artfynd.xlsx
+++ b/artfynd/A 35482-2025 artfynd.xlsx
@@ -15522,10 +15522,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127723550</v>
+        <v>127729084</v>
       </c>
       <c r="B144" t="n">
-        <v>57673</v>
+        <v>78791</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15533,39 +15533,34 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>443283</v>
+        <v>443550</v>
       </c>
       <c r="R144" t="n">
-        <v>6767277</v>
+        <v>6767191</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15595,39 +15590,50 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
       <c r="AD144" t="b">
         <v>0</v>
       </c>
       <c r="AE144" t="b">
         <v>0</v>
       </c>
+      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>127723582</v>
+        <v>127723036</v>
       </c>
       <c r="B145" t="n">
-        <v>78699</v>
+        <v>78791</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15635,21 +15641,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15659,10 +15665,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>443606</v>
+        <v>443607</v>
       </c>
       <c r="R145" t="n">
-        <v>6767114</v>
+        <v>6766848</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15721,32 +15727,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>127723579</v>
+        <v>127722924</v>
       </c>
       <c r="B146" t="n">
-        <v>78699</v>
+        <v>97355</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>353</v>
+        <v>221945</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15756,10 +15762,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>443583</v>
+        <v>443272</v>
       </c>
       <c r="R146" t="n">
-        <v>6767093</v>
+        <v>6767292</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15818,45 +15824,50 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>127723317</v>
+        <v>127722803</v>
       </c>
       <c r="B147" t="n">
-        <v>79032</v>
+        <v>5197</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>443589</v>
+        <v>443270</v>
       </c>
       <c r="R147" t="n">
-        <v>6767070</v>
+        <v>6767291</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15915,45 +15926,50 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>127723326</v>
+        <v>127722995</v>
       </c>
       <c r="B148" t="n">
-        <v>79032</v>
+        <v>8450</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P148" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>443655</v>
+        <v>443979</v>
       </c>
       <c r="R148" t="n">
-        <v>6767102</v>
+        <v>6766943</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16012,45 +16028,50 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>127723263</v>
+        <v>127722974</v>
       </c>
       <c r="B149" t="n">
-        <v>79032</v>
+        <v>8450</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>443279</v>
+        <v>443325</v>
       </c>
       <c r="R149" t="n">
-        <v>6767392</v>
+        <v>6767381</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16109,10 +16130,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>127729106</v>
+        <v>127723582</v>
       </c>
       <c r="B150" t="n">
-        <v>79032</v>
+        <v>78699</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16120,34 +16141,34 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>443777</v>
+        <v>443606</v>
       </c>
       <c r="R150" t="n">
-        <v>6766919</v>
+        <v>6767114</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16177,50 +16198,39 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z150" t="inlineStr">
-        <is>
-          <t>16:47</t>
-        </is>
-      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB150" t="inlineStr">
-        <is>
-          <t>16:47</t>
-        </is>
-      </c>
       <c r="AD150" t="b">
         <v>0</v>
       </c>
       <c r="AE150" t="b">
         <v>0</v>
       </c>
-      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>127723213</v>
+        <v>127723579</v>
       </c>
       <c r="B151" t="n">
-        <v>79032</v>
+        <v>78699</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16228,21 +16238,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16252,10 +16262,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>443470</v>
+        <v>443583</v>
       </c>
       <c r="R151" t="n">
-        <v>6766976</v>
+        <v>6767093</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16314,7 +16324,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>127723370</v>
+        <v>127723317</v>
       </c>
       <c r="B152" t="n">
         <v>79032</v>
@@ -16349,10 +16359,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>443826</v>
+        <v>443589</v>
       </c>
       <c r="R152" t="n">
-        <v>6767008</v>
+        <v>6767070</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16411,7 +16421,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>127723357</v>
+        <v>127723326</v>
       </c>
       <c r="B153" t="n">
         <v>79032</v>
@@ -16446,10 +16456,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>443931</v>
+        <v>443655</v>
       </c>
       <c r="R153" t="n">
-        <v>6766931</v>
+        <v>6767102</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16508,7 +16518,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>127723199</v>
+        <v>127723263</v>
       </c>
       <c r="B154" t="n">
         <v>79032</v>
@@ -16543,10 +16553,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>443540</v>
+        <v>443279</v>
       </c>
       <c r="R154" t="n">
-        <v>6766894</v>
+        <v>6767392</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16605,7 +16615,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>127723236</v>
+        <v>127729106</v>
       </c>
       <c r="B155" t="n">
         <v>79032</v>
@@ -16636,14 +16646,14 @@
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>443310</v>
+        <v>443777</v>
       </c>
       <c r="R155" t="n">
-        <v>6767138</v>
+        <v>6766919</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16673,36 +16683,47 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
       <c r="AD155" t="b">
         <v>0</v>
       </c>
       <c r="AE155" t="b">
         <v>0</v>
       </c>
+      <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="b">
         <v>0</v>
       </c>
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>127723207</v>
+        <v>127723213</v>
       </c>
       <c r="B156" t="n">
         <v>79032</v>
@@ -16737,10 +16758,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>443526</v>
+        <v>443470</v>
       </c>
       <c r="R156" t="n">
-        <v>6766954</v>
+        <v>6766976</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16799,7 +16820,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>127729129</v>
+        <v>127723370</v>
       </c>
       <c r="B157" t="n">
         <v>79032</v>
@@ -16830,14 +16851,14 @@
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>443947</v>
+        <v>443826</v>
       </c>
       <c r="R157" t="n">
-        <v>6766584</v>
+        <v>6767008</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16867,50 +16888,39 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z157" t="inlineStr">
-        <is>
-          <t>15:17</t>
-        </is>
-      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB157" t="inlineStr">
-        <is>
-          <t>15:17</t>
-        </is>
-      </c>
       <c r="AD157" t="b">
         <v>0</v>
       </c>
       <c r="AE157" t="b">
         <v>0</v>
       </c>
-      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>127723248</v>
+        <v>127723550</v>
       </c>
       <c r="B158" t="n">
-        <v>79032</v>
+        <v>57673</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16918,34 +16928,39 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P158" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>443275</v>
+        <v>443283</v>
       </c>
       <c r="R158" t="n">
-        <v>6767256</v>
+        <v>6767277</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17004,7 +17019,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>127730382</v>
+        <v>127723357</v>
       </c>
       <c r="B159" t="n">
         <v>79032</v>
@@ -17033,19 +17048,16 @@
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
-      <c r="K159" t="inlineStr"/>
-      <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Oxeråsen S om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>443332</v>
+        <v>443931</v>
       </c>
       <c r="R159" t="n">
-        <v>6767071</v>
+        <v>6766931</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17080,37 +17092,31 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>På 10 tallstammar</t>
-        </is>
-      </c>
       <c r="AD159" t="b">
         <v>0</v>
       </c>
       <c r="AE159" t="b">
         <v>0</v>
       </c>
-      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>127723234</v>
+        <v>127723199</v>
       </c>
       <c r="B160" t="n">
         <v>79032</v>
@@ -17145,10 +17151,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>443321</v>
+        <v>443540</v>
       </c>
       <c r="R160" t="n">
-        <v>6767103</v>
+        <v>6766894</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17207,45 +17213,45 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>127729075</v>
+        <v>127723236</v>
       </c>
       <c r="B161" t="n">
-        <v>92662</v>
+        <v>79032</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>443903</v>
+        <v>443310</v>
       </c>
       <c r="R161" t="n">
-        <v>6766793</v>
+        <v>6767138</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17275,90 +17281,74 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z161" t="inlineStr">
-        <is>
-          <t>16:29</t>
-        </is>
-      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB161" t="inlineStr">
-        <is>
-          <t>16:29</t>
-        </is>
-      </c>
       <c r="AD161" t="b">
         <v>0</v>
       </c>
       <c r="AE161" t="b">
         <v>0</v>
       </c>
-      <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="b">
         <v>0</v>
       </c>
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>127722803</v>
+        <v>127723207</v>
       </c>
       <c r="B162" t="n">
-        <v>5197</v>
+        <v>79032</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P162" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>443270</v>
+        <v>443526</v>
       </c>
       <c r="R162" t="n">
-        <v>6767291</v>
+        <v>6766954</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17417,50 +17407,45 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>127722995</v>
+        <v>127729129</v>
       </c>
       <c r="B163" t="n">
-        <v>8450</v>
+        <v>79032</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
-      <c r="M163" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>443979</v>
+        <v>443947</v>
       </c>
       <c r="R163" t="n">
-        <v>6766943</v>
+        <v>6766584</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17490,79 +17475,85 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
       <c r="AA163" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB163" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
       <c r="AD163" t="b">
         <v>0</v>
       </c>
       <c r="AE163" t="b">
         <v>0</v>
       </c>
+      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>127722974</v>
+        <v>127723248</v>
       </c>
       <c r="B164" t="n">
-        <v>8450</v>
+        <v>79032</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
-      <c r="M164" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P164" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>443325</v>
+        <v>443275</v>
       </c>
       <c r="R164" t="n">
-        <v>6767381</v>
+        <v>6767256</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17621,45 +17612,48 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>127722924</v>
+        <v>127730382</v>
       </c>
       <c r="B165" t="n">
-        <v>97355</v>
+        <v>79032</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S om, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>443272</v>
+        <v>443332</v>
       </c>
       <c r="R165" t="n">
-        <v>6767292</v>
+        <v>6767071</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17694,34 +17688,40 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>På 10 tallstammar</t>
+        </is>
+      </c>
       <c r="AD165" t="b">
         <v>0</v>
       </c>
       <c r="AE165" t="b">
         <v>0</v>
       </c>
+      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>127729084</v>
+        <v>127723234</v>
       </c>
       <c r="B166" t="n">
-        <v>78791</v>
+        <v>79032</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17729,34 +17729,34 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>443550</v>
+        <v>443321</v>
       </c>
       <c r="R166" t="n">
-        <v>6767191</v>
+        <v>6767103</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17786,85 +17786,74 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z166" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB166" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
       <c r="AD166" t="b">
         <v>0</v>
       </c>
       <c r="AE166" t="b">
         <v>0</v>
       </c>
-      <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="b">
         <v>0</v>
       </c>
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>127723036</v>
+        <v>127729075</v>
       </c>
       <c r="B167" t="n">
-        <v>78791</v>
+        <v>92662</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>228912</v>
+        <v>4366</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>443607</v>
+        <v>443903</v>
       </c>
       <c r="R167" t="n">
-        <v>6766848</v>
+        <v>6766793</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17894,39 +17883,50 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
       <c r="AD167" t="b">
         <v>0</v>
       </c>
       <c r="AE167" t="b">
         <v>0</v>
       </c>
+      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>127723613</v>
+        <v>127722964</v>
       </c>
       <c r="B168" t="n">
-        <v>5177</v>
+        <v>8450</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17934,21 +17934,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17963,10 +17963,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>443517</v>
+        <v>443313</v>
       </c>
       <c r="R168" t="n">
-        <v>6766984</v>
+        <v>6767122</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18025,45 +18025,54 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>127729080</v>
+        <v>127729088</v>
       </c>
       <c r="B169" t="n">
-        <v>79032</v>
+        <v>8450</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
           <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>443643</v>
+        <v>443854</v>
       </c>
       <c r="R169" t="n">
-        <v>6767081</v>
+        <v>6766866</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18095,7 +18104,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -18105,7 +18114,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -18133,45 +18142,50 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>127723288</v>
+        <v>127723003</v>
       </c>
       <c r="B170" t="n">
-        <v>79032</v>
+        <v>8450</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P170" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>443316</v>
+        <v>443826</v>
       </c>
       <c r="R170" t="n">
-        <v>6767429</v>
+        <v>6767094</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18230,45 +18244,50 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>127723060</v>
+        <v>127723005</v>
       </c>
       <c r="B171" t="n">
-        <v>78790</v>
+        <v>8450</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P171" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>443583</v>
+        <v>443760</v>
       </c>
       <c r="R171" t="n">
-        <v>6767184</v>
+        <v>6767115</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18309,7 +18328,6 @@
       <c r="AE171" t="b">
         <v>0</v>
       </c>
-      <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="b">
         <v>0</v>
       </c>
@@ -18328,10 +18346,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>127722907</v>
+        <v>127723580</v>
       </c>
       <c r="B172" t="n">
-        <v>57673</v>
+        <v>78699</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18339,39 +18357,34 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
-      <c r="M172" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P172" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>443485</v>
+        <v>443589</v>
       </c>
       <c r="R172" t="n">
-        <v>6766960</v>
+        <v>6767070</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18404,11 +18417,6 @@
       <c r="AA172" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC172" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18435,50 +18443,45 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>127722964</v>
+        <v>127723577</v>
       </c>
       <c r="B173" t="n">
-        <v>8450</v>
+        <v>78699</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
-      <c r="M173" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P173" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>443313</v>
+        <v>443607</v>
       </c>
       <c r="R173" t="n">
-        <v>6767122</v>
+        <v>6767160</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18537,54 +18540,45 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>127729088</v>
+        <v>127723209</v>
       </c>
       <c r="B174" t="n">
-        <v>8450</v>
+        <v>79032</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
-      <c r="J174" t="inlineStr"/>
-      <c r="K174" t="inlineStr"/>
-      <c r="L174" t="inlineStr"/>
-      <c r="M174" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>443854</v>
+        <v>443502</v>
       </c>
       <c r="R174" t="n">
-        <v>6766866</v>
+        <v>6766972</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18614,90 +18608,74 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z174" t="inlineStr">
-        <is>
-          <t>16:40</t>
-        </is>
-      </c>
       <c r="AA174" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB174" t="inlineStr">
-        <is>
-          <t>16:40</t>
-        </is>
-      </c>
       <c r="AD174" t="b">
         <v>0</v>
       </c>
       <c r="AE174" t="b">
         <v>0</v>
       </c>
-      <c r="AF174" t="inlineStr"/>
       <c r="AG174" t="b">
         <v>0</v>
       </c>
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>127723003</v>
+        <v>127723390</v>
       </c>
       <c r="B175" t="n">
-        <v>8450</v>
+        <v>79032</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
-      <c r="M175" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P175" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>443826</v>
+        <v>443729</v>
       </c>
       <c r="R175" t="n">
-        <v>6767094</v>
+        <v>6767169</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18756,50 +18734,45 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>127723005</v>
+        <v>127723256</v>
       </c>
       <c r="B176" t="n">
-        <v>8450</v>
+        <v>79032</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
-      <c r="M176" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P176" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>443760</v>
+        <v>443302</v>
       </c>
       <c r="R176" t="n">
-        <v>6767115</v>
+        <v>6767306</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18858,10 +18831,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>127723580</v>
+        <v>127723238</v>
       </c>
       <c r="B177" t="n">
-        <v>78699</v>
+        <v>79032</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18869,21 +18842,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18893,10 +18866,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>443589</v>
+        <v>443333</v>
       </c>
       <c r="R177" t="n">
-        <v>6767070</v>
+        <v>6767173</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18955,10 +18928,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>127723577</v>
+        <v>127729116</v>
       </c>
       <c r="B178" t="n">
-        <v>78699</v>
+        <v>79032</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18966,34 +18939,34 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>443607</v>
+        <v>443899</v>
       </c>
       <c r="R178" t="n">
-        <v>6767160</v>
+        <v>6766758</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19023,36 +18996,47 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z178" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
       <c r="AA178" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB178" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
       <c r="AD178" t="b">
         <v>0</v>
       </c>
       <c r="AE178" t="b">
         <v>0</v>
       </c>
+      <c r="AF178" t="inlineStr"/>
       <c r="AG178" t="b">
         <v>0</v>
       </c>
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>127723209</v>
+        <v>127723220</v>
       </c>
       <c r="B179" t="n">
         <v>79032</v>
@@ -19087,10 +19071,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>443502</v>
+        <v>443452</v>
       </c>
       <c r="R179" t="n">
-        <v>6766972</v>
+        <v>6767071</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19149,45 +19133,50 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>127723390</v>
+        <v>127723613</v>
       </c>
       <c r="B180" t="n">
-        <v>79032</v>
+        <v>5177</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P180" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>443729</v>
+        <v>443517</v>
       </c>
       <c r="R180" t="n">
-        <v>6767169</v>
+        <v>6766984</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19246,7 +19235,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>127723256</v>
+        <v>127729080</v>
       </c>
       <c r="B181" t="n">
         <v>79032</v>
@@ -19277,14 +19266,14 @@
       <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>443302</v>
+        <v>443643</v>
       </c>
       <c r="R181" t="n">
-        <v>6767306</v>
+        <v>6767081</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19314,36 +19303,47 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z181" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
       <c r="AA181" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB181" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
       <c r="AD181" t="b">
         <v>0</v>
       </c>
       <c r="AE181" t="b">
         <v>0</v>
       </c>
+      <c r="AF181" t="inlineStr"/>
       <c r="AG181" t="b">
         <v>0</v>
       </c>
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>127723238</v>
+        <v>127723288</v>
       </c>
       <c r="B182" t="n">
         <v>79032</v>
@@ -19378,10 +19378,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>443333</v>
+        <v>443316</v>
       </c>
       <c r="R182" t="n">
-        <v>6767173</v>
+        <v>6767429</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19440,10 +19440,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>127729116</v>
+        <v>127723060</v>
       </c>
       <c r="B183" t="n">
-        <v>79032</v>
+        <v>78790</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19451,34 +19451,34 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>443899</v>
+        <v>443583</v>
       </c>
       <c r="R183" t="n">
-        <v>6766758</v>
+        <v>6767184</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19508,19 +19508,9 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z183" t="inlineStr">
-        <is>
-          <t>16:14</t>
-        </is>
-      </c>
       <c r="AA183" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AB183" t="inlineStr">
-        <is>
-          <t>16:14</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -19536,22 +19526,22 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>127723220</v>
+        <v>127722907</v>
       </c>
       <c r="B184" t="n">
-        <v>79032</v>
+        <v>57673</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19559,34 +19549,39 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P184" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>443452</v>
+        <v>443485</v>
       </c>
       <c r="R184" t="n">
-        <v>6767071</v>
+        <v>6766960</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19619,6 +19614,11 @@
       <c r="AA184" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC184" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -21148,38 +21148,38 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>127723618</v>
+        <v>127723614</v>
       </c>
       <c r="B200" t="n">
-        <v>57673</v>
+        <v>5177</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
       <c r="M200" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
@@ -21188,10 +21188,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>443680</v>
+        <v>443275</v>
       </c>
       <c r="R200" t="n">
-        <v>6767062</v>
+        <v>6767256</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21250,38 +21250,38 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>127723614</v>
+        <v>127723618</v>
       </c>
       <c r="B201" t="n">
-        <v>5177</v>
+        <v>57673</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
       <c r="M201" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="P201" t="inlineStr">
@@ -21290,10 +21290,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>443275</v>
+        <v>443680</v>
       </c>
       <c r="R201" t="n">
-        <v>6767256</v>
+        <v>6767062</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -23058,10 +23058,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>127723574</v>
+        <v>127722857</v>
       </c>
       <c r="B219" t="n">
-        <v>78699</v>
+        <v>79621</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -23069,21 +23069,21 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -23093,10 +23093,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>443316</v>
+        <v>443698</v>
       </c>
       <c r="R219" t="n">
-        <v>6767322</v>
+        <v>6767038</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -23155,45 +23155,50 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>127723590</v>
+        <v>127722969</v>
       </c>
       <c r="B220" t="n">
-        <v>78699</v>
+        <v>8450</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P220" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>443762</v>
+        <v>443285</v>
       </c>
       <c r="R220" t="n">
-        <v>6767123</v>
+        <v>6767253</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -23252,45 +23257,50 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>127723261</v>
+        <v>127722970</v>
       </c>
       <c r="B221" t="n">
-        <v>79032</v>
+        <v>8450</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P221" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>443289</v>
+        <v>443315</v>
       </c>
       <c r="R221" t="n">
-        <v>6767380</v>
+        <v>6767311</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -23349,45 +23359,50 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>127723085</v>
+        <v>127722937</v>
       </c>
       <c r="B222" t="n">
-        <v>79032</v>
+        <v>8450</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P222" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>443713</v>
+        <v>443632</v>
       </c>
       <c r="R222" t="n">
-        <v>6766756</v>
+        <v>6766845</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -23446,10 +23461,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>127723281</v>
+        <v>127723574</v>
       </c>
       <c r="B223" t="n">
-        <v>79032</v>
+        <v>78699</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -23457,21 +23472,21 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -23481,10 +23496,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>443279</v>
+        <v>443316</v>
       </c>
       <c r="R223" t="n">
-        <v>6767429</v>
+        <v>6767322</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -23543,10 +23558,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>127723383</v>
+        <v>127723590</v>
       </c>
       <c r="B224" t="n">
-        <v>79032</v>
+        <v>78699</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -23554,21 +23569,21 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -23578,10 +23593,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>443801</v>
+        <v>443762</v>
       </c>
       <c r="R224" t="n">
-        <v>6767104</v>
+        <v>6767123</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -23640,7 +23655,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>127723208</v>
+        <v>127723261</v>
       </c>
       <c r="B225" t="n">
         <v>79032</v>
@@ -23675,10 +23690,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>443534</v>
+        <v>443289</v>
       </c>
       <c r="R225" t="n">
-        <v>6766982</v>
+        <v>6767380</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23737,7 +23752,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>127723391</v>
+        <v>127723085</v>
       </c>
       <c r="B226" t="n">
         <v>79032</v>
@@ -23772,10 +23787,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>443677</v>
+        <v>443713</v>
       </c>
       <c r="R226" t="n">
-        <v>6767163</v>
+        <v>6766756</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -23834,7 +23849,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>127723384</v>
+        <v>127723281</v>
       </c>
       <c r="B227" t="n">
         <v>79032</v>
@@ -23869,10 +23884,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>443778</v>
+        <v>443279</v>
       </c>
       <c r="R227" t="n">
-        <v>6767109</v>
+        <v>6767429</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -23931,7 +23946,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>127723298</v>
+        <v>127723383</v>
       </c>
       <c r="B228" t="n">
         <v>79032</v>
@@ -23966,10 +23981,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>443379</v>
+        <v>443801</v>
       </c>
       <c r="R228" t="n">
-        <v>6767340</v>
+        <v>6767104</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -24028,7 +24043,7 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>127723400</v>
+        <v>127723208</v>
       </c>
       <c r="B229" t="n">
         <v>79032</v>
@@ -24063,10 +24078,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>443583</v>
+        <v>443534</v>
       </c>
       <c r="R229" t="n">
-        <v>6767200</v>
+        <v>6766982</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -24125,7 +24140,7 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>127723275</v>
+        <v>127723391</v>
       </c>
       <c r="B230" t="n">
         <v>79032</v>
@@ -24160,10 +24175,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>443267</v>
+        <v>443677</v>
       </c>
       <c r="R230" t="n">
-        <v>6767460</v>
+        <v>6767163</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -24222,7 +24237,7 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>127723316</v>
+        <v>127723384</v>
       </c>
       <c r="B231" t="n">
         <v>79032</v>
@@ -24257,10 +24272,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>443580</v>
+        <v>443778</v>
       </c>
       <c r="R231" t="n">
-        <v>6767058</v>
+        <v>6767109</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -24319,7 +24334,7 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>127723373</v>
+        <v>127723298</v>
       </c>
       <c r="B232" t="n">
         <v>79032</v>
@@ -24354,10 +24369,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>443799</v>
+        <v>443379</v>
       </c>
       <c r="R232" t="n">
-        <v>6767022</v>
+        <v>6767340</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -24416,10 +24431,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>127722808</v>
+        <v>127723400</v>
       </c>
       <c r="B233" t="n">
-        <v>79650</v>
+        <v>79032</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -24427,21 +24442,21 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -24451,10 +24466,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>443273</v>
+        <v>443583</v>
       </c>
       <c r="R233" t="n">
-        <v>6767233</v>
+        <v>6767200</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -24513,10 +24528,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>127723350</v>
+        <v>127722808</v>
       </c>
       <c r="B234" t="n">
-        <v>79032</v>
+        <v>79650</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -24524,21 +24539,21 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -24548,10 +24563,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>443834</v>
+        <v>443273</v>
       </c>
       <c r="R234" t="n">
-        <v>6766955</v>
+        <v>6767233</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -24610,50 +24625,45 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>127722969</v>
+        <v>127723350</v>
       </c>
       <c r="B235" t="n">
-        <v>8450</v>
+        <v>79032</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
-      <c r="M235" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P235" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>443285</v>
+        <v>443834</v>
       </c>
       <c r="R235" t="n">
-        <v>6767253</v>
+        <v>6766955</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -24712,50 +24722,45 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>127722970</v>
+        <v>127723275</v>
       </c>
       <c r="B236" t="n">
-        <v>8450</v>
+        <v>79032</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
-      <c r="M236" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P236" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>443315</v>
+        <v>443267</v>
       </c>
       <c r="R236" t="n">
-        <v>6767311</v>
+        <v>6767460</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -24814,50 +24819,45 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>127722937</v>
+        <v>127723316</v>
       </c>
       <c r="B237" t="n">
-        <v>8450</v>
+        <v>79032</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
-      <c r="M237" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P237" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>443632</v>
+        <v>443580</v>
       </c>
       <c r="R237" t="n">
-        <v>6766845</v>
+        <v>6767058</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -24916,10 +24916,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>127730406</v>
+        <v>127723373</v>
       </c>
       <c r="B238" t="n">
-        <v>57673</v>
+        <v>79032</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -24927,42 +24927,34 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
-      <c r="K238" t="inlineStr"/>
-      <c r="L238" t="inlineStr"/>
-      <c r="M238" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
-          <t>Oxeråsen S om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>443450</v>
+        <v>443799</v>
       </c>
       <c r="R238" t="n">
-        <v>6766975</v>
+        <v>6767022</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -24997,11 +24989,6 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC238" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD238" t="b">
         <v>0</v>
       </c>
@@ -25014,22 +25001,22 @@
       <c r="AT238" t="inlineStr"/>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>127722857</v>
+        <v>127730406</v>
       </c>
       <c r="B239" t="n">
-        <v>79621</v>
+        <v>57673</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -25037,34 +25024,42 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
+      <c r="K239" t="inlineStr"/>
+      <c r="L239" t="inlineStr"/>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S om, Dlr</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>443698</v>
+        <v>443450</v>
       </c>
       <c r="R239" t="n">
-        <v>6767038</v>
+        <v>6766975</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -25099,6 +25094,11 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AC239" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD239" t="b">
         <v>0</v>
       </c>
@@ -25111,62 +25111,57 @@
       <c r="AT239" t="inlineStr"/>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>127723008</v>
+        <v>127723585</v>
       </c>
       <c r="B240" t="n">
-        <v>8450</v>
+        <v>78699</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
-      <c r="M240" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P240" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>443716</v>
+        <v>443740</v>
       </c>
       <c r="R240" t="n">
-        <v>6767159</v>
+        <v>6766973</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -25225,50 +25220,45 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>127722991</v>
+        <v>127723203</v>
       </c>
       <c r="B241" t="n">
-        <v>8450</v>
+        <v>79032</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
-      <c r="M241" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P241" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>443828</v>
+        <v>443563</v>
       </c>
       <c r="R241" t="n">
-        <v>6766951</v>
+        <v>6766938</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -25327,50 +25317,45 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>127723000</v>
+        <v>127723392</v>
       </c>
       <c r="B242" t="n">
-        <v>8450</v>
+        <v>79032</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
-      <c r="M242" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P242" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>443873</v>
+        <v>443671</v>
       </c>
       <c r="R242" t="n">
-        <v>6766975</v>
+        <v>6767161</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -25429,50 +25414,45 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>127723004</v>
+        <v>127723227</v>
       </c>
       <c r="B243" t="n">
-        <v>8450</v>
+        <v>79032</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
-      <c r="M243" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P243" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>443813</v>
+        <v>443373</v>
       </c>
       <c r="R243" t="n">
-        <v>6767105</v>
+        <v>6767063</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -25531,10 +25511,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>127723049</v>
+        <v>127723398</v>
       </c>
       <c r="B244" t="n">
-        <v>78791</v>
+        <v>79032</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -25542,21 +25522,21 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
@@ -25566,10 +25546,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>443584</v>
+        <v>443635</v>
       </c>
       <c r="R244" t="n">
-        <v>6767184</v>
+        <v>6767173</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -25628,7 +25608,7 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>127723203</v>
+        <v>127723297</v>
       </c>
       <c r="B245" t="n">
         <v>79032</v>
@@ -25663,10 +25643,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>443563</v>
+        <v>443385</v>
       </c>
       <c r="R245" t="n">
-        <v>6766938</v>
+        <v>6767329</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -25725,10 +25705,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>127723392</v>
+        <v>127722819</v>
       </c>
       <c r="B246" t="n">
-        <v>79032</v>
+        <v>79650</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -25736,21 +25716,21 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
@@ -25760,10 +25740,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>443671</v>
+        <v>443651</v>
       </c>
       <c r="R246" t="n">
-        <v>6767161</v>
+        <v>6767092</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -25822,7 +25802,7 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>127723227</v>
+        <v>127723310</v>
       </c>
       <c r="B247" t="n">
         <v>79032</v>
@@ -25857,10 +25837,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>443373</v>
+        <v>443543</v>
       </c>
       <c r="R247" t="n">
-        <v>6767063</v>
+        <v>6767181</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -25919,10 +25899,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>127723398</v>
+        <v>127722906</v>
       </c>
       <c r="B248" t="n">
-        <v>79032</v>
+        <v>57673</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -25930,34 +25910,39 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P248" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>443635</v>
+        <v>443405</v>
       </c>
       <c r="R248" t="n">
-        <v>6767173</v>
+        <v>6767407</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -25990,6 +25975,11 @@
       <c r="AA248" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC248" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall), 3-4 år gamla</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -26016,10 +26006,10 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>127723585</v>
+        <v>127723546</v>
       </c>
       <c r="B249" t="n">
-        <v>78699</v>
+        <v>57673</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -26027,34 +26017,39 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P249" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>443740</v>
+        <v>443517</v>
       </c>
       <c r="R249" t="n">
-        <v>6766973</v>
+        <v>6766984</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -26113,45 +26108,50 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>127723297</v>
+        <v>127723008</v>
       </c>
       <c r="B250" t="n">
-        <v>79032</v>
+        <v>8450</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P250" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>443385</v>
+        <v>443716</v>
       </c>
       <c r="R250" t="n">
-        <v>6767329</v>
+        <v>6767159</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -26210,45 +26210,50 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>127722819</v>
+        <v>127722991</v>
       </c>
       <c r="B251" t="n">
-        <v>79650</v>
+        <v>8450</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P251" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>443651</v>
+        <v>443828</v>
       </c>
       <c r="R251" t="n">
-        <v>6767092</v>
+        <v>6766951</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -26307,45 +26312,50 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>127723310</v>
+        <v>127723000</v>
       </c>
       <c r="B252" t="n">
-        <v>79032</v>
+        <v>8450</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P252" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>443543</v>
+        <v>443873</v>
       </c>
       <c r="R252" t="n">
-        <v>6767181</v>
+        <v>6766975</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -26404,45 +26414,50 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>127723610</v>
+        <v>127723004</v>
       </c>
       <c r="B253" t="n">
-        <v>78010</v>
+        <v>8450</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>6487</v>
+        <v>106545</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P253" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>443680</v>
+        <v>443813</v>
       </c>
       <c r="R253" t="n">
-        <v>6766998</v>
+        <v>6767105</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -26501,10 +26516,10 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>127722906</v>
+        <v>127723049</v>
       </c>
       <c r="B254" t="n">
-        <v>57673</v>
+        <v>78791</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -26512,39 +26527,34 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
-      <c r="M254" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P254" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>443405</v>
+        <v>443584</v>
       </c>
       <c r="R254" t="n">
-        <v>6767407</v>
+        <v>6767184</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -26577,11 +26587,6 @@
       <c r="AA254" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC254" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall), 3-4 år gamla</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -26608,10 +26613,10 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>127723546</v>
+        <v>127723610</v>
       </c>
       <c r="B255" t="n">
-        <v>57673</v>
+        <v>78010</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -26619,39 +26624,34 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
-      <c r="M255" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P255" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>443517</v>
+        <v>443680</v>
       </c>
       <c r="R255" t="n">
-        <v>6766984</v>
+        <v>6766998</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -29139,7 +29139,7 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>127723253</v>
+        <v>127723280</v>
       </c>
       <c r="B280" t="n">
         <v>79032</v>
@@ -29174,10 +29174,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>443258</v>
+        <v>443281</v>
       </c>
       <c r="R280" t="n">
-        <v>6767313</v>
+        <v>6767440</v>
       </c>
       <c r="S280" t="n">
         <v>10</v>
@@ -29236,10 +29236,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>127723249</v>
+        <v>127722820</v>
       </c>
       <c r="B281" t="n">
-        <v>79032</v>
+        <v>79650</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -29247,21 +29247,21 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
@@ -29271,10 +29271,10 @@
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>443272</v>
+        <v>443903</v>
       </c>
       <c r="R281" t="n">
-        <v>6767269</v>
+        <v>6766943</v>
       </c>
       <c r="S281" t="n">
         <v>10</v>
@@ -29333,7 +29333,7 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>127729130</v>
+        <v>127729117</v>
       </c>
       <c r="B282" t="n">
         <v>79032</v>
@@ -29368,10 +29368,10 @@
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>443942</v>
+        <v>443904</v>
       </c>
       <c r="R282" t="n">
-        <v>6766584</v>
+        <v>6766753</v>
       </c>
       <c r="S282" t="n">
         <v>10</v>
@@ -29403,7 +29403,7 @@
       </c>
       <c r="Z282" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA282" t="inlineStr">
@@ -29413,7 +29413,7 @@
       </c>
       <c r="AB282" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD282" t="b">
@@ -29441,7 +29441,7 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>127723280</v>
+        <v>127723296</v>
       </c>
       <c r="B283" t="n">
         <v>79032</v>
@@ -29476,10 +29476,10 @@
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>443281</v>
+        <v>443372</v>
       </c>
       <c r="R283" t="n">
-        <v>6767440</v>
+        <v>6767321</v>
       </c>
       <c r="S283" t="n">
         <v>10</v>
@@ -29538,10 +29538,10 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>127722820</v>
+        <v>127723320</v>
       </c>
       <c r="B284" t="n">
-        <v>79650</v>
+        <v>79032</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -29549,21 +29549,21 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I284" t="inlineStr"/>
@@ -29573,10 +29573,10 @@
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>443903</v>
+        <v>443616</v>
       </c>
       <c r="R284" t="n">
-        <v>6766943</v>
+        <v>6767105</v>
       </c>
       <c r="S284" t="n">
         <v>10</v>
@@ -29635,10 +29635,10 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>127729117</v>
+        <v>127730386</v>
       </c>
       <c r="B285" t="n">
-        <v>79032</v>
+        <v>79650</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -29646,34 +29646,37 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I285" t="inlineStr"/>
+      <c r="J285" t="inlineStr"/>
+      <c r="K285" t="inlineStr"/>
+      <c r="N285" t="inlineStr"/>
       <c r="P285" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen S om, Dlr</t>
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>443904</v>
+        <v>443335</v>
       </c>
       <c r="R285" t="n">
-        <v>6766753</v>
+        <v>6767051</v>
       </c>
       <c r="S285" t="n">
         <v>10</v>
@@ -29703,19 +29706,9 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z285" t="inlineStr">
-        <is>
-          <t>16:13</t>
-        </is>
-      </c>
       <c r="AA285" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AB285" t="inlineStr">
-        <is>
-          <t>16:13</t>
         </is>
       </c>
       <c r="AD285" t="b">
@@ -29743,10 +29736,10 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>127723296</v>
+        <v>127722911</v>
       </c>
       <c r="B286" t="n">
-        <v>79032</v>
+        <v>57673</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -29754,34 +29747,39 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I286" t="inlineStr"/>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P286" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>443372</v>
+        <v>443272</v>
       </c>
       <c r="R286" t="n">
-        <v>6767321</v>
+        <v>6767269</v>
       </c>
       <c r="S286" t="n">
         <v>10</v>
@@ -29814,6 +29812,11 @@
       <c r="AA286" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC286" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD286" t="b">
@@ -29840,45 +29843,50 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>127723320</v>
+        <v>127723006</v>
       </c>
       <c r="B287" t="n">
-        <v>79032</v>
+        <v>8450</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E287" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I287" t="inlineStr"/>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P287" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>443616</v>
+        <v>443749</v>
       </c>
       <c r="R287" t="n">
-        <v>6767105</v>
+        <v>6767151</v>
       </c>
       <c r="S287" t="n">
         <v>10</v>
@@ -29937,48 +29945,50 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>127730386</v>
+        <v>127723009</v>
       </c>
       <c r="B288" t="n">
-        <v>79650</v>
+        <v>8450</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E288" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I288" t="inlineStr"/>
-      <c r="J288" t="inlineStr"/>
-      <c r="K288" t="inlineStr"/>
-      <c r="N288" t="inlineStr"/>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P288" t="inlineStr">
         <is>
-          <t>Oxeråsen S om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>443335</v>
+        <v>443652</v>
       </c>
       <c r="R288" t="n">
-        <v>6767051</v>
+        <v>6767168</v>
       </c>
       <c r="S288" t="n">
         <v>10</v>
@@ -30019,29 +30029,28 @@
       <c r="AE288" t="b">
         <v>0</v>
       </c>
-      <c r="AF288" t="inlineStr"/>
       <c r="AG288" t="b">
         <v>0</v>
       </c>
       <c r="AT288" t="inlineStr"/>
       <c r="AW288" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX288" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>127722911</v>
+        <v>127723253</v>
       </c>
       <c r="B289" t="n">
-        <v>57673</v>
+        <v>79032</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -30049,39 +30058,34 @@
         </is>
       </c>
       <c r="E289" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I289" t="inlineStr"/>
-      <c r="M289" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P289" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>443272</v>
+        <v>443258</v>
       </c>
       <c r="R289" t="n">
-        <v>6767269</v>
+        <v>6767313</v>
       </c>
       <c r="S289" t="n">
         <v>10</v>
@@ -30114,11 +30118,6 @@
       <c r="AA289" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC289" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD289" t="b">
@@ -30145,50 +30144,45 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>127723006</v>
+        <v>127723249</v>
       </c>
       <c r="B290" t="n">
-        <v>8450</v>
+        <v>79032</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E290" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I290" t="inlineStr"/>
-      <c r="M290" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P290" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q290" t="n">
-        <v>443749</v>
+        <v>443272</v>
       </c>
       <c r="R290" t="n">
-        <v>6767151</v>
+        <v>6767269</v>
       </c>
       <c r="S290" t="n">
         <v>10</v>
@@ -30247,50 +30241,45 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>127723009</v>
+        <v>127729130</v>
       </c>
       <c r="B291" t="n">
-        <v>8450</v>
+        <v>79032</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E291" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I291" t="inlineStr"/>
-      <c r="M291" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P291" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q291" t="n">
-        <v>443652</v>
+        <v>443942</v>
       </c>
       <c r="R291" t="n">
-        <v>6767168</v>
+        <v>6766584</v>
       </c>
       <c r="S291" t="n">
         <v>10</v>
@@ -30320,36 +30309,47 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z291" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
       <c r="AA291" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB291" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
       <c r="AD291" t="b">
         <v>0</v>
       </c>
       <c r="AE291" t="b">
         <v>0</v>
       </c>
+      <c r="AF291" t="inlineStr"/>
       <c r="AG291" t="b">
         <v>0</v>
       </c>
       <c r="AT291" t="inlineStr"/>
       <c r="AW291" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX291" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>127723083</v>
+        <v>127723200</v>
       </c>
       <c r="B292" t="n">
         <v>79032</v>
@@ -30384,10 +30384,10 @@
         </is>
       </c>
       <c r="Q292" t="n">
-        <v>443688</v>
+        <v>443531</v>
       </c>
       <c r="R292" t="n">
-        <v>6766773</v>
+        <v>6766902</v>
       </c>
       <c r="S292" t="n">
         <v>10</v>
@@ -30446,10 +30446,10 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>127722886</v>
+        <v>127723336</v>
       </c>
       <c r="B293" t="n">
-        <v>57670</v>
+        <v>79032</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -30457,39 +30457,34 @@
         </is>
       </c>
       <c r="E293" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I293" t="inlineStr"/>
-      <c r="M293" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P293" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q293" t="n">
-        <v>443668</v>
+        <v>443683</v>
       </c>
       <c r="R293" t="n">
-        <v>6766780</v>
+        <v>6767017</v>
       </c>
       <c r="S293" t="n">
         <v>10</v>
@@ -30548,10 +30543,10 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>127722913</v>
+        <v>127723354</v>
       </c>
       <c r="B294" t="n">
-        <v>57673</v>
+        <v>79032</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -30559,39 +30554,34 @@
         </is>
       </c>
       <c r="E294" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I294" t="inlineStr"/>
-      <c r="M294" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P294" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q294" t="n">
-        <v>443389</v>
+        <v>443864</v>
       </c>
       <c r="R294" t="n">
-        <v>6767345</v>
+        <v>6766958</v>
       </c>
       <c r="S294" t="n">
         <v>10</v>
@@ -30624,11 +30614,6 @@
       <c r="AA294" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC294" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD294" t="b">
@@ -30655,54 +30640,45 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>127730354</v>
+        <v>127723386</v>
       </c>
       <c r="B295" t="n">
-        <v>8450</v>
+        <v>79032</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E295" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I295" t="inlineStr"/>
-      <c r="J295" t="inlineStr"/>
-      <c r="K295" t="inlineStr"/>
-      <c r="L295" t="inlineStr"/>
-      <c r="M295" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N295" t="inlineStr"/>
       <c r="P295" t="inlineStr">
         <is>
-          <t>Oxeråsen S om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q295" t="n">
-        <v>443272</v>
+        <v>443737</v>
       </c>
       <c r="R295" t="n">
-        <v>6767198</v>
+        <v>6767119</v>
       </c>
       <c r="S295" t="n">
         <v>10</v>
@@ -30737,40 +30713,34 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC295" t="inlineStr">
-        <is>
-          <t>På 3 rakor</t>
-        </is>
-      </c>
       <c r="AD295" t="b">
         <v>0</v>
       </c>
       <c r="AE295" t="b">
         <v>0</v>
       </c>
-      <c r="AF295" t="inlineStr"/>
       <c r="AG295" t="b">
         <v>0</v>
       </c>
       <c r="AT295" t="inlineStr"/>
       <c r="AW295" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX295" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>127723045</v>
+        <v>127723083</v>
       </c>
       <c r="B296" t="n">
-        <v>78791</v>
+        <v>79032</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -30778,21 +30748,21 @@
         </is>
       </c>
       <c r="E296" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I296" t="inlineStr"/>
@@ -30802,10 +30772,10 @@
         </is>
       </c>
       <c r="Q296" t="n">
-        <v>443582</v>
+        <v>443688</v>
       </c>
       <c r="R296" t="n">
-        <v>6767183</v>
+        <v>6766773</v>
       </c>
       <c r="S296" t="n">
         <v>10</v>
@@ -30864,10 +30834,10 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>127723200</v>
+        <v>127722886</v>
       </c>
       <c r="B297" t="n">
-        <v>79032</v>
+        <v>57670</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -30875,34 +30845,39 @@
         </is>
       </c>
       <c r="E297" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I297" t="inlineStr"/>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P297" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q297" t="n">
-        <v>443531</v>
+        <v>443668</v>
       </c>
       <c r="R297" t="n">
-        <v>6766902</v>
+        <v>6766780</v>
       </c>
       <c r="S297" t="n">
         <v>10</v>
@@ -30961,10 +30936,10 @@
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>127723336</v>
+        <v>127722913</v>
       </c>
       <c r="B298" t="n">
-        <v>79032</v>
+        <v>57673</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -30972,34 +30947,39 @@
         </is>
       </c>
       <c r="E298" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I298" t="inlineStr"/>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P298" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q298" t="n">
-        <v>443683</v>
+        <v>443389</v>
       </c>
       <c r="R298" t="n">
-        <v>6767017</v>
+        <v>6767345</v>
       </c>
       <c r="S298" t="n">
         <v>10</v>
@@ -31032,6 +31012,11 @@
       <c r="AA298" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC298" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD298" t="b">
@@ -31058,45 +31043,54 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>127723354</v>
+        <v>127730354</v>
       </c>
       <c r="B299" t="n">
-        <v>79032</v>
+        <v>8450</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E299" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I299" t="inlineStr"/>
+      <c r="J299" t="inlineStr"/>
+      <c r="K299" t="inlineStr"/>
+      <c r="L299" t="inlineStr"/>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N299" t="inlineStr"/>
       <c r="P299" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S om, Dlr</t>
         </is>
       </c>
       <c r="Q299" t="n">
-        <v>443864</v>
+        <v>443272</v>
       </c>
       <c r="R299" t="n">
-        <v>6766958</v>
+        <v>6767198</v>
       </c>
       <c r="S299" t="n">
         <v>10</v>
@@ -31131,34 +31125,40 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AC299" t="inlineStr">
+        <is>
+          <t>På 3 rakor</t>
+        </is>
+      </c>
       <c r="AD299" t="b">
         <v>0</v>
       </c>
       <c r="AE299" t="b">
         <v>0</v>
       </c>
+      <c r="AF299" t="inlineStr"/>
       <c r="AG299" t="b">
         <v>0</v>
       </c>
       <c r="AT299" t="inlineStr"/>
       <c r="AW299" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX299" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>127723386</v>
+        <v>127723045</v>
       </c>
       <c r="B300" t="n">
-        <v>79032</v>
+        <v>78791</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -31166,21 +31166,21 @@
         </is>
       </c>
       <c r="E300" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I300" t="inlineStr"/>
@@ -31190,10 +31190,10 @@
         </is>
       </c>
       <c r="Q300" t="n">
-        <v>443737</v>
+        <v>443582</v>
       </c>
       <c r="R300" t="n">
-        <v>6767119</v>
+        <v>6767183</v>
       </c>
       <c r="S300" t="n">
         <v>10</v>
@@ -35936,7 +35936,7 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>127723313</v>
+        <v>127723333</v>
       </c>
       <c r="B348" t="n">
         <v>79032</v>
@@ -35971,10 +35971,10 @@
         </is>
       </c>
       <c r="Q348" t="n">
-        <v>443612</v>
+        <v>443690</v>
       </c>
       <c r="R348" t="n">
-        <v>6767149</v>
+        <v>6767074</v>
       </c>
       <c r="S348" t="n">
         <v>10</v>
@@ -36033,7 +36033,7 @@
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>127723553</v>
+        <v>127723211</v>
       </c>
       <c r="B349" t="n">
         <v>79032</v>
@@ -36068,10 +36068,10 @@
         </is>
       </c>
       <c r="Q349" t="n">
-        <v>443748</v>
+        <v>443486</v>
       </c>
       <c r="R349" t="n">
-        <v>6767154</v>
+        <v>6766965</v>
       </c>
       <c r="S349" t="n">
         <v>10</v>
@@ -36130,7 +36130,7 @@
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>127723258</v>
+        <v>127723313</v>
       </c>
       <c r="B350" t="n">
         <v>79032</v>
@@ -36165,10 +36165,10 @@
         </is>
       </c>
       <c r="Q350" t="n">
-        <v>443306</v>
+        <v>443612</v>
       </c>
       <c r="R350" t="n">
-        <v>6767334</v>
+        <v>6767149</v>
       </c>
       <c r="S350" t="n">
         <v>10</v>
@@ -36227,10 +36227,10 @@
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>127722812</v>
+        <v>127723553</v>
       </c>
       <c r="B351" t="n">
-        <v>79650</v>
+        <v>79032</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -36238,21 +36238,21 @@
         </is>
       </c>
       <c r="E351" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I351" t="inlineStr"/>
@@ -36262,10 +36262,10 @@
         </is>
       </c>
       <c r="Q351" t="n">
-        <v>443600</v>
+        <v>443748</v>
       </c>
       <c r="R351" t="n">
-        <v>6767125</v>
+        <v>6767154</v>
       </c>
       <c r="S351" t="n">
         <v>10</v>
@@ -36324,7 +36324,7 @@
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>127723328</v>
+        <v>127723258</v>
       </c>
       <c r="B352" t="n">
         <v>79032</v>
@@ -36359,10 +36359,10 @@
         </is>
       </c>
       <c r="Q352" t="n">
-        <v>443653</v>
+        <v>443306</v>
       </c>
       <c r="R352" t="n">
-        <v>6767086</v>
+        <v>6767334</v>
       </c>
       <c r="S352" t="n">
         <v>10</v>
@@ -36421,45 +36421,45 @@
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>127729076</v>
+        <v>127722812</v>
       </c>
       <c r="B353" t="n">
-        <v>92662</v>
+        <v>79650</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E353" t="n">
-        <v>4366</v>
+        <v>6453</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I353" t="inlineStr"/>
       <c r="P353" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q353" t="n">
-        <v>443894</v>
+        <v>443600</v>
       </c>
       <c r="R353" t="n">
-        <v>6766720</v>
+        <v>6767125</v>
       </c>
       <c r="S353" t="n">
         <v>10</v>
@@ -36489,96 +36489,74 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z353" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
       <c r="AA353" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB353" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
       <c r="AD353" t="b">
         <v>0</v>
       </c>
       <c r="AE353" t="b">
         <v>0</v>
       </c>
-      <c r="AF353" t="inlineStr"/>
       <c r="AG353" t="b">
         <v>0</v>
       </c>
       <c r="AT353" t="inlineStr"/>
       <c r="AW353" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX353" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>127730396</v>
+        <v>127723328</v>
       </c>
       <c r="B354" t="n">
-        <v>92650</v>
+        <v>79032</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E354" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I354" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J354" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K354" t="inlineStr"/>
-      <c r="N354" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr"/>
       <c r="P354" t="inlineStr">
         <is>
-          <t>Oxeråsen S om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q354" t="n">
-        <v>443376</v>
+        <v>443653</v>
       </c>
       <c r="R354" t="n">
-        <v>6767009</v>
+        <v>6767086</v>
       </c>
       <c r="S354" t="n">
         <v>10</v>
@@ -36619,69 +36597,71 @@
       <c r="AE354" t="b">
         <v>0</v>
       </c>
-      <c r="AF354" t="inlineStr"/>
       <c r="AG354" t="b">
         <v>0</v>
       </c>
       <c r="AT354" t="inlineStr"/>
       <c r="AW354" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX354" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>127722961</v>
+        <v>127730270</v>
       </c>
       <c r="B355" t="n">
-        <v>8450</v>
+        <v>57673</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E355" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I355" t="inlineStr"/>
+      <c r="K355" t="inlineStr"/>
+      <c r="L355" t="inlineStr"/>
       <c r="M355" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N355" t="inlineStr"/>
       <c r="P355" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S om, Dlr</t>
         </is>
       </c>
       <c r="Q355" t="n">
-        <v>443402</v>
+        <v>443273</v>
       </c>
       <c r="R355" t="n">
-        <v>6767070</v>
+        <v>6767233</v>
       </c>
       <c r="S355" t="n">
         <v>10</v>
@@ -36716,6 +36696,11 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AC355" t="inlineStr">
+        <is>
+          <t>Ringhack gamla</t>
+        </is>
+      </c>
       <c r="AD355" t="b">
         <v>0</v>
       </c>
@@ -36728,19 +36713,19 @@
       <c r="AT355" t="inlineStr"/>
       <c r="AW355" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX355" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>127722962</v>
+        <v>127722961</v>
       </c>
       <c r="B356" t="n">
         <v>8450</v>
@@ -36780,10 +36765,10 @@
         </is>
       </c>
       <c r="Q356" t="n">
-        <v>443365</v>
+        <v>443402</v>
       </c>
       <c r="R356" t="n">
-        <v>6767049</v>
+        <v>6767070</v>
       </c>
       <c r="S356" t="n">
         <v>10</v>
@@ -36842,45 +36827,50 @@
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>127723333</v>
+        <v>127722962</v>
       </c>
       <c r="B357" t="n">
-        <v>79032</v>
+        <v>8450</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E357" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I357" t="inlineStr"/>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P357" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q357" t="n">
-        <v>443690</v>
+        <v>443365</v>
       </c>
       <c r="R357" t="n">
-        <v>6767074</v>
+        <v>6767049</v>
       </c>
       <c r="S357" t="n">
         <v>10</v>
@@ -36939,45 +36929,45 @@
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>127723211</v>
+        <v>127729076</v>
       </c>
       <c r="B358" t="n">
-        <v>79032</v>
+        <v>92662</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E358" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I358" t="inlineStr"/>
       <c r="P358" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q358" t="n">
-        <v>443486</v>
+        <v>443894</v>
       </c>
       <c r="R358" t="n">
-        <v>6766965</v>
+        <v>6766720</v>
       </c>
       <c r="S358" t="n">
         <v>10</v>
@@ -37007,71 +36997,85 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z358" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
       <c r="AA358" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB358" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
       <c r="AD358" t="b">
         <v>0</v>
       </c>
       <c r="AE358" t="b">
         <v>0</v>
       </c>
+      <c r="AF358" t="inlineStr"/>
       <c r="AG358" t="b">
         <v>0</v>
       </c>
       <c r="AT358" t="inlineStr"/>
       <c r="AW358" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX358" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>127730270</v>
+        <v>127730396</v>
       </c>
       <c r="B359" t="n">
-        <v>57673</v>
+        <v>92650</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E359" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I359" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K359" t="inlineStr"/>
-      <c r="L359" t="inlineStr"/>
-      <c r="M359" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N359" t="inlineStr"/>
       <c r="P359" t="inlineStr">
         <is>
@@ -37079,10 +37083,10 @@
         </is>
       </c>
       <c r="Q359" t="n">
-        <v>443273</v>
+        <v>443376</v>
       </c>
       <c r="R359" t="n">
-        <v>6767233</v>
+        <v>6767009</v>
       </c>
       <c r="S359" t="n">
         <v>10</v>
@@ -37117,17 +37121,13 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC359" t="inlineStr">
-        <is>
-          <t>Ringhack gamla</t>
-        </is>
-      </c>
       <c r="AD359" t="b">
         <v>0</v>
       </c>
       <c r="AE359" t="b">
         <v>0</v>
       </c>
+      <c r="AF359" t="inlineStr"/>
       <c r="AG359" t="b">
         <v>0</v>
       </c>
@@ -39947,45 +39947,54 @@
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>127723353</v>
+        <v>127729089</v>
       </c>
       <c r="B388" t="n">
-        <v>79032</v>
+        <v>8450</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E388" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I388" t="inlineStr"/>
+      <c r="J388" t="inlineStr"/>
+      <c r="K388" t="inlineStr"/>
+      <c r="L388" t="inlineStr"/>
+      <c r="M388" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N388" t="inlineStr"/>
       <c r="P388" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q388" t="n">
-        <v>443860</v>
+        <v>443908</v>
       </c>
       <c r="R388" t="n">
-        <v>6766958</v>
+        <v>6766751</v>
       </c>
       <c r="S388" t="n">
         <v>10</v>
@@ -40015,74 +40024,90 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z388" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
       <c r="AA388" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB388" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
       <c r="AD388" t="b">
         <v>0</v>
       </c>
       <c r="AE388" t="b">
         <v>0</v>
       </c>
+      <c r="AF388" t="inlineStr"/>
       <c r="AG388" t="b">
         <v>0</v>
       </c>
       <c r="AT388" t="inlineStr"/>
       <c r="AW388" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX388" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>127729107</v>
+        <v>127722967</v>
       </c>
       <c r="B389" t="n">
-        <v>79032</v>
+        <v>8450</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E389" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I389" t="inlineStr"/>
+      <c r="M389" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P389" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q389" t="n">
-        <v>443847</v>
+        <v>443274</v>
       </c>
       <c r="R389" t="n">
-        <v>6766880</v>
+        <v>6767205</v>
       </c>
       <c r="S389" t="n">
         <v>10</v>
@@ -40112,47 +40137,36 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z389" t="inlineStr">
-        <is>
-          <t>16:42</t>
-        </is>
-      </c>
       <c r="AA389" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB389" t="inlineStr">
-        <is>
-          <t>16:42</t>
-        </is>
-      </c>
       <c r="AD389" t="b">
         <v>0</v>
       </c>
       <c r="AE389" t="b">
         <v>0</v>
       </c>
-      <c r="AF389" t="inlineStr"/>
       <c r="AG389" t="b">
         <v>0</v>
       </c>
       <c r="AT389" t="inlineStr"/>
       <c r="AW389" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX389" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>127723379</v>
+        <v>127723353</v>
       </c>
       <c r="B390" t="n">
         <v>79032</v>
@@ -40187,10 +40201,10 @@
         </is>
       </c>
       <c r="Q390" t="n">
-        <v>443820</v>
+        <v>443860</v>
       </c>
       <c r="R390" t="n">
-        <v>6767075</v>
+        <v>6766958</v>
       </c>
       <c r="S390" t="n">
         <v>10</v>
@@ -40249,7 +40263,7 @@
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>127723332</v>
+        <v>127729107</v>
       </c>
       <c r="B391" t="n">
         <v>79032</v>
@@ -40280,14 +40294,14 @@
       <c r="I391" t="inlineStr"/>
       <c r="P391" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q391" t="n">
-        <v>443690</v>
+        <v>443847</v>
       </c>
       <c r="R391" t="n">
-        <v>6767067</v>
+        <v>6766880</v>
       </c>
       <c r="S391" t="n">
         <v>10</v>
@@ -40317,36 +40331,47 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z391" t="inlineStr">
+        <is>
+          <t>16:42</t>
+        </is>
+      </c>
       <c r="AA391" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB391" t="inlineStr">
+        <is>
+          <t>16:42</t>
+        </is>
+      </c>
       <c r="AD391" t="b">
         <v>0</v>
       </c>
       <c r="AE391" t="b">
         <v>0</v>
       </c>
+      <c r="AF391" t="inlineStr"/>
       <c r="AG391" t="b">
         <v>0</v>
       </c>
       <c r="AT391" t="inlineStr"/>
       <c r="AW391" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX391" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>127723341</v>
+        <v>127723379</v>
       </c>
       <c r="B392" t="n">
         <v>79032</v>
@@ -40381,10 +40406,10 @@
         </is>
       </c>
       <c r="Q392" t="n">
-        <v>443695</v>
+        <v>443820</v>
       </c>
       <c r="R392" t="n">
-        <v>6766960</v>
+        <v>6767075</v>
       </c>
       <c r="S392" t="n">
         <v>10</v>
@@ -40443,10 +40468,10 @@
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>127729144</v>
+        <v>127723332</v>
       </c>
       <c r="B393" t="n">
-        <v>92644</v>
+        <v>79032</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -40454,45 +40479,34 @@
         </is>
       </c>
       <c r="E393" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I393" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J393" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K393" t="inlineStr"/>
-      <c r="N393" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr"/>
       <c r="P393" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q393" t="n">
-        <v>443900</v>
+        <v>443690</v>
       </c>
       <c r="R393" t="n">
-        <v>6766718</v>
+        <v>6767067</v>
       </c>
       <c r="S393" t="n">
         <v>10</v>
@@ -40522,50 +40536,39 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z393" t="inlineStr">
-        <is>
-          <t>16:17</t>
-        </is>
-      </c>
       <c r="AA393" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB393" t="inlineStr">
-        <is>
-          <t>16:17</t>
-        </is>
-      </c>
       <c r="AD393" t="b">
         <v>0</v>
       </c>
       <c r="AE393" t="b">
         <v>0</v>
       </c>
-      <c r="AF393" t="inlineStr"/>
       <c r="AG393" t="b">
         <v>0</v>
       </c>
       <c r="AT393" t="inlineStr"/>
       <c r="AW393" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX393" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>127722818</v>
+        <v>127723341</v>
       </c>
       <c r="B394" t="n">
-        <v>79650</v>
+        <v>79032</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -40573,21 +40576,21 @@
         </is>
       </c>
       <c r="E394" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I394" t="inlineStr"/>
@@ -40597,10 +40600,10 @@
         </is>
       </c>
       <c r="Q394" t="n">
-        <v>443606</v>
+        <v>443695</v>
       </c>
       <c r="R394" t="n">
-        <v>6767114</v>
+        <v>6766960</v>
       </c>
       <c r="S394" t="n">
         <v>10</v>
@@ -40659,54 +40662,45 @@
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>127729089</v>
+        <v>127722818</v>
       </c>
       <c r="B395" t="n">
-        <v>8450</v>
+        <v>79650</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E395" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I395" t="inlineStr"/>
-      <c r="J395" t="inlineStr"/>
-      <c r="K395" t="inlineStr"/>
-      <c r="L395" t="inlineStr"/>
-      <c r="M395" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N395" t="inlineStr"/>
       <c r="P395" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q395" t="n">
-        <v>443908</v>
+        <v>443606</v>
       </c>
       <c r="R395" t="n">
-        <v>6766751</v>
+        <v>6767114</v>
       </c>
       <c r="S395" t="n">
         <v>10</v>
@@ -40736,90 +40730,74 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z395" t="inlineStr">
-        <is>
-          <t>16:26</t>
-        </is>
-      </c>
       <c r="AA395" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB395" t="inlineStr">
-        <is>
-          <t>16:26</t>
-        </is>
-      </c>
       <c r="AD395" t="b">
         <v>0</v>
       </c>
       <c r="AE395" t="b">
         <v>0</v>
       </c>
-      <c r="AF395" t="inlineStr"/>
       <c r="AG395" t="b">
         <v>0</v>
       </c>
       <c r="AT395" t="inlineStr"/>
       <c r="AW395" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX395" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>127722967</v>
+        <v>127722905</v>
       </c>
       <c r="B396" t="n">
-        <v>8450</v>
+        <v>57673</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E396" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I396" t="inlineStr"/>
-      <c r="M396" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P396" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q396" t="n">
-        <v>443274</v>
+        <v>443743</v>
       </c>
       <c r="R396" t="n">
-        <v>6767205</v>
+        <v>6767161</v>
       </c>
       <c r="S396" t="n">
         <v>10</v>
@@ -40852,6 +40830,11 @@
       <c r="AA396" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC396" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD396" t="b">
@@ -40878,10 +40861,10 @@
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>127722905</v>
+        <v>127722854</v>
       </c>
       <c r="B397" t="n">
-        <v>57673</v>
+        <v>79621</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -40889,21 +40872,21 @@
         </is>
       </c>
       <c r="E397" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I397" t="inlineStr"/>
@@ -40913,10 +40896,10 @@
         </is>
       </c>
       <c r="Q397" t="n">
-        <v>443743</v>
+        <v>443682</v>
       </c>
       <c r="R397" t="n">
-        <v>6767161</v>
+        <v>6766771</v>
       </c>
       <c r="S397" t="n">
         <v>10</v>
@@ -40953,7 +40936,7 @@
       </c>
       <c r="AC397" t="inlineStr">
         <is>
-          <t>Äldre ringhack (tall)</t>
+          <t>På naturlig högstubbe av "skorstenskaraktär"</t>
         </is>
       </c>
       <c r="AD397" t="b">
@@ -40980,10 +40963,10 @@
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>127722854</v>
+        <v>127723285</v>
       </c>
       <c r="B398" t="n">
-        <v>79621</v>
+        <v>79032</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -40991,21 +40974,21 @@
         </is>
       </c>
       <c r="E398" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I398" t="inlineStr"/>
@@ -41015,10 +40998,10 @@
         </is>
       </c>
       <c r="Q398" t="n">
-        <v>443682</v>
+        <v>443311</v>
       </c>
       <c r="R398" t="n">
-        <v>6766771</v>
+        <v>6767434</v>
       </c>
       <c r="S398" t="n">
         <v>10</v>
@@ -41051,11 +41034,6 @@
       <c r="AA398" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC398" t="inlineStr">
-        <is>
-          <t>På naturlig högstubbe av "skorstenskaraktär"</t>
         </is>
       </c>
       <c r="AD398" t="b">
@@ -41082,7 +41060,7 @@
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>127723285</v>
+        <v>127723346</v>
       </c>
       <c r="B399" t="n">
         <v>79032</v>
@@ -41117,10 +41095,10 @@
         </is>
       </c>
       <c r="Q399" t="n">
-        <v>443311</v>
+        <v>443773</v>
       </c>
       <c r="R399" t="n">
-        <v>6767434</v>
+        <v>6766946</v>
       </c>
       <c r="S399" t="n">
         <v>10</v>
@@ -41179,7 +41157,7 @@
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>127723346</v>
+        <v>127729132</v>
       </c>
       <c r="B400" t="n">
         <v>79032</v>
@@ -41210,14 +41188,14 @@
       <c r="I400" t="inlineStr"/>
       <c r="P400" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q400" t="n">
-        <v>443773</v>
+        <v>443918</v>
       </c>
       <c r="R400" t="n">
-        <v>6766946</v>
+        <v>6766588</v>
       </c>
       <c r="S400" t="n">
         <v>10</v>
@@ -41247,36 +41225,47 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z400" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
       <c r="AA400" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB400" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
       <c r="AD400" t="b">
         <v>0</v>
       </c>
       <c r="AE400" t="b">
         <v>0</v>
       </c>
+      <c r="AF400" t="inlineStr"/>
       <c r="AG400" t="b">
         <v>0</v>
       </c>
       <c r="AT400" t="inlineStr"/>
       <c r="AW400" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX400" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>127729132</v>
+        <v>127723082</v>
       </c>
       <c r="B401" t="n">
         <v>79032</v>
@@ -41307,14 +41296,14 @@
       <c r="I401" t="inlineStr"/>
       <c r="P401" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q401" t="n">
-        <v>443918</v>
+        <v>443674</v>
       </c>
       <c r="R401" t="n">
-        <v>6766588</v>
+        <v>6766780</v>
       </c>
       <c r="S401" t="n">
         <v>10</v>
@@ -41344,47 +41333,36 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z401" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
       <c r="AA401" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB401" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
       <c r="AD401" t="b">
         <v>0</v>
       </c>
       <c r="AE401" t="b">
         <v>0</v>
       </c>
-      <c r="AF401" t="inlineStr"/>
       <c r="AG401" t="b">
         <v>0</v>
       </c>
       <c r="AT401" t="inlineStr"/>
       <c r="AW401" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX401" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>127723082</v>
+        <v>127723087</v>
       </c>
       <c r="B402" t="n">
         <v>79032</v>
@@ -41419,10 +41397,10 @@
         </is>
       </c>
       <c r="Q402" t="n">
-        <v>443674</v>
+        <v>443713</v>
       </c>
       <c r="R402" t="n">
-        <v>6766780</v>
+        <v>6766723</v>
       </c>
       <c r="S402" t="n">
         <v>10</v>
@@ -41481,7 +41459,7 @@
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>127723087</v>
+        <v>127723283</v>
       </c>
       <c r="B403" t="n">
         <v>79032</v>
@@ -41516,10 +41494,10 @@
         </is>
       </c>
       <c r="Q403" t="n">
-        <v>443713</v>
+        <v>443290</v>
       </c>
       <c r="R403" t="n">
-        <v>6766723</v>
+        <v>6767430</v>
       </c>
       <c r="S403" t="n">
         <v>10</v>
@@ -41578,7 +41556,7 @@
     </row>
     <row r="404">
       <c r="A404" t="n">
-        <v>127723283</v>
+        <v>127723218</v>
       </c>
       <c r="B404" t="n">
         <v>79032</v>
@@ -41613,10 +41591,10 @@
         </is>
       </c>
       <c r="Q404" t="n">
-        <v>443290</v>
+        <v>443425</v>
       </c>
       <c r="R404" t="n">
-        <v>6767430</v>
+        <v>6767031</v>
       </c>
       <c r="S404" t="n">
         <v>10</v>
@@ -41675,10 +41653,10 @@
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>127723218</v>
+        <v>127729144</v>
       </c>
       <c r="B405" t="n">
-        <v>79032</v>
+        <v>92644</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -41686,34 +41664,45 @@
         </is>
       </c>
       <c r="E405" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I405" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J405" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K405" t="inlineStr"/>
+      <c r="N405" t="inlineStr"/>
       <c r="P405" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q405" t="n">
-        <v>443425</v>
+        <v>443900</v>
       </c>
       <c r="R405" t="n">
-        <v>6767031</v>
+        <v>6766718</v>
       </c>
       <c r="S405" t="n">
         <v>10</v>
@@ -41743,29 +41732,40 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z405" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
       <c r="AA405" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB405" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
       <c r="AD405" t="b">
         <v>0</v>
       </c>
       <c r="AE405" t="b">
         <v>0</v>
       </c>
+      <c r="AF405" t="inlineStr"/>
       <c r="AG405" t="b">
         <v>0</v>
       </c>
       <c r="AT405" t="inlineStr"/>
       <c r="AW405" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX405" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY405" t="inlineStr"/>
@@ -42569,7 +42569,7 @@
     </row>
     <row r="414">
       <c r="A414" t="n">
-        <v>127723364</v>
+        <v>127723294</v>
       </c>
       <c r="B414" t="n">
         <v>79032</v>
@@ -42604,10 +42604,10 @@
         </is>
       </c>
       <c r="Q414" t="n">
-        <v>443902</v>
+        <v>443362</v>
       </c>
       <c r="R414" t="n">
-        <v>6766957</v>
+        <v>6767353</v>
       </c>
       <c r="S414" t="n">
         <v>10</v>
@@ -42666,7 +42666,7 @@
     </row>
     <row r="415">
       <c r="A415" t="n">
-        <v>127729114</v>
+        <v>127730308</v>
       </c>
       <c r="B415" t="n">
         <v>79032</v>
@@ -42695,16 +42695,19 @@
         </is>
       </c>
       <c r="I415" t="inlineStr"/>
+      <c r="J415" t="inlineStr"/>
+      <c r="K415" t="inlineStr"/>
+      <c r="N415" t="inlineStr"/>
       <c r="P415" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen S om, Dlr</t>
         </is>
       </c>
       <c r="Q415" t="n">
-        <v>443901</v>
+        <v>443272</v>
       </c>
       <c r="R415" t="n">
-        <v>6766792</v>
+        <v>6767198</v>
       </c>
       <c r="S415" t="n">
         <v>10</v>
@@ -42734,19 +42737,9 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z415" t="inlineStr">
-        <is>
-          <t>16:33</t>
-        </is>
-      </c>
       <c r="AA415" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AB415" t="inlineStr">
-        <is>
-          <t>16:33</t>
         </is>
       </c>
       <c r="AD415" t="b">
@@ -42774,7 +42767,7 @@
     </row>
     <row r="416">
       <c r="A416" t="n">
-        <v>127723072</v>
+        <v>127723397</v>
       </c>
       <c r="B416" t="n">
         <v>79032</v>
@@ -42809,10 +42802,10 @@
         </is>
       </c>
       <c r="Q416" t="n">
-        <v>443402</v>
+        <v>443645</v>
       </c>
       <c r="R416" t="n">
-        <v>6767406</v>
+        <v>6767178</v>
       </c>
       <c r="S416" t="n">
         <v>10</v>
@@ -42871,7 +42864,7 @@
     </row>
     <row r="417">
       <c r="A417" t="n">
-        <v>127723086</v>
+        <v>127723232</v>
       </c>
       <c r="B417" t="n">
         <v>79032</v>
@@ -42906,10 +42899,10 @@
         </is>
       </c>
       <c r="Q417" t="n">
-        <v>443721</v>
+        <v>443320</v>
       </c>
       <c r="R417" t="n">
-        <v>6766733</v>
+        <v>6767074</v>
       </c>
       <c r="S417" t="n">
         <v>10</v>
@@ -42968,7 +42961,7 @@
     </row>
     <row r="418">
       <c r="A418" t="n">
-        <v>127723223</v>
+        <v>127723233</v>
       </c>
       <c r="B418" t="n">
         <v>79032</v>
@@ -43003,10 +42996,10 @@
         </is>
       </c>
       <c r="Q418" t="n">
-        <v>443427</v>
+        <v>443339</v>
       </c>
       <c r="R418" t="n">
-        <v>6767066</v>
+        <v>6767096</v>
       </c>
       <c r="S418" t="n">
         <v>10</v>
@@ -43065,10 +43058,10 @@
     </row>
     <row r="419">
       <c r="A419" t="n">
-        <v>127723247</v>
+        <v>127729091</v>
       </c>
       <c r="B419" t="n">
-        <v>79032</v>
+        <v>78790</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -43076,34 +43069,34 @@
         </is>
       </c>
       <c r="E419" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I419" t="inlineStr"/>
       <c r="P419" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q419" t="n">
-        <v>443291</v>
+        <v>443605</v>
       </c>
       <c r="R419" t="n">
-        <v>6767272</v>
+        <v>6767136</v>
       </c>
       <c r="S419" t="n">
         <v>10</v>
@@ -43133,39 +43126,50 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z419" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
       <c r="AA419" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB419" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
       <c r="AD419" t="b">
         <v>0</v>
       </c>
       <c r="AE419" t="b">
         <v>0</v>
       </c>
+      <c r="AF419" t="inlineStr"/>
       <c r="AG419" t="b">
         <v>0</v>
       </c>
       <c r="AT419" t="inlineStr"/>
       <c r="AW419" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX419" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" t="n">
-        <v>127723055</v>
+        <v>127723365</v>
       </c>
       <c r="B420" t="n">
-        <v>81007</v>
+        <v>79032</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -43173,21 +43177,21 @@
         </is>
       </c>
       <c r="E420" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I420" t="inlineStr"/>
@@ -43197,10 +43201,10 @@
         </is>
       </c>
       <c r="Q420" t="n">
-        <v>443583</v>
+        <v>443894</v>
       </c>
       <c r="R420" t="n">
-        <v>6767185</v>
+        <v>6766978</v>
       </c>
       <c r="S420" t="n">
         <v>10</v>
@@ -43259,32 +43263,32 @@
     </row>
     <row r="421">
       <c r="A421" t="n">
-        <v>127723066</v>
+        <v>127723077</v>
       </c>
       <c r="B421" t="n">
-        <v>91521</v>
+        <v>79032</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E421" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I421" t="inlineStr"/>
@@ -43294,10 +43298,10 @@
         </is>
       </c>
       <c r="Q421" t="n">
-        <v>443271</v>
+        <v>443405</v>
       </c>
       <c r="R421" t="n">
-        <v>6767289</v>
+        <v>6767010</v>
       </c>
       <c r="S421" t="n">
         <v>10</v>
@@ -43356,7 +43360,7 @@
     </row>
     <row r="422">
       <c r="A422" t="n">
-        <v>127723294</v>
+        <v>127723351</v>
       </c>
       <c r="B422" t="n">
         <v>79032</v>
@@ -43391,10 +43395,10 @@
         </is>
       </c>
       <c r="Q422" t="n">
-        <v>443362</v>
+        <v>443843</v>
       </c>
       <c r="R422" t="n">
-        <v>6767353</v>
+        <v>6766950</v>
       </c>
       <c r="S422" t="n">
         <v>10</v>
@@ -43453,37 +43457,43 @@
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>127730308</v>
+        <v>127730365</v>
       </c>
       <c r="B423" t="n">
-        <v>79032</v>
+        <v>8450</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E423" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I423" t="inlineStr"/>
       <c r="J423" t="inlineStr"/>
       <c r="K423" t="inlineStr"/>
+      <c r="L423" t="inlineStr"/>
+      <c r="M423" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N423" t="inlineStr"/>
       <c r="P423" t="inlineStr">
         <is>
@@ -43491,10 +43501,10 @@
         </is>
       </c>
       <c r="Q423" t="n">
-        <v>443272</v>
+        <v>443316</v>
       </c>
       <c r="R423" t="n">
-        <v>6767198</v>
+        <v>6767119</v>
       </c>
       <c r="S423" t="n">
         <v>10</v>
@@ -43554,45 +43564,50 @@
     </row>
     <row r="424">
       <c r="A424" t="n">
-        <v>127723397</v>
+        <v>127722804</v>
       </c>
       <c r="B424" t="n">
-        <v>79032</v>
+        <v>5197</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E424" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I424" t="inlineStr"/>
+      <c r="M424" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P424" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q424" t="n">
-        <v>443645</v>
+        <v>443955</v>
       </c>
       <c r="R424" t="n">
-        <v>6767178</v>
+        <v>6766920</v>
       </c>
       <c r="S424" t="n">
         <v>10</v>
@@ -43651,45 +43666,50 @@
     </row>
     <row r="425">
       <c r="A425" t="n">
-        <v>127723232</v>
+        <v>127722973</v>
       </c>
       <c r="B425" t="n">
-        <v>79032</v>
+        <v>8450</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E425" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I425" t="inlineStr"/>
+      <c r="M425" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P425" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q425" t="n">
-        <v>443320</v>
+        <v>443316</v>
       </c>
       <c r="R425" t="n">
-        <v>6767074</v>
+        <v>6767406</v>
       </c>
       <c r="S425" t="n">
         <v>10</v>
@@ -43748,45 +43768,50 @@
     </row>
     <row r="426">
       <c r="A426" t="n">
-        <v>127723233</v>
+        <v>127723001</v>
       </c>
       <c r="B426" t="n">
-        <v>79032</v>
+        <v>8450</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E426" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I426" t="inlineStr"/>
+      <c r="M426" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P426" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q426" t="n">
-        <v>443339</v>
+        <v>443849</v>
       </c>
       <c r="R426" t="n">
-        <v>6767096</v>
+        <v>6766983</v>
       </c>
       <c r="S426" t="n">
         <v>10</v>
@@ -43845,10 +43870,10 @@
     </row>
     <row r="427">
       <c r="A427" t="n">
-        <v>127729091</v>
+        <v>127723364</v>
       </c>
       <c r="B427" t="n">
-        <v>78790</v>
+        <v>79032</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -43856,34 +43881,34 @@
         </is>
       </c>
       <c r="E427" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I427" t="inlineStr"/>
       <c r="P427" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q427" t="n">
-        <v>443605</v>
+        <v>443902</v>
       </c>
       <c r="R427" t="n">
-        <v>6767136</v>
+        <v>6766957</v>
       </c>
       <c r="S427" t="n">
         <v>10</v>
@@ -43913,47 +43938,36 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z427" t="inlineStr">
-        <is>
-          <t>17:07</t>
-        </is>
-      </c>
       <c r="AA427" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB427" t="inlineStr">
-        <is>
-          <t>17:07</t>
-        </is>
-      </c>
       <c r="AD427" t="b">
         <v>0</v>
       </c>
       <c r="AE427" t="b">
         <v>0</v>
       </c>
-      <c r="AF427" t="inlineStr"/>
       <c r="AG427" t="b">
         <v>0</v>
       </c>
       <c r="AT427" t="inlineStr"/>
       <c r="AW427" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX427" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY427" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" t="n">
-        <v>127723365</v>
+        <v>127729114</v>
       </c>
       <c r="B428" t="n">
         <v>79032</v>
@@ -43984,14 +43998,14 @@
       <c r="I428" t="inlineStr"/>
       <c r="P428" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q428" t="n">
-        <v>443894</v>
+        <v>443901</v>
       </c>
       <c r="R428" t="n">
-        <v>6766978</v>
+        <v>6766792</v>
       </c>
       <c r="S428" t="n">
         <v>10</v>
@@ -44021,36 +44035,47 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z428" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
       <c r="AA428" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB428" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
       <c r="AD428" t="b">
         <v>0</v>
       </c>
       <c r="AE428" t="b">
         <v>0</v>
       </c>
+      <c r="AF428" t="inlineStr"/>
       <c r="AG428" t="b">
         <v>0</v>
       </c>
       <c r="AT428" t="inlineStr"/>
       <c r="AW428" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX428" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY428" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" t="n">
-        <v>127723077</v>
+        <v>127723072</v>
       </c>
       <c r="B429" t="n">
         <v>79032</v>
@@ -44085,10 +44110,10 @@
         </is>
       </c>
       <c r="Q429" t="n">
-        <v>443405</v>
+        <v>443402</v>
       </c>
       <c r="R429" t="n">
-        <v>6767010</v>
+        <v>6767406</v>
       </c>
       <c r="S429" t="n">
         <v>10</v>
@@ -44147,7 +44172,7 @@
     </row>
     <row r="430">
       <c r="A430" t="n">
-        <v>127723351</v>
+        <v>127723086</v>
       </c>
       <c r="B430" t="n">
         <v>79032</v>
@@ -44182,10 +44207,10 @@
         </is>
       </c>
       <c r="Q430" t="n">
-        <v>443843</v>
+        <v>443721</v>
       </c>
       <c r="R430" t="n">
-        <v>6766950</v>
+        <v>6766733</v>
       </c>
       <c r="S430" t="n">
         <v>10</v>
@@ -44244,54 +44269,45 @@
     </row>
     <row r="431">
       <c r="A431" t="n">
-        <v>127730365</v>
+        <v>127723223</v>
       </c>
       <c r="B431" t="n">
-        <v>8450</v>
+        <v>79032</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E431" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I431" t="inlineStr"/>
-      <c r="J431" t="inlineStr"/>
-      <c r="K431" t="inlineStr"/>
-      <c r="L431" t="inlineStr"/>
-      <c r="M431" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N431" t="inlineStr"/>
       <c r="P431" t="inlineStr">
         <is>
-          <t>Oxeråsen S om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q431" t="n">
-        <v>443316</v>
+        <v>443427</v>
       </c>
       <c r="R431" t="n">
-        <v>6767119</v>
+        <v>6767066</v>
       </c>
       <c r="S431" t="n">
         <v>10</v>
@@ -44332,69 +44348,63 @@
       <c r="AE431" t="b">
         <v>0</v>
       </c>
-      <c r="AF431" t="inlineStr"/>
       <c r="AG431" t="b">
         <v>0</v>
       </c>
       <c r="AT431" t="inlineStr"/>
       <c r="AW431" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX431" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY431" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" t="n">
-        <v>127722804</v>
+        <v>127723247</v>
       </c>
       <c r="B432" t="n">
-        <v>5197</v>
+        <v>79032</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E432" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I432" t="inlineStr"/>
-      <c r="M432" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P432" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q432" t="n">
-        <v>443955</v>
+        <v>443291</v>
       </c>
       <c r="R432" t="n">
-        <v>6766920</v>
+        <v>6767272</v>
       </c>
       <c r="S432" t="n">
         <v>10</v>
@@ -44453,50 +44463,45 @@
     </row>
     <row r="433">
       <c r="A433" t="n">
-        <v>127722973</v>
+        <v>127723055</v>
       </c>
       <c r="B433" t="n">
-        <v>8450</v>
+        <v>81007</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E433" t="n">
-        <v>106545</v>
+        <v>1049</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I433" t="inlineStr"/>
-      <c r="M433" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P433" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q433" t="n">
-        <v>443316</v>
+        <v>443583</v>
       </c>
       <c r="R433" t="n">
-        <v>6767406</v>
+        <v>6767185</v>
       </c>
       <c r="S433" t="n">
         <v>10</v>
@@ -44555,50 +44560,45 @@
     </row>
     <row r="434">
       <c r="A434" t="n">
-        <v>127723001</v>
+        <v>127723066</v>
       </c>
       <c r="B434" t="n">
-        <v>8450</v>
+        <v>91521</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E434" t="n">
-        <v>106545</v>
+        <v>1503</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I434" t="inlineStr"/>
-      <c r="M434" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P434" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q434" t="n">
-        <v>443849</v>
+        <v>443271</v>
       </c>
       <c r="R434" t="n">
-        <v>6766983</v>
+        <v>6767289</v>
       </c>
       <c r="S434" t="n">
         <v>10</v>
@@ -49108,32 +49108,32 @@
     </row>
     <row r="479">
       <c r="A479" t="n">
-        <v>127736008</v>
+        <v>127736016</v>
       </c>
       <c r="B479" t="n">
-        <v>92662</v>
+        <v>78790</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E479" t="n">
-        <v>4366</v>
+        <v>6446</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G479" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I479" t="inlineStr"/>
@@ -49143,10 +49143,10 @@
         </is>
       </c>
       <c r="Q479" t="n">
-        <v>443321</v>
+        <v>443941</v>
       </c>
       <c r="R479" t="n">
-        <v>6767336</v>
+        <v>6766675</v>
       </c>
       <c r="S479" t="n">
         <v>10</v>
@@ -49178,7 +49178,7 @@
       </c>
       <c r="Z479" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA479" t="inlineStr">
@@ -49188,7 +49188,7 @@
       </c>
       <c r="AB479" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD479" t="b">
@@ -49197,7 +49197,6 @@
       <c r="AE479" t="b">
         <v>0</v>
       </c>
-      <c r="AF479" t="inlineStr"/>
       <c r="AG479" t="b">
         <v>0</v>
       </c>
@@ -49216,32 +49215,32 @@
     </row>
     <row r="480">
       <c r="A480" t="n">
-        <v>127736016</v>
+        <v>127736008</v>
       </c>
       <c r="B480" t="n">
-        <v>78790</v>
+        <v>92662</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E480" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I480" t="inlineStr"/>
@@ -49251,10 +49250,10 @@
         </is>
       </c>
       <c r="Q480" t="n">
-        <v>443941</v>
+        <v>443321</v>
       </c>
       <c r="R480" t="n">
-        <v>6766675</v>
+        <v>6767336</v>
       </c>
       <c r="S480" t="n">
         <v>10</v>
@@ -49286,7 +49285,7 @@
       </c>
       <c r="Z480" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA480" t="inlineStr">
@@ -49296,7 +49295,7 @@
       </c>
       <c r="AB480" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD480" t="b">
@@ -49305,6 +49304,7 @@
       <c r="AE480" t="b">
         <v>0</v>
       </c>
+      <c r="AF480" t="inlineStr"/>
       <c r="AG480" t="b">
         <v>0</v>
       </c>
@@ -50621,10 +50621,10 @@
     </row>
     <row r="493">
       <c r="A493" t="n">
-        <v>127795807</v>
+        <v>127795436</v>
       </c>
       <c r="B493" t="n">
-        <v>88630</v>
+        <v>79032</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -50632,28 +50632,24 @@
         </is>
       </c>
       <c r="E493" t="n">
-        <v>4412</v>
+        <v>6425</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H493" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
-        </is>
-      </c>
-      <c r="I493" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I493" t="inlineStr"/>
       <c r="J493" t="inlineStr"/>
       <c r="K493" t="inlineStr"/>
       <c r="N493" t="inlineStr"/>
@@ -50663,10 +50659,10 @@
         </is>
       </c>
       <c r="Q493" t="n">
-        <v>443370</v>
+        <v>443900</v>
       </c>
       <c r="R493" t="n">
-        <v>6767363</v>
+        <v>6766619</v>
       </c>
       <c r="S493" t="n">
         <v>50</v>
@@ -50726,10 +50722,10 @@
     </row>
     <row r="494">
       <c r="A494" t="n">
-        <v>127795436</v>
+        <v>127795451</v>
       </c>
       <c r="B494" t="n">
-        <v>79032</v>
+        <v>78790</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -50737,21 +50733,21 @@
         </is>
       </c>
       <c r="E494" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G494" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I494" t="inlineStr"/>
@@ -50764,10 +50760,10 @@
         </is>
       </c>
       <c r="Q494" t="n">
-        <v>443900</v>
+        <v>443863</v>
       </c>
       <c r="R494" t="n">
-        <v>6766619</v>
+        <v>6766645</v>
       </c>
       <c r="S494" t="n">
         <v>50</v>
@@ -50827,10 +50823,10 @@
     </row>
     <row r="495">
       <c r="A495" t="n">
-        <v>127795451</v>
+        <v>127795807</v>
       </c>
       <c r="B495" t="n">
-        <v>78790</v>
+        <v>88630</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -50838,24 +50834,28 @@
         </is>
       </c>
       <c r="E495" t="n">
-        <v>6446</v>
+        <v>4412</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I495" t="inlineStr"/>
+          <t>Sacc. &amp; Cub.</t>
+        </is>
+      </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J495" t="inlineStr"/>
       <c r="K495" t="inlineStr"/>
       <c r="N495" t="inlineStr"/>
@@ -50865,10 +50865,10 @@
         </is>
       </c>
       <c r="Q495" t="n">
-        <v>443863</v>
+        <v>443370</v>
       </c>
       <c r="R495" t="n">
-        <v>6766645</v>
+        <v>6767363</v>
       </c>
       <c r="S495" t="n">
         <v>50</v>

--- a/artfynd/A 35482-2025 artfynd.xlsx
+++ b/artfynd/A 35482-2025 artfynd.xlsx
@@ -49974,10 +49974,10 @@
     </row>
     <row r="487">
       <c r="A487" t="n">
-        <v>127785471</v>
+        <v>127785477</v>
       </c>
       <c r="B487" t="n">
-        <v>91472</v>
+        <v>79083</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -49985,21 +49985,21 @@
         </is>
       </c>
       <c r="E487" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I487" t="inlineStr"/>
@@ -50009,10 +50009,10 @@
         </is>
       </c>
       <c r="Q487" t="n">
-        <v>443867</v>
+        <v>443827</v>
       </c>
       <c r="R487" t="n">
-        <v>6766575</v>
+        <v>6766865</v>
       </c>
       <c r="S487" t="n">
         <v>10</v>
@@ -50044,7 +50044,7 @@
       </c>
       <c r="Z487" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA487" t="inlineStr">
@@ -50054,7 +50054,12 @@
       </c>
       <c r="AB487" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AC487" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD487" t="b">
@@ -50063,6 +50068,7 @@
       <c r="AE487" t="b">
         <v>0</v>
       </c>
+      <c r="AF487" t="inlineStr"/>
       <c r="AG487" t="b">
         <v>0</v>
       </c>
@@ -50081,10 +50087,10 @@
     </row>
     <row r="488">
       <c r="A488" t="n">
-        <v>127785477</v>
+        <v>127785471</v>
       </c>
       <c r="B488" t="n">
-        <v>79083</v>
+        <v>91472</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -50092,21 +50098,21 @@
         </is>
       </c>
       <c r="E488" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I488" t="inlineStr"/>
@@ -50116,10 +50122,10 @@
         </is>
       </c>
       <c r="Q488" t="n">
-        <v>443827</v>
+        <v>443867</v>
       </c>
       <c r="R488" t="n">
-        <v>6766865</v>
+        <v>6766575</v>
       </c>
       <c r="S488" t="n">
         <v>10</v>
@@ -50151,7 +50157,7 @@
       </c>
       <c r="Z488" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA488" t="inlineStr">
@@ -50161,12 +50167,7 @@
       </c>
       <c r="AB488" t="inlineStr">
         <is>
-          <t>15:06</t>
-        </is>
-      </c>
-      <c r="AC488" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD488" t="b">
@@ -50175,7 +50176,6 @@
       <c r="AE488" t="b">
         <v>0</v>
       </c>
-      <c r="AF488" t="inlineStr"/>
       <c r="AG488" t="b">
         <v>0</v>
       </c>
@@ -50407,10 +50407,10 @@
     </row>
     <row r="491">
       <c r="A491" t="n">
-        <v>127785475</v>
+        <v>127785485</v>
       </c>
       <c r="B491" t="n">
-        <v>78841</v>
+        <v>79083</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -50418,21 +50418,21 @@
         </is>
       </c>
       <c r="E491" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I491" t="inlineStr"/>
@@ -50442,10 +50442,10 @@
         </is>
       </c>
       <c r="Q491" t="n">
-        <v>443548</v>
+        <v>443269</v>
       </c>
       <c r="R491" t="n">
-        <v>6767183</v>
+        <v>6767260</v>
       </c>
       <c r="S491" t="n">
         <v>10</v>
@@ -50477,7 +50477,7 @@
       </c>
       <c r="Z491" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA491" t="inlineStr">
@@ -50487,7 +50487,7 @@
       </c>
       <c r="AB491" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD491" t="b">
@@ -50514,10 +50514,10 @@
     </row>
     <row r="492">
       <c r="A492" t="n">
-        <v>127785485</v>
+        <v>127785475</v>
       </c>
       <c r="B492" t="n">
-        <v>79083</v>
+        <v>78841</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -50525,21 +50525,21 @@
         </is>
       </c>
       <c r="E492" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I492" t="inlineStr"/>
@@ -50549,10 +50549,10 @@
         </is>
       </c>
       <c r="Q492" t="n">
-        <v>443269</v>
+        <v>443548</v>
       </c>
       <c r="R492" t="n">
-        <v>6767260</v>
+        <v>6767183</v>
       </c>
       <c r="S492" t="n">
         <v>10</v>
@@ -50584,7 +50584,7 @@
       </c>
       <c r="Z492" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA492" t="inlineStr">
@@ -50594,7 +50594,7 @@
       </c>
       <c r="AB492" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD492" t="b">
@@ -50621,10 +50621,10 @@
     </row>
     <row r="493">
       <c r="A493" t="n">
-        <v>127795436</v>
+        <v>127795807</v>
       </c>
       <c r="B493" t="n">
-        <v>79083</v>
+        <v>88722</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -50632,24 +50632,28 @@
         </is>
       </c>
       <c r="E493" t="n">
-        <v>6425</v>
+        <v>4412</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H493" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I493" t="inlineStr"/>
+          <t>Sacc. &amp; Cub.</t>
+        </is>
+      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J493" t="inlineStr"/>
       <c r="K493" t="inlineStr"/>
       <c r="N493" t="inlineStr"/>
@@ -50659,10 +50663,10 @@
         </is>
       </c>
       <c r="Q493" t="n">
-        <v>443900</v>
+        <v>443370</v>
       </c>
       <c r="R493" t="n">
-        <v>6766619</v>
+        <v>6767363</v>
       </c>
       <c r="S493" t="n">
         <v>50</v>
@@ -50722,10 +50726,10 @@
     </row>
     <row r="494">
       <c r="A494" t="n">
-        <v>127795451</v>
+        <v>127795436</v>
       </c>
       <c r="B494" t="n">
-        <v>78840</v>
+        <v>79083</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -50733,21 +50737,21 @@
         </is>
       </c>
       <c r="E494" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G494" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I494" t="inlineStr"/>
@@ -50760,10 +50764,10 @@
         </is>
       </c>
       <c r="Q494" t="n">
-        <v>443863</v>
+        <v>443900</v>
       </c>
       <c r="R494" t="n">
-        <v>6766645</v>
+        <v>6766619</v>
       </c>
       <c r="S494" t="n">
         <v>50</v>
@@ -50823,10 +50827,10 @@
     </row>
     <row r="495">
       <c r="A495" t="n">
-        <v>127795807</v>
+        <v>127795451</v>
       </c>
       <c r="B495" t="n">
-        <v>88722</v>
+        <v>78840</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -50834,28 +50838,24 @@
         </is>
       </c>
       <c r="E495" t="n">
-        <v>4412</v>
+        <v>6446</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
-        </is>
-      </c>
-      <c r="I495" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I495" t="inlineStr"/>
       <c r="J495" t="inlineStr"/>
       <c r="K495" t="inlineStr"/>
       <c r="N495" t="inlineStr"/>
@@ -50865,10 +50865,10 @@
         </is>
       </c>
       <c r="Q495" t="n">
-        <v>443370</v>
+        <v>443863</v>
       </c>
       <c r="R495" t="n">
-        <v>6767363</v>
+        <v>6766645</v>
       </c>
       <c r="S495" t="n">
         <v>50</v>
@@ -51233,7 +51233,7 @@
     </row>
     <row r="499">
       <c r="A499" t="n">
-        <v>127795468</v>
+        <v>127795418</v>
       </c>
       <c r="B499" t="n">
         <v>79083</v>
@@ -51271,10 +51271,10 @@
         </is>
       </c>
       <c r="Q499" t="n">
-        <v>443904</v>
+        <v>443861</v>
       </c>
       <c r="R499" t="n">
-        <v>6766715</v>
+        <v>6766594</v>
       </c>
       <c r="S499" t="n">
         <v>50</v>
@@ -51334,7 +51334,7 @@
     </row>
     <row r="500">
       <c r="A500" t="n">
-        <v>127795418</v>
+        <v>127795468</v>
       </c>
       <c r="B500" t="n">
         <v>79083</v>
@@ -51372,10 +51372,10 @@
         </is>
       </c>
       <c r="Q500" t="n">
-        <v>443861</v>
+        <v>443904</v>
       </c>
       <c r="R500" t="n">
-        <v>6766594</v>
+        <v>6766715</v>
       </c>
       <c r="S500" t="n">
         <v>50</v>
@@ -52142,10 +52142,10 @@
     </row>
     <row r="508">
       <c r="A508" t="n">
-        <v>127795545</v>
+        <v>127795430</v>
       </c>
       <c r="B508" t="n">
-        <v>57685</v>
+        <v>79083</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -52153,31 +52153,26 @@
         </is>
       </c>
       <c r="E508" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H508" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I508" t="inlineStr"/>
+      <c r="J508" t="inlineStr"/>
       <c r="K508" t="inlineStr"/>
-      <c r="L508" t="inlineStr"/>
-      <c r="M508" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N508" t="inlineStr"/>
       <c r="P508" t="inlineStr">
         <is>
@@ -52185,10 +52180,10 @@
         </is>
       </c>
       <c r="Q508" t="n">
-        <v>443818</v>
+        <v>443873</v>
       </c>
       <c r="R508" t="n">
-        <v>6766813</v>
+        <v>6766631</v>
       </c>
       <c r="S508" t="n">
         <v>50</v>
@@ -52223,17 +52218,13 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC508" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD508" t="b">
         <v>0</v>
       </c>
       <c r="AE508" t="b">
         <v>0</v>
       </c>
+      <c r="AF508" t="inlineStr"/>
       <c r="AG508" t="b">
         <v>0</v>
       </c>
@@ -52252,10 +52243,10 @@
     </row>
     <row r="509">
       <c r="A509" t="n">
-        <v>127795430</v>
+        <v>127795545</v>
       </c>
       <c r="B509" t="n">
-        <v>79083</v>
+        <v>57685</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -52263,26 +52254,31 @@
         </is>
       </c>
       <c r="E509" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I509" t="inlineStr"/>
-      <c r="J509" t="inlineStr"/>
       <c r="K509" t="inlineStr"/>
+      <c r="L509" t="inlineStr"/>
+      <c r="M509" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N509" t="inlineStr"/>
       <c r="P509" t="inlineStr">
         <is>
@@ -52290,10 +52286,10 @@
         </is>
       </c>
       <c r="Q509" t="n">
-        <v>443873</v>
+        <v>443818</v>
       </c>
       <c r="R509" t="n">
-        <v>6766631</v>
+        <v>6766813</v>
       </c>
       <c r="S509" t="n">
         <v>50</v>
@@ -52328,13 +52324,17 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AC509" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD509" t="b">
         <v>0</v>
       </c>
       <c r="AE509" t="b">
         <v>0</v>
       </c>
-      <c r="AF509" t="inlineStr"/>
       <c r="AG509" t="b">
         <v>0</v>
       </c>
@@ -52353,7 +52353,7 @@
     </row>
     <row r="510">
       <c r="A510" t="n">
-        <v>127795709</v>
+        <v>127795426</v>
       </c>
       <c r="B510" t="n">
         <v>79083</v>
@@ -52391,10 +52391,10 @@
         </is>
       </c>
       <c r="Q510" t="n">
-        <v>443744</v>
+        <v>443856</v>
       </c>
       <c r="R510" t="n">
-        <v>6767161</v>
+        <v>6766617</v>
       </c>
       <c r="S510" t="n">
         <v>50</v>
@@ -52454,7 +52454,7 @@
     </row>
     <row r="511">
       <c r="A511" t="n">
-        <v>127795426</v>
+        <v>127795709</v>
       </c>
       <c r="B511" t="n">
         <v>79083</v>
@@ -52492,10 +52492,10 @@
         </is>
       </c>
       <c r="Q511" t="n">
-        <v>443856</v>
+        <v>443744</v>
       </c>
       <c r="R511" t="n">
-        <v>6766617</v>
+        <v>6767161</v>
       </c>
       <c r="S511" t="n">
         <v>50</v>

--- a/artfynd/A 35482-2025 artfynd.xlsx
+++ b/artfynd/A 35482-2025 artfynd.xlsx
@@ -51233,7 +51233,7 @@
     </row>
     <row r="499">
       <c r="A499" t="n">
-        <v>127795418</v>
+        <v>127795468</v>
       </c>
       <c r="B499" t="n">
         <v>79083</v>
@@ -51271,10 +51271,10 @@
         </is>
       </c>
       <c r="Q499" t="n">
-        <v>443861</v>
+        <v>443904</v>
       </c>
       <c r="R499" t="n">
-        <v>6766594</v>
+        <v>6766715</v>
       </c>
       <c r="S499" t="n">
         <v>50</v>
@@ -51334,7 +51334,7 @@
     </row>
     <row r="500">
       <c r="A500" t="n">
-        <v>127795468</v>
+        <v>127795418</v>
       </c>
       <c r="B500" t="n">
         <v>79083</v>
@@ -51372,10 +51372,10 @@
         </is>
       </c>
       <c r="Q500" t="n">
-        <v>443904</v>
+        <v>443861</v>
       </c>
       <c r="R500" t="n">
-        <v>6766715</v>
+        <v>6766594</v>
       </c>
       <c r="S500" t="n">
         <v>50</v>
@@ -51637,32 +51637,32 @@
     </row>
     <row r="503">
       <c r="A503" t="n">
-        <v>127795391</v>
+        <v>127795182</v>
       </c>
       <c r="B503" t="n">
-        <v>91417</v>
+        <v>79083</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E503" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H503" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I503" t="inlineStr"/>
@@ -51675,10 +51675,10 @@
         </is>
       </c>
       <c r="Q503" t="n">
-        <v>443869</v>
+        <v>443286</v>
       </c>
       <c r="R503" t="n">
-        <v>6766593</v>
+        <v>6767102</v>
       </c>
       <c r="S503" t="n">
         <v>50</v>
@@ -51738,32 +51738,32 @@
     </row>
     <row r="504">
       <c r="A504" t="n">
-        <v>127795182</v>
+        <v>127795391</v>
       </c>
       <c r="B504" t="n">
-        <v>79083</v>
+        <v>91417</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E504" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I504" t="inlineStr"/>
@@ -51776,10 +51776,10 @@
         </is>
       </c>
       <c r="Q504" t="n">
-        <v>443286</v>
+        <v>443869</v>
       </c>
       <c r="R504" t="n">
-        <v>6767102</v>
+        <v>6766593</v>
       </c>
       <c r="S504" t="n">
         <v>50</v>
@@ -52353,7 +52353,7 @@
     </row>
     <row r="510">
       <c r="A510" t="n">
-        <v>127795426</v>
+        <v>127795709</v>
       </c>
       <c r="B510" t="n">
         <v>79083</v>
@@ -52391,10 +52391,10 @@
         </is>
       </c>
       <c r="Q510" t="n">
-        <v>443856</v>
+        <v>443744</v>
       </c>
       <c r="R510" t="n">
-        <v>6766617</v>
+        <v>6767161</v>
       </c>
       <c r="S510" t="n">
         <v>50</v>
@@ -52454,7 +52454,7 @@
     </row>
     <row r="511">
       <c r="A511" t="n">
-        <v>127795709</v>
+        <v>127795426</v>
       </c>
       <c r="B511" t="n">
         <v>79083</v>
@@ -52492,10 +52492,10 @@
         </is>
       </c>
       <c r="Q511" t="n">
-        <v>443744</v>
+        <v>443856</v>
       </c>
       <c r="R511" t="n">
-        <v>6767161</v>
+        <v>6766617</v>
       </c>
       <c r="S511" t="n">
         <v>50</v>

--- a/artfynd/A 35482-2025 artfynd.xlsx
+++ b/artfynd/A 35482-2025 artfynd.xlsx
@@ -52861,7 +52861,7 @@
         <v>127468276</v>
       </c>
       <c r="B515" t="n">
-        <v>78749</v>
+        <v>78753</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>

--- a/artfynd/A 35482-2025 artfynd.xlsx
+++ b/artfynd/A 35482-2025 artfynd.xlsx
@@ -52861,7 +52861,7 @@
         <v>127468276</v>
       </c>
       <c r="B515" t="n">
-        <v>78753</v>
+        <v>78755</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>

--- a/artfynd/A 35482-2025 artfynd.xlsx
+++ b/artfynd/A 35482-2025 artfynd.xlsx
@@ -52861,7 +52861,7 @@
         <v>127468276</v>
       </c>
       <c r="B515" t="n">
-        <v>78755</v>
+        <v>78782</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>

--- a/artfynd/A 35482-2025 artfynd.xlsx
+++ b/artfynd/A 35482-2025 artfynd.xlsx
@@ -52861,7 +52861,7 @@
         <v>127468276</v>
       </c>
       <c r="B515" t="n">
-        <v>78782</v>
+        <v>78786</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>

--- a/artfynd/A 35482-2025 artfynd.xlsx
+++ b/artfynd/A 35482-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY515"/>
+  <dimension ref="A1:AY519"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52963,6 +52963,399 @@
       </c>
       <c r="AY515" t="inlineStr"/>
     </row>
+    <row r="516">
+      <c r="A516" t="n">
+        <v>129927748</v>
+      </c>
+      <c r="B516" t="n">
+        <v>92325</v>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E516" t="n">
+        <v>757</v>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>Apelsinticka</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>Hapalopilus aurantiacus</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I516" t="inlineStr"/>
+      <c r="P516" t="inlineStr">
+        <is>
+          <t>Kråkberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q516" t="n">
+        <v>443550</v>
+      </c>
+      <c r="R516" t="n">
+        <v>6767174</v>
+      </c>
+      <c r="S516" t="n">
+        <v>5</v>
+      </c>
+      <c r="T516" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U516" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V516" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W516" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y516" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA516" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD516" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE516" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF516" t="inlineStr"/>
+      <c r="AG516" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT516" t="inlineStr"/>
+      <c r="AW516" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX516" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY516" t="inlineStr"/>
+    </row>
+    <row r="517">
+      <c r="A517" t="n">
+        <v>129927751</v>
+      </c>
+      <c r="B517" t="n">
+        <v>92885</v>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E517" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I517" t="inlineStr"/>
+      <c r="P517" t="inlineStr">
+        <is>
+          <t>Kråkberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q517" t="n">
+        <v>443555</v>
+      </c>
+      <c r="R517" t="n">
+        <v>6767183</v>
+      </c>
+      <c r="S517" t="n">
+        <v>5</v>
+      </c>
+      <c r="T517" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U517" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V517" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W517" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y517" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA517" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD517" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE517" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG517" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT517" t="inlineStr"/>
+      <c r="AW517" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX517" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY517" t="inlineStr"/>
+    </row>
+    <row r="518">
+      <c r="A518" t="n">
+        <v>129927752</v>
+      </c>
+      <c r="B518" t="n">
+        <v>92919</v>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E518" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I518" t="inlineStr"/>
+      <c r="J518" t="inlineStr"/>
+      <c r="K518" t="inlineStr"/>
+      <c r="N518" t="inlineStr"/>
+      <c r="P518" t="inlineStr">
+        <is>
+          <t>Kråkberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q518" t="n">
+        <v>443706</v>
+      </c>
+      <c r="R518" t="n">
+        <v>6766990</v>
+      </c>
+      <c r="S518" t="n">
+        <v>5</v>
+      </c>
+      <c r="T518" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U518" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V518" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W518" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y518" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA518" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD518" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE518" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF518" t="inlineStr"/>
+      <c r="AG518" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT518" t="inlineStr"/>
+      <c r="AW518" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX518" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY518" t="inlineStr"/>
+    </row>
+    <row r="519">
+      <c r="A519" t="n">
+        <v>129927750</v>
+      </c>
+      <c r="B519" t="n">
+        <v>92907</v>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E519" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I519" t="inlineStr"/>
+      <c r="P519" t="inlineStr">
+        <is>
+          <t>Kråkberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q519" t="n">
+        <v>443549</v>
+      </c>
+      <c r="R519" t="n">
+        <v>6767173</v>
+      </c>
+      <c r="S519" t="n">
+        <v>5</v>
+      </c>
+      <c r="T519" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U519" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V519" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W519" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y519" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA519" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD519" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE519" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG519" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT519" t="inlineStr"/>
+      <c r="AW519" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX519" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY519" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35482-2025 artfynd.xlsx
+++ b/artfynd/A 35482-2025 artfynd.xlsx
@@ -52968,7 +52968,7 @@
         <v>129927748</v>
       </c>
       <c r="B516" t="n">
-        <v>92325</v>
+        <v>92328</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -53066,7 +53066,7 @@
         <v>129927751</v>
       </c>
       <c r="B517" t="n">
-        <v>92885</v>
+        <v>92888</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -53163,7 +53163,7 @@
         <v>129927752</v>
       </c>
       <c r="B518" t="n">
-        <v>92919</v>
+        <v>92922</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -53264,7 +53264,7 @@
         <v>129927750</v>
       </c>
       <c r="B519" t="n">
-        <v>92907</v>
+        <v>92910</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>

--- a/artfynd/A 35482-2025 artfynd.xlsx
+++ b/artfynd/A 35482-2025 artfynd.xlsx
@@ -52994,6 +52994,9 @@
         </is>
       </c>
       <c r="I516" t="inlineStr"/>
+      <c r="J516" t="inlineStr"/>
+      <c r="K516" t="inlineStr"/>
+      <c r="N516" t="inlineStr"/>
       <c r="P516" t="inlineStr">
         <is>
           <t>Kråkberg, Dlr</t>
@@ -53036,6 +53039,11 @@
       <c r="AA516" t="inlineStr">
         <is>
           <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC516" t="inlineStr">
+        <is>
+          <t>Kurs om naturvärden i tallskog - Mellanskog</t>
         </is>
       </c>
       <c r="AD516" t="b">
@@ -53092,6 +53100,9 @@
         </is>
       </c>
       <c r="I517" t="inlineStr"/>
+      <c r="J517" t="inlineStr"/>
+      <c r="K517" t="inlineStr"/>
+      <c r="N517" t="inlineStr"/>
       <c r="P517" t="inlineStr">
         <is>
           <t>Kråkberg, Dlr</t>
@@ -53136,12 +53147,18 @@
           <t>2025-11-04</t>
         </is>
       </c>
+      <c r="AC517" t="inlineStr">
+        <is>
+          <t>Kurs om naturvärden i tallskog - Mellanskog</t>
+        </is>
+      </c>
       <c r="AD517" t="b">
         <v>0</v>
       </c>
       <c r="AE517" t="b">
         <v>0</v>
       </c>
+      <c r="AF517" t="inlineStr"/>
       <c r="AG517" t="b">
         <v>0</v>
       </c>
@@ -53236,6 +53253,11 @@
           <t>2025-11-04</t>
         </is>
       </c>
+      <c r="AC518" t="inlineStr">
+        <is>
+          <t>Kurs om naturvärden i tallskog - Mellanskog</t>
+        </is>
+      </c>
       <c r="AD518" t="b">
         <v>0</v>
       </c>
@@ -53290,6 +53312,9 @@
         </is>
       </c>
       <c r="I519" t="inlineStr"/>
+      <c r="J519" t="inlineStr"/>
+      <c r="K519" t="inlineStr"/>
+      <c r="N519" t="inlineStr"/>
       <c r="P519" t="inlineStr">
         <is>
           <t>Kråkberg, Dlr</t>
@@ -53334,12 +53359,18 @@
           <t>2025-11-04</t>
         </is>
       </c>
+      <c r="AC519" t="inlineStr">
+        <is>
+          <t>Kurs om naturvärden i tallskog - Mellanskog</t>
+        </is>
+      </c>
       <c r="AD519" t="b">
         <v>0</v>
       </c>
       <c r="AE519" t="b">
         <v>0</v>
       </c>
+      <c r="AF519" t="inlineStr"/>
       <c r="AG519" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35482-2025 artfynd.xlsx
+++ b/artfynd/A 35482-2025 artfynd.xlsx
@@ -52968,7 +52968,7 @@
         <v>129927748</v>
       </c>
       <c r="B516" t="n">
-        <v>92328</v>
+        <v>92331</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -53074,7 +53074,7 @@
         <v>129927751</v>
       </c>
       <c r="B517" t="n">
-        <v>92888</v>
+        <v>92891</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -53180,7 +53180,7 @@
         <v>129927752</v>
       </c>
       <c r="B518" t="n">
-        <v>92922</v>
+        <v>92925</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -53286,7 +53286,7 @@
         <v>129927750</v>
       </c>
       <c r="B519" t="n">
-        <v>92910</v>
+        <v>92913</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>

--- a/artfynd/A 35482-2025 artfynd.xlsx
+++ b/artfynd/A 35482-2025 artfynd.xlsx
@@ -52968,7 +52968,7 @@
         <v>129927748</v>
       </c>
       <c r="B516" t="n">
-        <v>92331</v>
+        <v>92332</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -53074,7 +53074,7 @@
         <v>129927751</v>
       </c>
       <c r="B517" t="n">
-        <v>92891</v>
+        <v>92892</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -53180,7 +53180,7 @@
         <v>129927752</v>
       </c>
       <c r="B518" t="n">
-        <v>92925</v>
+        <v>92926</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -53286,7 +53286,7 @@
         <v>129927750</v>
       </c>
       <c r="B519" t="n">
-        <v>92913</v>
+        <v>92914</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>

--- a/artfynd/A 35482-2025 artfynd.xlsx
+++ b/artfynd/A 35482-2025 artfynd.xlsx
@@ -52968,7 +52968,7 @@
         <v>129927748</v>
       </c>
       <c r="B516" t="n">
-        <v>92332</v>
+        <v>92349</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -53074,7 +53074,7 @@
         <v>129927751</v>
       </c>
       <c r="B517" t="n">
-        <v>92892</v>
+        <v>92909</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -53180,7 +53180,7 @@
         <v>129927752</v>
       </c>
       <c r="B518" t="n">
-        <v>92926</v>
+        <v>92943</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -53286,7 +53286,7 @@
         <v>129927750</v>
       </c>
       <c r="B519" t="n">
-        <v>92914</v>
+        <v>92931</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>

--- a/artfynd/A 35482-2025 artfynd.xlsx
+++ b/artfynd/A 35482-2025 artfynd.xlsx
@@ -52968,7 +52968,7 @@
         <v>129927748</v>
       </c>
       <c r="B516" t="n">
-        <v>92365</v>
+        <v>92367</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -53074,7 +53074,7 @@
         <v>129927751</v>
       </c>
       <c r="B517" t="n">
-        <v>92925</v>
+        <v>92927</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -53180,7 +53180,7 @@
         <v>129927752</v>
       </c>
       <c r="B518" t="n">
-        <v>92959</v>
+        <v>92961</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -53286,7 +53286,7 @@
         <v>129927750</v>
       </c>
       <c r="B519" t="n">
-        <v>92947</v>
+        <v>92949</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>

--- a/artfynd/A 35482-2025 artfynd.xlsx
+++ b/artfynd/A 35482-2025 artfynd.xlsx
@@ -52968,7 +52968,7 @@
         <v>129927748</v>
       </c>
       <c r="B516" t="n">
-        <v>92367</v>
+        <v>92454</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -53074,7 +53074,7 @@
         <v>129927751</v>
       </c>
       <c r="B517" t="n">
-        <v>92927</v>
+        <v>93014</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -53180,7 +53180,7 @@
         <v>129927752</v>
       </c>
       <c r="B518" t="n">
-        <v>92961</v>
+        <v>93048</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -53286,7 +53286,7 @@
         <v>129927750</v>
       </c>
       <c r="B519" t="n">
-        <v>92949</v>
+        <v>93036</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>

--- a/artfynd/A 35482-2025 artfynd.xlsx
+++ b/artfynd/A 35482-2025 artfynd.xlsx
@@ -20929,7 +20929,7 @@
         <v>0</v>
       </c>
       <c r="AE197" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG197" t="b">
         <v>0</v>
@@ -34484,7 +34484,7 @@
         <v>0</v>
       </c>
       <c r="AE333" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG333" t="b">
         <v>0</v>
@@ -50705,7 +50705,7 @@
         <v>0</v>
       </c>
       <c r="AE493" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF493" t="inlineStr"/>
       <c r="AG493" t="b">
@@ -52945,7 +52945,7 @@
         <v>0</v>
       </c>
       <c r="AE515" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG515" t="b">
         <v>0</v>

--- a/artfynd/A 35482-2025 artfynd.xlsx
+++ b/artfynd/A 35482-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY576"/>
+  <dimension ref="A1:AZ576"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722852</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127783199</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722848</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1069,6 +1089,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722849</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729067</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127468276</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723564</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1483,6 +1523,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723566</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1580,6 +1625,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723567</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1677,6 +1727,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723572</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1774,6 +1829,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723573</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1871,6 +1931,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723574</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1968,6 +2033,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723575</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2065,6 +2135,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723577</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2162,6 +2237,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723578</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2259,6 +2339,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723579</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2356,6 +2441,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723580</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2453,6 +2543,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723581</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2550,6 +2645,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723582</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2647,6 +2747,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723583</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2744,6 +2849,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723584</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2841,6 +2951,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723585</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2938,6 +3053,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723586</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3035,6 +3155,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723587</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3132,6 +3257,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723588</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3229,6 +3359,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723589</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3326,6 +3461,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723590</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3423,6 +3563,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723591</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3530,6 +3675,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736009</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3636,6 +3786,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129927748</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3733,6 +3888,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723055</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3830,6 +3990,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723066</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3933,6 +4098,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723068</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4040,6 +4210,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729095</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4144,6 +4319,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2016 Dalarna</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60771989</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4256,6 +4436,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2016 Dalarna</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60771906</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4375,6 +4560,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729144</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4489,6 +4679,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127618762</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4586,6 +4781,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723557</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4695,6 +4895,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127730396</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4802,6 +5007,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736037</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4908,6 +5118,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129927751</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5027,6 +5242,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729074</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5135,6 +5355,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729075</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5243,6 +5468,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729076</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5351,6 +5581,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736008</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5456,6 +5691,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127795807</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5557,6 +5797,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127608339</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5670,6 +5915,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729142</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5779,6 +6029,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127730330</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5886,6 +6141,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127785471</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5993,6 +6253,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729069</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6094,6 +6359,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127795391</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6200,6 +6470,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129927750</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6306,6 +6581,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129927752</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6414,6 +6694,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2016 Dalarna</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60771910</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6521,6 +6806,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127467710</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6628,6 +6918,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127471682</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6735,6 +7030,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127471795</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6842,6 +7142,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127472077</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6954,6 +7259,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127472854</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7066,6 +7376,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127473274</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7178,6 +7493,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127473637</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7284,6 +7604,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127606633</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7385,6 +7710,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127606796</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7491,6 +7821,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127606827</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7597,6 +7932,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127606939</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7698,6 +8038,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127608010</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7804,6 +8149,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127608039</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7905,6 +8255,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127608059</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8011,6 +8366,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127608263</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8117,6 +8477,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127608276</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8218,6 +8583,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127608341</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8324,6 +8694,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127608356</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8430,6 +8805,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127613169</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8536,6 +8916,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127613359</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8637,6 +9022,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127613372</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8743,6 +9133,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127613400</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8844,6 +9239,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127613428</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8945,6 +9345,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127618438</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9046,6 +9451,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127618474</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9147,6 +9557,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127618485</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9253,6 +9668,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127618498</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9359,6 +9779,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127618534</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9460,6 +9885,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127618548</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9561,6 +9991,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127618623</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9662,6 +10097,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127618637</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9768,6 +10208,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127618666</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9869,6 +10314,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127618673</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9970,6 +10420,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127618680</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10071,6 +10526,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127618689</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10172,6 +10632,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127618716</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10273,6 +10738,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127618895</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10374,6 +10844,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127619059</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10480,6 +10955,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127619291</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10586,6 +11066,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127619312</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10692,6 +11177,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127620944</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10793,6 +11283,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127620953</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10899,6 +11394,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127620991</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11005,6 +11505,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127621072</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11111,6 +11616,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127621090</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11217,6 +11727,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127621131</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11323,6 +11838,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127621155</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11424,6 +11944,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127621185</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11530,6 +12055,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127621237</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11631,6 +12161,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127621265</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11728,6 +12263,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723072</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11825,6 +12365,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723073</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11922,6 +12467,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723074</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12019,6 +12569,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723075</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12116,6 +12671,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723076</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12213,6 +12773,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723077</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12310,6 +12875,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723079</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12407,6 +12977,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723080</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12504,6 +13079,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723081</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12601,6 +13181,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723082</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12698,6 +13283,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723083</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12795,6 +13385,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723084</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12892,6 +13487,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723085</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12989,6 +13589,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723086</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13086,6 +13691,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723087</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13183,6 +13793,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723088</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13280,6 +13895,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723196</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13377,6 +13997,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723198</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13474,6 +14099,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723199</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13571,6 +14201,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723200</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13668,6 +14303,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723201</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13765,6 +14405,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723202</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13862,6 +14507,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723203</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13959,6 +14609,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723205</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14056,6 +14711,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723206</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14153,6 +14813,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723207</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14250,6 +14915,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723208</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14347,6 +15017,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723209</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14444,6 +15119,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723210</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14541,6 +15221,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723211</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14638,6 +15323,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723212</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14735,6 +15425,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723213</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14832,6 +15527,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723214</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -14929,6 +15629,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723215</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15026,6 +15731,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723216</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15123,6 +15833,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723217</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15220,6 +15935,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723218</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15317,6 +16037,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723219</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15414,6 +16139,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723220</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15511,6 +16241,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723221</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15608,6 +16343,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723222</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -15705,6 +16445,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723223</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -15802,6 +16547,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723224</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -15899,6 +16649,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723225</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -15996,6 +16751,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723226</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -16093,6 +16853,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723227</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -16190,6 +16955,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723228</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -16287,6 +17057,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723229</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -16384,6 +17159,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723230</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -16481,6 +17261,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723231</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -16578,6 +17363,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723232</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -16675,6 +17465,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723233</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -16772,6 +17567,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723234</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -16869,6 +17669,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723235</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -16966,6 +17771,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723236</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -17063,6 +17873,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723237</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -17160,6 +17975,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723238</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -17257,6 +18077,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723239</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -17354,6 +18179,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723240</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -17451,6 +18281,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723241</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -17548,6 +18383,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723242</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -17645,6 +18485,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723244</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -17742,6 +18587,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723245</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -17839,6 +18689,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723246</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -17936,6 +18791,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723247</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -18033,6 +18893,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723248</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -18130,6 +18995,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723249</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -18227,6 +19097,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723250</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -18324,6 +19199,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723251</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -18421,6 +19301,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723252</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -18518,6 +19403,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723253</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -18615,6 +19505,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723254</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -18712,6 +19607,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723255</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -18809,6 +19709,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723256</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -18906,6 +19811,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723257</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -19003,6 +19913,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723258</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -19100,6 +20015,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723259</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -19197,6 +20117,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723260</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -19294,6 +20219,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723261</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -19391,6 +20321,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723263</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -19488,6 +20423,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723264</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -19585,6 +20525,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723266</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -19682,6 +20627,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723269</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -19779,6 +20729,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723271</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -19876,6 +20831,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723273</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -19973,6 +20933,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723275</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -20070,6 +21035,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723277</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -20167,6 +21137,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723278</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -20264,6 +21239,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723280</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -20361,6 +21341,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723281</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -20458,6 +21443,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723283</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -20555,6 +21545,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723285</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -20652,6 +21647,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723286</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -20749,6 +21749,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723288</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -20846,6 +21851,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723289</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -20943,6 +21953,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723291</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -21040,6 +22055,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723292</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -21137,6 +22157,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723294</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -21234,6 +22259,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723295</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -21331,6 +22361,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723296</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -21428,6 +22463,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723297</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -21525,6 +22565,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723298</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -21622,6 +22667,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723299</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -21719,6 +22769,11 @@
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723300</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -21816,6 +22871,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723301</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -21913,6 +22973,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723302</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -22010,6 +23075,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723303</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -22107,6 +23177,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723304</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -22204,6 +23279,11 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723305</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -22301,6 +23381,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723310</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -22398,6 +23483,11 @@
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723311</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -22495,6 +23585,11 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723312</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -22592,6 +23687,11 @@
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723313</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -22689,6 +23789,11 @@
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723314</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -22786,6 +23891,11 @@
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723315</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -22883,6 +23993,11 @@
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723316</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -22980,6 +24095,11 @@
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723317</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -23077,6 +24197,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723318</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -23174,6 +24299,11 @@
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723319</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -23271,6 +24401,11 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723320</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -23368,6 +24503,11 @@
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723321</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -23465,6 +24605,11 @@
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723322</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -23562,6 +24707,11 @@
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723324</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -23659,6 +24809,11 @@
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723325</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -23756,6 +24911,11 @@
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723326</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -23853,6 +25013,11 @@
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723327</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -23950,6 +25115,11 @@
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723328</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -24047,6 +25217,11 @@
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723329</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -24144,6 +25319,11 @@
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723330</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -24241,6 +25421,11 @@
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723331</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -24338,6 +25523,11 @@
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723332</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -24435,6 +25625,11 @@
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723333</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -24532,6 +25727,11 @@
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723334</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -24629,6 +25829,11 @@
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723335</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -24726,6 +25931,11 @@
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723336</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -24823,6 +26033,11 @@
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723337</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -24920,6 +26135,11 @@
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723338</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -25017,6 +26237,11 @@
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723339</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -25114,6 +26339,11 @@
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723341</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -25211,6 +26441,11 @@
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723342</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -25308,6 +26543,11 @@
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723344</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -25405,6 +26645,11 @@
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723345</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -25502,6 +26747,11 @@
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723346</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -25599,6 +26849,11 @@
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723347</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -25696,6 +26951,11 @@
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723348</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -25793,6 +27053,11 @@
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723349</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -25890,6 +27155,11 @@
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723350</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -25987,6 +27257,11 @@
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723351</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -26084,6 +27359,11 @@
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723352</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -26181,6 +27461,11 @@
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723353</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -26278,6 +27563,11 @@
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723354</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -26375,6 +27665,11 @@
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723355</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -26472,6 +27767,11 @@
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
+      <c r="AZ260" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723356</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -26569,6 +27869,11 @@
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723357</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -26666,6 +27971,11 @@
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723358</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -26763,6 +28073,11 @@
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
+      <c r="AZ263" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723359</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -26860,6 +28175,11 @@
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
+      <c r="AZ264" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723360</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -26957,6 +28277,11 @@
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
+      <c r="AZ265" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723361</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -27054,6 +28379,11 @@
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
+      <c r="AZ266" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723362</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -27151,6 +28481,11 @@
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
+      <c r="AZ267" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723363</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -27248,6 +28583,11 @@
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
+      <c r="AZ268" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723364</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -27345,6 +28685,11 @@
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
+      <c r="AZ269" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723365</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -27442,6 +28787,11 @@
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
+      <c r="AZ270" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723366</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -27539,6 +28889,11 @@
         </is>
       </c>
       <c r="AY271" t="inlineStr"/>
+      <c r="AZ271" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723367</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -27636,6 +28991,11 @@
         </is>
       </c>
       <c r="AY272" t="inlineStr"/>
+      <c r="AZ272" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723369</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -27733,6 +29093,11 @@
         </is>
       </c>
       <c r="AY273" t="inlineStr"/>
+      <c r="AZ273" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723370</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -27830,6 +29195,11 @@
         </is>
       </c>
       <c r="AY274" t="inlineStr"/>
+      <c r="AZ274" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723371</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -27927,6 +29297,11 @@
         </is>
       </c>
       <c r="AY275" t="inlineStr"/>
+      <c r="AZ275" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723372</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -28024,6 +29399,11 @@
         </is>
       </c>
       <c r="AY276" t="inlineStr"/>
+      <c r="AZ276" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723373</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -28121,6 +29501,11 @@
         </is>
       </c>
       <c r="AY277" t="inlineStr"/>
+      <c r="AZ277" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723374</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -28218,6 +29603,11 @@
         </is>
       </c>
       <c r="AY278" t="inlineStr"/>
+      <c r="AZ278" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723375</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -28315,6 +29705,11 @@
         </is>
       </c>
       <c r="AY279" t="inlineStr"/>
+      <c r="AZ279" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723376</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -28412,6 +29807,11 @@
         </is>
       </c>
       <c r="AY280" t="inlineStr"/>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723377</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -28509,6 +29909,11 @@
         </is>
       </c>
       <c r="AY281" t="inlineStr"/>
+      <c r="AZ281" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723378</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -28606,6 +30011,11 @@
         </is>
       </c>
       <c r="AY282" t="inlineStr"/>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723379</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -28703,6 +30113,11 @@
         </is>
       </c>
       <c r="AY283" t="inlineStr"/>
+      <c r="AZ283" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723380</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -28800,6 +30215,11 @@
         </is>
       </c>
       <c r="AY284" t="inlineStr"/>
+      <c r="AZ284" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723381</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -28897,6 +30317,11 @@
         </is>
       </c>
       <c r="AY285" t="inlineStr"/>
+      <c r="AZ285" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723382</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -28994,6 +30419,11 @@
         </is>
       </c>
       <c r="AY286" t="inlineStr"/>
+      <c r="AZ286" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723383</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -29091,6 +30521,11 @@
         </is>
       </c>
       <c r="AY287" t="inlineStr"/>
+      <c r="AZ287" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723384</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -29188,6 +30623,11 @@
         </is>
       </c>
       <c r="AY288" t="inlineStr"/>
+      <c r="AZ288" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723385</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -29285,6 +30725,11 @@
         </is>
       </c>
       <c r="AY289" t="inlineStr"/>
+      <c r="AZ289" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723386</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -29382,6 +30827,11 @@
         </is>
       </c>
       <c r="AY290" t="inlineStr"/>
+      <c r="AZ290" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723387</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -29479,6 +30929,11 @@
         </is>
       </c>
       <c r="AY291" t="inlineStr"/>
+      <c r="AZ291" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723388</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -29576,6 +31031,11 @@
         </is>
       </c>
       <c r="AY292" t="inlineStr"/>
+      <c r="AZ292" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723389</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -29673,6 +31133,11 @@
         </is>
       </c>
       <c r="AY293" t="inlineStr"/>
+      <c r="AZ293" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723390</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -29770,6 +31235,11 @@
         </is>
       </c>
       <c r="AY294" t="inlineStr"/>
+      <c r="AZ294" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723391</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -29867,6 +31337,11 @@
         </is>
       </c>
       <c r="AY295" t="inlineStr"/>
+      <c r="AZ295" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723392</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -29964,6 +31439,11 @@
         </is>
       </c>
       <c r="AY296" t="inlineStr"/>
+      <c r="AZ296" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723393</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -30061,6 +31541,11 @@
         </is>
       </c>
       <c r="AY297" t="inlineStr"/>
+      <c r="AZ297" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723395</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -30158,6 +31643,11 @@
         </is>
       </c>
       <c r="AY298" t="inlineStr"/>
+      <c r="AZ298" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723396</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -30255,6 +31745,11 @@
         </is>
       </c>
       <c r="AY299" t="inlineStr"/>
+      <c r="AZ299" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723397</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -30352,6 +31847,11 @@
         </is>
       </c>
       <c r="AY300" t="inlineStr"/>
+      <c r="AZ300" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723398</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -30449,6 +31949,11 @@
         </is>
       </c>
       <c r="AY301" t="inlineStr"/>
+      <c r="AZ301" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723399</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -30546,6 +32051,11 @@
         </is>
       </c>
       <c r="AY302" t="inlineStr"/>
+      <c r="AZ302" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723400</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -30643,6 +32153,11 @@
         </is>
       </c>
       <c r="AY303" t="inlineStr"/>
+      <c r="AZ303" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723553</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -30751,6 +32266,11 @@
         </is>
       </c>
       <c r="AY304" t="inlineStr"/>
+      <c r="AZ304" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729078</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -30859,6 +32379,11 @@
         </is>
       </c>
       <c r="AY305" t="inlineStr"/>
+      <c r="AZ305" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729079</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -30967,6 +32492,11 @@
         </is>
       </c>
       <c r="AY306" t="inlineStr"/>
+      <c r="AZ306" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729080</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -31075,6 +32605,11 @@
         </is>
       </c>
       <c r="AY307" t="inlineStr"/>
+      <c r="AZ307" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729081</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -31183,6 +32718,11 @@
         </is>
       </c>
       <c r="AY308" t="inlineStr"/>
+      <c r="AZ308" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729096</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -31291,6 +32831,11 @@
         </is>
       </c>
       <c r="AY309" t="inlineStr"/>
+      <c r="AZ309" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729097</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -31399,6 +32944,11 @@
         </is>
       </c>
       <c r="AY310" t="inlineStr"/>
+      <c r="AZ310" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729098</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -31507,6 +33057,11 @@
         </is>
       </c>
       <c r="AY311" t="inlineStr"/>
+      <c r="AZ311" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729099</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -31615,6 +33170,11 @@
         </is>
       </c>
       <c r="AY312" t="inlineStr"/>
+      <c r="AZ312" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729100</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -31723,6 +33283,11 @@
         </is>
       </c>
       <c r="AY313" t="inlineStr"/>
+      <c r="AZ313" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729101</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -31831,6 +33396,11 @@
         </is>
       </c>
       <c r="AY314" t="inlineStr"/>
+      <c r="AZ314" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729102</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -31939,6 +33509,11 @@
         </is>
       </c>
       <c r="AY315" t="inlineStr"/>
+      <c r="AZ315" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729104</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -32047,6 +33622,11 @@
         </is>
       </c>
       <c r="AY316" t="inlineStr"/>
+      <c r="AZ316" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729106</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -32155,6 +33735,11 @@
         </is>
       </c>
       <c r="AY317" t="inlineStr"/>
+      <c r="AZ317" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729107</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -32263,6 +33848,11 @@
         </is>
       </c>
       <c r="AY318" t="inlineStr"/>
+      <c r="AZ318" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729108</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -32371,6 +33961,11 @@
         </is>
       </c>
       <c r="AY319" t="inlineStr"/>
+      <c r="AZ319" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729109</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -32479,6 +34074,11 @@
         </is>
       </c>
       <c r="AY320" t="inlineStr"/>
+      <c r="AZ320" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729110</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -32587,6 +34187,11 @@
         </is>
       </c>
       <c r="AY321" t="inlineStr"/>
+      <c r="AZ321" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729111</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -32695,6 +34300,11 @@
         </is>
       </c>
       <c r="AY322" t="inlineStr"/>
+      <c r="AZ322" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729112</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -32803,6 +34413,11 @@
         </is>
       </c>
       <c r="AY323" t="inlineStr"/>
+      <c r="AZ323" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729113</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -32911,6 +34526,11 @@
         </is>
       </c>
       <c r="AY324" t="inlineStr"/>
+      <c r="AZ324" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729114</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -33019,6 +34639,11 @@
         </is>
       </c>
       <c r="AY325" t="inlineStr"/>
+      <c r="AZ325" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729116</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -33127,6 +34752,11 @@
         </is>
       </c>
       <c r="AY326" t="inlineStr"/>
+      <c r="AZ326" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729117</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -33235,6 +34865,11 @@
         </is>
       </c>
       <c r="AY327" t="inlineStr"/>
+      <c r="AZ327" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729118</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -33343,6 +34978,11 @@
         </is>
       </c>
       <c r="AY328" t="inlineStr"/>
+      <c r="AZ328" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729119</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -33451,6 +35091,11 @@
         </is>
       </c>
       <c r="AY329" t="inlineStr"/>
+      <c r="AZ329" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729120</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -33559,6 +35204,11 @@
         </is>
       </c>
       <c r="AY330" t="inlineStr"/>
+      <c r="AZ330" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729121</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -33667,6 +35317,11 @@
         </is>
       </c>
       <c r="AY331" t="inlineStr"/>
+      <c r="AZ331" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729123</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -33775,6 +35430,11 @@
         </is>
       </c>
       <c r="AY332" t="inlineStr"/>
+      <c r="AZ332" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729124</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -33883,6 +35543,11 @@
         </is>
       </c>
       <c r="AY333" t="inlineStr"/>
+      <c r="AZ333" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729125</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -33991,6 +35656,11 @@
         </is>
       </c>
       <c r="AY334" t="inlineStr"/>
+      <c r="AZ334" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729126</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -34099,6 +35769,11 @@
         </is>
       </c>
       <c r="AY335" t="inlineStr"/>
+      <c r="AZ335" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729127</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -34207,6 +35882,11 @@
         </is>
       </c>
       <c r="AY336" t="inlineStr"/>
+      <c r="AZ336" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729128</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -34315,6 +35995,11 @@
         </is>
       </c>
       <c r="AY337" t="inlineStr"/>
+      <c r="AZ337" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729129</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -34423,6 +36108,11 @@
         </is>
       </c>
       <c r="AY338" t="inlineStr"/>
+      <c r="AZ338" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729130</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -34531,6 +36221,11 @@
         </is>
       </c>
       <c r="AY339" t="inlineStr"/>
+      <c r="AZ339" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729131</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -34639,6 +36334,11 @@
         </is>
       </c>
       <c r="AY340" t="inlineStr"/>
+      <c r="AZ340" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729132</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -34747,6 +36447,11 @@
         </is>
       </c>
       <c r="AY341" t="inlineStr"/>
+      <c r="AZ341" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729133</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -34855,6 +36560,11 @@
         </is>
       </c>
       <c r="AY342" t="inlineStr"/>
+      <c r="AZ342" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729134</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -34963,6 +36673,11 @@
         </is>
       </c>
       <c r="AY343" t="inlineStr"/>
+      <c r="AZ343" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729135</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -35071,6 +36786,11 @@
         </is>
       </c>
       <c r="AY344" t="inlineStr"/>
+      <c r="AZ344" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729136</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -35177,6 +36897,11 @@
         </is>
       </c>
       <c r="AY345" t="inlineStr"/>
+      <c r="AZ345" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127730292</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -35278,6 +37003,11 @@
         </is>
       </c>
       <c r="AY346" t="inlineStr"/>
+      <c r="AZ346" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127730308</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -35384,6 +37114,11 @@
         </is>
       </c>
       <c r="AY347" t="inlineStr"/>
+      <c r="AZ347" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127730374</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -35490,6 +37225,11 @@
         </is>
       </c>
       <c r="AY348" t="inlineStr"/>
+      <c r="AZ348" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127730382</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -35597,6 +37337,11 @@
         </is>
       </c>
       <c r="AY349" t="inlineStr"/>
+      <c r="AZ349" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736018</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -35704,6 +37449,11 @@
         </is>
       </c>
       <c r="AY350" t="inlineStr"/>
+      <c r="AZ350" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736020</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -35811,6 +37561,11 @@
         </is>
       </c>
       <c r="AY351" t="inlineStr"/>
+      <c r="AZ351" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736021</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -35918,6 +37673,11 @@
         </is>
       </c>
       <c r="AY352" t="inlineStr"/>
+      <c r="AZ352" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736022</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -36025,6 +37785,11 @@
         </is>
       </c>
       <c r="AY353" t="inlineStr"/>
+      <c r="AZ353" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736023</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -36132,6 +37897,11 @@
         </is>
       </c>
       <c r="AY354" t="inlineStr"/>
+      <c r="AZ354" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736036</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -36245,6 +38015,11 @@
         </is>
       </c>
       <c r="AY355" t="inlineStr"/>
+      <c r="AZ355" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127785476</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -36358,6 +38133,11 @@
         </is>
       </c>
       <c r="AY356" t="inlineStr"/>
+      <c r="AZ356" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127785477</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -36474,6 +38254,11 @@
         </is>
       </c>
       <c r="AY357" t="inlineStr"/>
+      <c r="AZ357" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127785479</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -36581,6 +38366,11 @@
         </is>
       </c>
       <c r="AY358" t="inlineStr"/>
+      <c r="AZ358" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127785485</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -36688,6 +38478,11 @@
         </is>
       </c>
       <c r="AY359" t="inlineStr"/>
+      <c r="AZ359" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127785486</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -36795,6 +38590,11 @@
         </is>
       </c>
       <c r="AY360" t="inlineStr"/>
+      <c r="AZ360" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127785487</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -36896,6 +38696,11 @@
         </is>
       </c>
       <c r="AY361" t="inlineStr"/>
+      <c r="AZ361" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127795182</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -36997,6 +38802,11 @@
         </is>
       </c>
       <c r="AY362" t="inlineStr"/>
+      <c r="AZ362" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127795213</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -37098,6 +38908,11 @@
         </is>
       </c>
       <c r="AY363" t="inlineStr"/>
+      <c r="AZ363" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127795217</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -37199,6 +39014,11 @@
         </is>
       </c>
       <c r="AY364" t="inlineStr"/>
+      <c r="AZ364" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127795418</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -37300,6 +39120,11 @@
         </is>
       </c>
       <c r="AY365" t="inlineStr"/>
+      <c r="AZ365" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127795426</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -37401,6 +39226,11 @@
         </is>
       </c>
       <c r="AY366" t="inlineStr"/>
+      <c r="AZ366" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127795430</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -37502,6 +39332,11 @@
         </is>
       </c>
       <c r="AY367" t="inlineStr"/>
+      <c r="AZ367" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127795436</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -37603,6 +39438,11 @@
         </is>
       </c>
       <c r="AY368" t="inlineStr"/>
+      <c r="AZ368" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127795460</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -37704,6 +39544,11 @@
         </is>
       </c>
       <c r="AY369" t="inlineStr"/>
+      <c r="AZ369" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127795468</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -37805,6 +39650,11 @@
         </is>
       </c>
       <c r="AY370" t="inlineStr"/>
+      <c r="AZ370" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127795477</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -37906,6 +39756,11 @@
         </is>
       </c>
       <c r="AY371" t="inlineStr"/>
+      <c r="AZ371" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127795620</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -38007,6 +39862,11 @@
         </is>
       </c>
       <c r="AY372" t="inlineStr"/>
+      <c r="AZ372" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127795709</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -38104,6 +39964,11 @@
         </is>
       </c>
       <c r="AY373" t="inlineStr"/>
+      <c r="AZ373" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723611</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -38205,6 +40070,11 @@
         </is>
       </c>
       <c r="AY374" t="inlineStr"/>
+      <c r="AZ374" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127608076</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -38307,6 +40177,11 @@
         </is>
       </c>
       <c r="AY375" t="inlineStr"/>
+      <c r="AZ375" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722837</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -38404,6 +40279,11 @@
         </is>
       </c>
       <c r="AY376" t="inlineStr"/>
+      <c r="AZ376" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722838</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -38505,6 +40385,11 @@
         </is>
       </c>
       <c r="AY377" t="inlineStr"/>
+      <c r="AZ377" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127608047</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -38606,6 +40491,11 @@
         </is>
       </c>
       <c r="AY378" t="inlineStr"/>
+      <c r="AZ378" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127618554</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -38707,6 +40597,11 @@
         </is>
       </c>
       <c r="AY379" t="inlineStr"/>
+      <c r="AZ379" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127619016</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -38808,6 +40703,11 @@
         </is>
       </c>
       <c r="AY380" t="inlineStr"/>
+      <c r="AZ380" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127620818</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -38909,6 +40809,11 @@
         </is>
       </c>
       <c r="AY381" t="inlineStr"/>
+      <c r="AZ381" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127621011</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -39010,6 +40915,11 @@
         </is>
       </c>
       <c r="AY382" t="inlineStr"/>
+      <c r="AZ382" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127621268</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -39108,6 +41018,11 @@
         </is>
       </c>
       <c r="AY383" t="inlineStr"/>
+      <c r="AZ383" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723057</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -39206,6 +41121,11 @@
         </is>
       </c>
       <c r="AY384" t="inlineStr"/>
+      <c r="AZ384" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723058</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -39304,6 +41224,11 @@
         </is>
       </c>
       <c r="AY385" t="inlineStr"/>
+      <c r="AZ385" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723060</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -39412,6 +41337,11 @@
         </is>
       </c>
       <c r="AY386" t="inlineStr"/>
+      <c r="AZ386" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729090</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -39520,6 +41450,11 @@
         </is>
       </c>
       <c r="AY387" t="inlineStr"/>
+      <c r="AZ387" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729091</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -39627,6 +41562,11 @@
         </is>
       </c>
       <c r="AY388" t="inlineStr"/>
+      <c r="AZ388" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736015</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -39734,6 +41674,11 @@
         </is>
       </c>
       <c r="AY389" t="inlineStr"/>
+      <c r="AZ389" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736016</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -39835,6 +41780,11 @@
         </is>
       </c>
       <c r="AY390" t="inlineStr"/>
+      <c r="AZ390" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127795451</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -39937,6 +41887,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2016 Dalarna</t>
         </is>
       </c>
+      <c r="AZ391" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61497947</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -40034,6 +41989,11 @@
         </is>
       </c>
       <c r="AY392" t="inlineStr"/>
+      <c r="AZ392" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722805</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -40131,6 +42091,11 @@
         </is>
       </c>
       <c r="AY393" t="inlineStr"/>
+      <c r="AZ393" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722806</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -40228,6 +42193,11 @@
         </is>
       </c>
       <c r="AY394" t="inlineStr"/>
+      <c r="AZ394" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722807</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -40325,6 +42295,11 @@
         </is>
       </c>
       <c r="AY395" t="inlineStr"/>
+      <c r="AZ395" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722808</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -40422,6 +42397,11 @@
         </is>
       </c>
       <c r="AY396" t="inlineStr"/>
+      <c r="AZ396" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722809</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -40519,6 +42499,11 @@
         </is>
       </c>
       <c r="AY397" t="inlineStr"/>
+      <c r="AZ397" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722810</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -40616,6 +42601,11 @@
         </is>
       </c>
       <c r="AY398" t="inlineStr"/>
+      <c r="AZ398" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722811</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -40713,6 +42703,11 @@
         </is>
       </c>
       <c r="AY399" t="inlineStr"/>
+      <c r="AZ399" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722812</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -40810,6 +42805,11 @@
         </is>
       </c>
       <c r="AY400" t="inlineStr"/>
+      <c r="AZ400" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722813</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -40907,6 +42907,11 @@
         </is>
       </c>
       <c r="AY401" t="inlineStr"/>
+      <c r="AZ401" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722815</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -41004,6 +43009,11 @@
         </is>
       </c>
       <c r="AY402" t="inlineStr"/>
+      <c r="AZ402" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722816</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -41101,6 +43111,11 @@
         </is>
       </c>
       <c r="AY403" t="inlineStr"/>
+      <c r="AZ403" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722817</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -41198,6 +43213,11 @@
         </is>
       </c>
       <c r="AY404" t="inlineStr"/>
+      <c r="AZ404" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722818</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -41295,6 +43315,11 @@
         </is>
       </c>
       <c r="AY405" t="inlineStr"/>
+      <c r="AZ405" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722819</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -41392,6 +43417,11 @@
         </is>
       </c>
       <c r="AY406" t="inlineStr"/>
+      <c r="AZ406" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722820</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -41489,6 +43519,11 @@
         </is>
       </c>
       <c r="AY407" t="inlineStr"/>
+      <c r="AZ407" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722822</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -41586,6 +43621,11 @@
         </is>
       </c>
       <c r="AY408" t="inlineStr"/>
+      <c r="AZ408" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722823</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -41687,6 +43727,11 @@
         </is>
       </c>
       <c r="AY409" t="inlineStr"/>
+      <c r="AZ409" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127730376</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -41788,6 +43833,11 @@
         </is>
       </c>
       <c r="AY410" t="inlineStr"/>
+      <c r="AZ410" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127730386</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -41895,6 +43945,11 @@
         </is>
       </c>
       <c r="AY411" t="inlineStr"/>
+      <c r="AZ411" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736004</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -42002,6 +44057,11 @@
         </is>
       </c>
       <c r="AY412" t="inlineStr"/>
+      <c r="AZ412" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127785466</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -42109,6 +44169,11 @@
         </is>
       </c>
       <c r="AY413" t="inlineStr"/>
+      <c r="AZ413" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127785467</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -42210,6 +44275,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2016 Dalarna</t>
         </is>
       </c>
+      <c r="AZ414" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61498256</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -42307,6 +44377,11 @@
         </is>
       </c>
       <c r="AY415" t="inlineStr"/>
+      <c r="AZ415" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723610</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -42412,6 +44487,11 @@
         </is>
       </c>
       <c r="AY416" t="inlineStr"/>
+      <c r="AZ416" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127619056</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -42514,6 +44594,11 @@
         </is>
       </c>
       <c r="AY417" t="inlineStr"/>
+      <c r="AZ417" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722886</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -42616,6 +44701,11 @@
         </is>
       </c>
       <c r="AY418" t="inlineStr"/>
+      <c r="AZ418" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722898</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
@@ -42718,6 +44808,11 @@
         </is>
       </c>
       <c r="AY419" t="inlineStr"/>
+      <c r="AZ419" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722899</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
@@ -42828,6 +44923,11 @@
         </is>
       </c>
       <c r="AY420" t="inlineStr"/>
+      <c r="AZ420" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127618880</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
@@ -42938,6 +45038,11 @@
         </is>
       </c>
       <c r="AY421" t="inlineStr"/>
+      <c r="AZ421" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127618950</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
@@ -43043,6 +45148,11 @@
         </is>
       </c>
       <c r="AY422" t="inlineStr"/>
+      <c r="AZ422" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127619053</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
@@ -43153,6 +45263,11 @@
         </is>
       </c>
       <c r="AY423" t="inlineStr"/>
+      <c r="AZ423" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127621213</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
@@ -43255,6 +45370,11 @@
         </is>
       </c>
       <c r="AY424" t="inlineStr"/>
+      <c r="AZ424" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722902</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
@@ -43357,6 +45477,11 @@
         </is>
       </c>
       <c r="AY425" t="inlineStr"/>
+      <c r="AZ425" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722905</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
@@ -43464,6 +45589,11 @@
         </is>
       </c>
       <c r="AY426" t="inlineStr"/>
+      <c r="AZ426" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722906</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
@@ -43571,6 +45701,11 @@
         </is>
       </c>
       <c r="AY427" t="inlineStr"/>
+      <c r="AZ427" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722907</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
@@ -43678,6 +45813,11 @@
         </is>
       </c>
       <c r="AY428" t="inlineStr"/>
+      <c r="AZ428" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722910</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
@@ -43785,6 +45925,11 @@
         </is>
       </c>
       <c r="AY429" t="inlineStr"/>
+      <c r="AZ429" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722911</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
@@ -43892,6 +46037,11 @@
         </is>
       </c>
       <c r="AY430" t="inlineStr"/>
+      <c r="AZ430" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722912</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
@@ -43999,6 +46149,11 @@
         </is>
       </c>
       <c r="AY431" t="inlineStr"/>
+      <c r="AZ431" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722913</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
@@ -44101,6 +46256,11 @@
         </is>
       </c>
       <c r="AY432" t="inlineStr"/>
+      <c r="AZ432" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723546</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
@@ -44203,6 +46363,11 @@
         </is>
       </c>
       <c r="AY433" t="inlineStr"/>
+      <c r="AZ433" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723547</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
@@ -44305,6 +46470,11 @@
         </is>
       </c>
       <c r="AY434" t="inlineStr"/>
+      <c r="AZ434" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723548</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
@@ -44407,6 +46577,11 @@
         </is>
       </c>
       <c r="AY435" t="inlineStr"/>
+      <c r="AZ435" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723549</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
@@ -44509,6 +46684,11 @@
         </is>
       </c>
       <c r="AY436" t="inlineStr"/>
+      <c r="AZ436" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723550</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
@@ -44611,6 +46791,11 @@
         </is>
       </c>
       <c r="AY437" t="inlineStr"/>
+      <c r="AZ437" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723551</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
@@ -44713,6 +46898,11 @@
         </is>
       </c>
       <c r="AY438" t="inlineStr"/>
+      <c r="AZ438" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723617</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
@@ -44815,6 +47005,11 @@
         </is>
       </c>
       <c r="AY439" t="inlineStr"/>
+      <c r="AZ439" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723618</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
@@ -44922,6 +47117,11 @@
         </is>
       </c>
       <c r="AY440" t="inlineStr"/>
+      <c r="AZ440" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723620</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
@@ -45032,6 +47232,11 @@
         </is>
       </c>
       <c r="AY441" t="inlineStr"/>
+      <c r="AZ441" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127730270</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
@@ -45142,6 +47347,11 @@
         </is>
       </c>
       <c r="AY442" t="inlineStr"/>
+      <c r="AZ442" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127730406</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
@@ -45252,6 +47462,11 @@
         </is>
       </c>
       <c r="AY443" t="inlineStr"/>
+      <c r="AZ443" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736307</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
@@ -45367,6 +47582,11 @@
         </is>
       </c>
       <c r="AY444" t="inlineStr"/>
+      <c r="AZ444" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127785469</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
@@ -45477,6 +47697,11 @@
         </is>
       </c>
       <c r="AY445" t="inlineStr"/>
+      <c r="AZ445" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127795545</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
@@ -45590,6 +47815,11 @@
         </is>
       </c>
       <c r="AY446" t="inlineStr"/>
+      <c r="AZ446" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127618987</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
@@ -45697,6 +47927,11 @@
         </is>
       </c>
       <c r="AY447" t="inlineStr"/>
+      <c r="AZ447" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127619038</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
@@ -45804,6 +48039,11 @@
         </is>
       </c>
       <c r="AY448" t="inlineStr"/>
+      <c r="AZ448" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127619035</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
@@ -45906,6 +48146,11 @@
         </is>
       </c>
       <c r="AY449" t="inlineStr"/>
+      <c r="AZ449" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723613</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
@@ -46008,6 +48253,11 @@
         </is>
       </c>
       <c r="AY450" t="inlineStr"/>
+      <c r="AZ450" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723614</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
@@ -46115,6 +48365,11 @@
         </is>
       </c>
       <c r="AY451" t="inlineStr"/>
+      <c r="AZ451" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127620831</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
@@ -46216,6 +48471,11 @@
         </is>
       </c>
       <c r="AY452" t="inlineStr"/>
+      <c r="AZ452" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127618897</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
@@ -46321,6 +48581,11 @@
         </is>
       </c>
       <c r="AY453" t="inlineStr"/>
+      <c r="AZ453" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127621194</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
@@ -46423,6 +48688,11 @@
         </is>
       </c>
       <c r="AY454" t="inlineStr"/>
+      <c r="AZ454" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722869</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
@@ -46525,6 +48795,11 @@
         </is>
       </c>
       <c r="AY455" t="inlineStr"/>
+      <c r="AZ455" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722871</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
@@ -46627,6 +48902,11 @@
         </is>
       </c>
       <c r="AY456" t="inlineStr"/>
+      <c r="AZ456" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722803</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
@@ -46729,6 +49009,11 @@
         </is>
       </c>
       <c r="AY457" t="inlineStr"/>
+      <c r="AZ457" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722804</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
@@ -46840,6 +49125,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2016 Dalarna</t>
         </is>
       </c>
+      <c r="AZ458" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60771954</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
@@ -46942,6 +49232,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2016 Dalarna</t>
         </is>
       </c>
+      <c r="AZ459" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61497948</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
@@ -47054,6 +49349,11 @@
         </is>
       </c>
       <c r="AY460" t="inlineStr"/>
+      <c r="AZ460" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127473199</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
@@ -47166,6 +49466,11 @@
         </is>
       </c>
       <c r="AY461" t="inlineStr"/>
+      <c r="AZ461" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127473294</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
@@ -47273,6 +49578,11 @@
         </is>
       </c>
       <c r="AY462" t="inlineStr"/>
+      <c r="AZ462" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127606882</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
@@ -47380,6 +49690,11 @@
         </is>
       </c>
       <c r="AY463" t="inlineStr"/>
+      <c r="AZ463" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127606899</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
@@ -47487,6 +49802,11 @@
         </is>
       </c>
       <c r="AY464" t="inlineStr"/>
+      <c r="AZ464" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127608027</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
@@ -47594,6 +49914,11 @@
         </is>
       </c>
       <c r="AY465" t="inlineStr"/>
+      <c r="AZ465" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127608037</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
@@ -47701,6 +50026,11 @@
         </is>
       </c>
       <c r="AY466" t="inlineStr"/>
+      <c r="AZ466" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127613349</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
@@ -47808,6 +50138,11 @@
         </is>
       </c>
       <c r="AY467" t="inlineStr"/>
+      <c r="AZ467" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127613386</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
@@ -47915,6 +50250,11 @@
         </is>
       </c>
       <c r="AY468" t="inlineStr"/>
+      <c r="AZ468" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127613395</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
@@ -48022,6 +50362,11 @@
         </is>
       </c>
       <c r="AY469" t="inlineStr"/>
+      <c r="AZ469" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127618512</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
@@ -48129,6 +50474,11 @@
         </is>
       </c>
       <c r="AY470" t="inlineStr"/>
+      <c r="AZ470" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127618615</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
@@ -48241,6 +50591,11 @@
         </is>
       </c>
       <c r="AY471" t="inlineStr"/>
+      <c r="AZ471" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127618658</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
@@ -48353,6 +50708,11 @@
         </is>
       </c>
       <c r="AY472" t="inlineStr"/>
+      <c r="AZ472" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127618701</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="n">
@@ -48465,6 +50825,11 @@
         </is>
       </c>
       <c r="AY473" t="inlineStr"/>
+      <c r="AZ473" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127618707</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
@@ -48577,6 +50942,11 @@
         </is>
       </c>
       <c r="AY474" t="inlineStr"/>
+      <c r="AZ474" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127619158</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
@@ -48689,6 +51059,11 @@
         </is>
       </c>
       <c r="AY475" t="inlineStr"/>
+      <c r="AZ475" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127619167</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
@@ -48801,6 +51176,11 @@
         </is>
       </c>
       <c r="AY476" t="inlineStr"/>
+      <c r="AZ476" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127619183</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
@@ -48903,6 +51283,11 @@
         </is>
       </c>
       <c r="AY477" t="inlineStr"/>
+      <c r="AZ477" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722934</t>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="n">
@@ -49005,6 +51390,11 @@
         </is>
       </c>
       <c r="AY478" t="inlineStr"/>
+      <c r="AZ478" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722935</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
@@ -49107,6 +51497,11 @@
         </is>
       </c>
       <c r="AY479" t="inlineStr"/>
+      <c r="AZ479" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722936</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="n">
@@ -49209,6 +51604,11 @@
         </is>
       </c>
       <c r="AY480" t="inlineStr"/>
+      <c r="AZ480" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722937</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="n">
@@ -49311,6 +51711,11 @@
         </is>
       </c>
       <c r="AY481" t="inlineStr"/>
+      <c r="AZ481" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722938</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="n">
@@ -49413,6 +51818,11 @@
         </is>
       </c>
       <c r="AY482" t="inlineStr"/>
+      <c r="AZ482" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722939</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
@@ -49515,6 +51925,11 @@
         </is>
       </c>
       <c r="AY483" t="inlineStr"/>
+      <c r="AZ483" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722940</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
@@ -49617,6 +52032,11 @@
         </is>
       </c>
       <c r="AY484" t="inlineStr"/>
+      <c r="AZ484" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722958</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="n">
@@ -49719,6 +52139,11 @@
         </is>
       </c>
       <c r="AY485" t="inlineStr"/>
+      <c r="AZ485" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722959</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="n">
@@ -49821,6 +52246,11 @@
         </is>
       </c>
       <c r="AY486" t="inlineStr"/>
+      <c r="AZ486" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722960</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
@@ -49923,6 +52353,11 @@
         </is>
       </c>
       <c r="AY487" t="inlineStr"/>
+      <c r="AZ487" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722961</t>
+        </is>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
@@ -50025,6 +52460,11 @@
         </is>
       </c>
       <c r="AY488" t="inlineStr"/>
+      <c r="AZ488" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722962</t>
+        </is>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
@@ -50127,6 +52567,11 @@
         </is>
       </c>
       <c r="AY489" t="inlineStr"/>
+      <c r="AZ489" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722963</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="n">
@@ -50229,6 +52674,11 @@
         </is>
       </c>
       <c r="AY490" t="inlineStr"/>
+      <c r="AZ490" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722964</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
@@ -50331,6 +52781,11 @@
         </is>
       </c>
       <c r="AY491" t="inlineStr"/>
+      <c r="AZ491" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722965</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="n">
@@ -50433,6 +52888,11 @@
         </is>
       </c>
       <c r="AY492" t="inlineStr"/>
+      <c r="AZ492" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722966</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="n">
@@ -50535,6 +52995,11 @@
         </is>
       </c>
       <c r="AY493" t="inlineStr"/>
+      <c r="AZ493" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722967</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="n">
@@ -50637,6 +53102,11 @@
         </is>
       </c>
       <c r="AY494" t="inlineStr"/>
+      <c r="AZ494" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722968</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
@@ -50739,6 +53209,11 @@
         </is>
       </c>
       <c r="AY495" t="inlineStr"/>
+      <c r="AZ495" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722969</t>
+        </is>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
@@ -50841,6 +53316,11 @@
         </is>
       </c>
       <c r="AY496" t="inlineStr"/>
+      <c r="AZ496" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722970</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="n">
@@ -50943,6 +53423,11 @@
         </is>
       </c>
       <c r="AY497" t="inlineStr"/>
+      <c r="AZ497" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722971</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="n">
@@ -51045,6 +53530,11 @@
         </is>
       </c>
       <c r="AY498" t="inlineStr"/>
+      <c r="AZ498" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722972</t>
+        </is>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="n">
@@ -51147,6 +53637,11 @@
         </is>
       </c>
       <c r="AY499" t="inlineStr"/>
+      <c r="AZ499" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722973</t>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="n">
@@ -51249,6 +53744,11 @@
         </is>
       </c>
       <c r="AY500" t="inlineStr"/>
+      <c r="AZ500" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722974</t>
+        </is>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="n">
@@ -51351,6 +53851,11 @@
         </is>
       </c>
       <c r="AY501" t="inlineStr"/>
+      <c r="AZ501" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722975</t>
+        </is>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="n">
@@ -51453,6 +53958,11 @@
         </is>
       </c>
       <c r="AY502" t="inlineStr"/>
+      <c r="AZ502" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722976</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="n">
@@ -51555,6 +54065,11 @@
         </is>
       </c>
       <c r="AY503" t="inlineStr"/>
+      <c r="AZ503" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722977</t>
+        </is>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="n">
@@ -51657,6 +54172,11 @@
         </is>
       </c>
       <c r="AY504" t="inlineStr"/>
+      <c r="AZ504" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722984</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="n">
@@ -51759,6 +54279,11 @@
         </is>
       </c>
       <c r="AY505" t="inlineStr"/>
+      <c r="AZ505" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722985</t>
+        </is>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="n">
@@ -51861,6 +54386,11 @@
         </is>
       </c>
       <c r="AY506" t="inlineStr"/>
+      <c r="AZ506" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722986</t>
+        </is>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="n">
@@ -51963,6 +54493,11 @@
         </is>
       </c>
       <c r="AY507" t="inlineStr"/>
+      <c r="AZ507" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722987</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="n">
@@ -52065,6 +54600,11 @@
         </is>
       </c>
       <c r="AY508" t="inlineStr"/>
+      <c r="AZ508" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722988</t>
+        </is>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="n">
@@ -52167,6 +54707,11 @@
         </is>
       </c>
       <c r="AY509" t="inlineStr"/>
+      <c r="AZ509" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722989</t>
+        </is>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="n">
@@ -52269,6 +54814,11 @@
         </is>
       </c>
       <c r="AY510" t="inlineStr"/>
+      <c r="AZ510" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722990</t>
+        </is>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="n">
@@ -52371,6 +54921,11 @@
         </is>
       </c>
       <c r="AY511" t="inlineStr"/>
+      <c r="AZ511" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722991</t>
+        </is>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="n">
@@ -52473,6 +55028,11 @@
         </is>
       </c>
       <c r="AY512" t="inlineStr"/>
+      <c r="AZ512" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722992</t>
+        </is>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="n">
@@ -52575,6 +55135,11 @@
         </is>
       </c>
       <c r="AY513" t="inlineStr"/>
+      <c r="AZ513" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722993</t>
+        </is>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="n">
@@ -52677,6 +55242,11 @@
         </is>
       </c>
       <c r="AY514" t="inlineStr"/>
+      <c r="AZ514" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722994</t>
+        </is>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="n">
@@ -52779,6 +55349,11 @@
         </is>
       </c>
       <c r="AY515" t="inlineStr"/>
+      <c r="AZ515" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722995</t>
+        </is>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="n">
@@ -52881,6 +55456,11 @@
         </is>
       </c>
       <c r="AY516" t="inlineStr"/>
+      <c r="AZ516" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722996</t>
+        </is>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="n">
@@ -52983,6 +55563,11 @@
         </is>
       </c>
       <c r="AY517" t="inlineStr"/>
+      <c r="AZ517" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722997</t>
+        </is>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="n">
@@ -53085,6 +55670,11 @@
         </is>
       </c>
       <c r="AY518" t="inlineStr"/>
+      <c r="AZ518" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722998</t>
+        </is>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="n">
@@ -53187,6 +55777,11 @@
         </is>
       </c>
       <c r="AY519" t="inlineStr"/>
+      <c r="AZ519" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722999</t>
+        </is>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="n">
@@ -53289,6 +55884,11 @@
         </is>
       </c>
       <c r="AY520" t="inlineStr"/>
+      <c r="AZ520" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723000</t>
+        </is>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="n">
@@ -53391,6 +55991,11 @@
         </is>
       </c>
       <c r="AY521" t="inlineStr"/>
+      <c r="AZ521" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723001</t>
+        </is>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="n">
@@ -53493,6 +56098,11 @@
         </is>
       </c>
       <c r="AY522" t="inlineStr"/>
+      <c r="AZ522" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723002</t>
+        </is>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="n">
@@ -53595,6 +56205,11 @@
         </is>
       </c>
       <c r="AY523" t="inlineStr"/>
+      <c r="AZ523" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723003</t>
+        </is>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="n">
@@ -53697,6 +56312,11 @@
         </is>
       </c>
       <c r="AY524" t="inlineStr"/>
+      <c r="AZ524" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723004</t>
+        </is>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="n">
@@ -53799,6 +56419,11 @@
         </is>
       </c>
       <c r="AY525" t="inlineStr"/>
+      <c r="AZ525" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723005</t>
+        </is>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="n">
@@ -53901,6 +56526,11 @@
         </is>
       </c>
       <c r="AY526" t="inlineStr"/>
+      <c r="AZ526" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723006</t>
+        </is>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="n">
@@ -54003,6 +56633,11 @@
         </is>
       </c>
       <c r="AY527" t="inlineStr"/>
+      <c r="AZ527" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723007</t>
+        </is>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="n">
@@ -54105,6 +56740,11 @@
         </is>
       </c>
       <c r="AY528" t="inlineStr"/>
+      <c r="AZ528" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723008</t>
+        </is>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="n">
@@ -54207,6 +56847,11 @@
         </is>
       </c>
       <c r="AY529" t="inlineStr"/>
+      <c r="AZ529" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723009</t>
+        </is>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="n">
@@ -54309,6 +56954,11 @@
         </is>
       </c>
       <c r="AY530" t="inlineStr"/>
+      <c r="AZ530" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723010</t>
+        </is>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="n">
@@ -54411,6 +57061,11 @@
         </is>
       </c>
       <c r="AY531" t="inlineStr"/>
+      <c r="AZ531" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723011</t>
+        </is>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="n">
@@ -54519,6 +57174,11 @@
         </is>
       </c>
       <c r="AY532" t="inlineStr"/>
+      <c r="AZ532" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729077</t>
+        </is>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="n">
@@ -54636,6 +57296,11 @@
         </is>
       </c>
       <c r="AY533" t="inlineStr"/>
+      <c r="AZ533" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729087</t>
+        </is>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="n">
@@ -54753,6 +57418,11 @@
         </is>
       </c>
       <c r="AY534" t="inlineStr"/>
+      <c r="AZ534" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729088</t>
+        </is>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="n">
@@ -54870,6 +57540,11 @@
         </is>
       </c>
       <c r="AY535" t="inlineStr"/>
+      <c r="AZ535" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729089</t>
+        </is>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="n">
@@ -54982,6 +57657,11 @@
         </is>
       </c>
       <c r="AY536" t="inlineStr"/>
+      <c r="AZ536" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127730354</t>
+        </is>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="n">
@@ -55089,6 +57769,11 @@
         </is>
       </c>
       <c r="AY537" t="inlineStr"/>
+      <c r="AZ537" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127730365</t>
+        </is>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="n">
@@ -55197,6 +57882,11 @@
         </is>
       </c>
       <c r="AY538" t="inlineStr"/>
+      <c r="AZ538" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736013</t>
+        </is>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="n">
@@ -55300,6 +57990,11 @@
         </is>
       </c>
       <c r="AY539" t="inlineStr"/>
+      <c r="AZ539" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127795366</t>
+        </is>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="n">
@@ -55398,6 +58093,11 @@
         </is>
       </c>
       <c r="AY540" t="inlineStr"/>
+      <c r="AZ540" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722859</t>
+        </is>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="n">
@@ -55495,6 +58195,11 @@
         </is>
       </c>
       <c r="AY541" t="inlineStr"/>
+      <c r="AZ541" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722924</t>
+        </is>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="n">
@@ -55592,6 +58297,11 @@
         </is>
       </c>
       <c r="AY542" t="inlineStr"/>
+      <c r="AZ542" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722893</t>
+        </is>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="n">
@@ -55689,6 +58399,11 @@
         </is>
       </c>
       <c r="AY543" t="inlineStr"/>
+      <c r="AZ543" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722894</t>
+        </is>
+      </c>
     </row>
     <row r="544">
       <c r="A544" t="n">
@@ -55798,6 +58513,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2016 Dalarna</t>
         </is>
       </c>
+      <c r="AZ544" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60771999</t>
+        </is>
+      </c>
     </row>
     <row r="545">
       <c r="A545" t="n">
@@ -55903,6 +58623,11 @@
         </is>
       </c>
       <c r="AY545" t="inlineStr"/>
+      <c r="AZ545" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60827298</t>
+        </is>
+      </c>
     </row>
     <row r="546">
       <c r="A546" t="n">
@@ -56009,6 +58734,11 @@
         </is>
       </c>
       <c r="AY546" t="inlineStr"/>
+      <c r="AZ546" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127608215</t>
+        </is>
+      </c>
     </row>
     <row r="547">
       <c r="A547" t="n">
@@ -56109,6 +58839,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2016 Dalarna</t>
         </is>
       </c>
+      <c r="AZ547" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60772015</t>
+        </is>
+      </c>
     </row>
     <row r="548">
       <c r="A548" t="n">
@@ -56217,6 +58952,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2016 Dalarna</t>
         </is>
       </c>
+      <c r="AZ548" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60771923</t>
+        </is>
+      </c>
     </row>
     <row r="549">
       <c r="A549" t="n">
@@ -56317,6 +59057,11 @@
       <c r="AY549" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2016 Dalarna</t>
+        </is>
+      </c>
+      <c r="AZ549" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61497950</t>
         </is>
       </c>
     </row>
@@ -56420,6 +59165,11 @@
         </is>
       </c>
       <c r="AY550" t="inlineStr"/>
+      <c r="AZ550" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127608048</t>
+        </is>
+      </c>
     </row>
     <row r="551">
       <c r="A551" t="n">
@@ -56521,6 +59271,11 @@
         </is>
       </c>
       <c r="AY551" t="inlineStr"/>
+      <c r="AZ551" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127618557</t>
+        </is>
+      </c>
     </row>
     <row r="552">
       <c r="A552" t="n">
@@ -56623,6 +59378,11 @@
         </is>
       </c>
       <c r="AY552" t="inlineStr"/>
+      <c r="AZ552" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723035</t>
+        </is>
+      </c>
     </row>
     <row r="553">
       <c r="A553" t="n">
@@ -56720,6 +59480,11 @@
         </is>
       </c>
       <c r="AY553" t="inlineStr"/>
+      <c r="AZ553" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723036</t>
+        </is>
+      </c>
     </row>
     <row r="554">
       <c r="A554" t="n">
@@ -56817,6 +59582,11 @@
         </is>
       </c>
       <c r="AY554" t="inlineStr"/>
+      <c r="AZ554" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723042</t>
+        </is>
+      </c>
     </row>
     <row r="555">
       <c r="A555" t="n">
@@ -56914,6 +59684,11 @@
         </is>
       </c>
       <c r="AY555" t="inlineStr"/>
+      <c r="AZ555" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723043</t>
+        </is>
+      </c>
     </row>
     <row r="556">
       <c r="A556" t="n">
@@ -57011,6 +59786,11 @@
         </is>
       </c>
       <c r="AY556" t="inlineStr"/>
+      <c r="AZ556" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723044</t>
+        </is>
+      </c>
     </row>
     <row r="557">
       <c r="A557" t="n">
@@ -57108,6 +59888,11 @@
         </is>
       </c>
       <c r="AY557" t="inlineStr"/>
+      <c r="AZ557" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723045</t>
+        </is>
+      </c>
     </row>
     <row r="558">
       <c r="A558" t="n">
@@ -57205,6 +59990,11 @@
         </is>
       </c>
       <c r="AY558" t="inlineStr"/>
+      <c r="AZ558" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723046</t>
+        </is>
+      </c>
     </row>
     <row r="559">
       <c r="A559" t="n">
@@ -57302,6 +60092,11 @@
         </is>
       </c>
       <c r="AY559" t="inlineStr"/>
+      <c r="AZ559" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723047</t>
+        </is>
+      </c>
     </row>
     <row r="560">
       <c r="A560" t="n">
@@ -57399,6 +60194,11 @@
         </is>
       </c>
       <c r="AY560" t="inlineStr"/>
+      <c r="AZ560" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723048</t>
+        </is>
+      </c>
     </row>
     <row r="561">
       <c r="A561" t="n">
@@ -57496,6 +60296,11 @@
         </is>
       </c>
       <c r="AY561" t="inlineStr"/>
+      <c r="AZ561" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723049</t>
+        </is>
+      </c>
     </row>
     <row r="562">
       <c r="A562" t="n">
@@ -57604,6 +60409,11 @@
         </is>
       </c>
       <c r="AY562" t="inlineStr"/>
+      <c r="AZ562" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729084</t>
+        </is>
+      </c>
     </row>
     <row r="563">
       <c r="A563" t="n">
@@ -57712,6 +60522,11 @@
         </is>
       </c>
       <c r="AY563" t="inlineStr"/>
+      <c r="AZ563" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729085</t>
+        </is>
+      </c>
     </row>
     <row r="564">
       <c r="A564" t="n">
@@ -57819,6 +60634,11 @@
         </is>
       </c>
       <c r="AY564" t="inlineStr"/>
+      <c r="AZ564" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736011</t>
+        </is>
+      </c>
     </row>
     <row r="565">
       <c r="A565" t="n">
@@ -57926,6 +60746,11 @@
         </is>
       </c>
       <c r="AY565" t="inlineStr"/>
+      <c r="AZ565" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736012</t>
+        </is>
+      </c>
     </row>
     <row r="566">
       <c r="A566" t="n">
@@ -58033,6 +60858,11 @@
         </is>
       </c>
       <c r="AY566" t="inlineStr"/>
+      <c r="AZ566" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127785475</t>
+        </is>
+      </c>
     </row>
     <row r="567">
       <c r="A567" t="n">
@@ -58134,6 +60964,11 @@
         </is>
       </c>
       <c r="AY567" t="inlineStr"/>
+      <c r="AZ567" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127795442</t>
+        </is>
+      </c>
     </row>
     <row r="568">
       <c r="A568" t="n">
@@ -58235,6 +61070,11 @@
         </is>
       </c>
       <c r="AY568" t="inlineStr"/>
+      <c r="AZ568" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127795592</t>
+        </is>
+      </c>
     </row>
     <row r="569">
       <c r="A569" t="n">
@@ -58336,6 +61176,11 @@
         </is>
       </c>
       <c r="AY569" t="inlineStr"/>
+      <c r="AZ569" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127795733</t>
+        </is>
+      </c>
     </row>
     <row r="570">
       <c r="A570" t="n">
@@ -58437,6 +61282,11 @@
         </is>
       </c>
       <c r="AY570" t="inlineStr"/>
+      <c r="AZ570" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127795748</t>
+        </is>
+      </c>
     </row>
     <row r="571">
       <c r="A571" t="n">
@@ -58539,6 +61389,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2016 Dalarna</t>
         </is>
       </c>
+      <c r="AZ571" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61497946</t>
+        </is>
+      </c>
     </row>
     <row r="572">
       <c r="A572" t="n">
@@ -58641,6 +61496,11 @@
         </is>
       </c>
       <c r="AY572" t="inlineStr"/>
+      <c r="AZ572" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722854</t>
+        </is>
+      </c>
     </row>
     <row r="573">
       <c r="A573" t="n">
@@ -58738,6 +61598,11 @@
         </is>
       </c>
       <c r="AY573" t="inlineStr"/>
+      <c r="AZ573" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722856</t>
+        </is>
+      </c>
     </row>
     <row r="574">
       <c r="A574" t="n">
@@ -58835,6 +61700,11 @@
         </is>
       </c>
       <c r="AY574" t="inlineStr"/>
+      <c r="AZ574" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722857</t>
+        </is>
+      </c>
     </row>
     <row r="575">
       <c r="A575" t="n">
@@ -58942,6 +61812,11 @@
         </is>
       </c>
       <c r="AY575" t="inlineStr"/>
+      <c r="AZ575" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736005</t>
+        </is>
+      </c>
     </row>
     <row r="576">
       <c r="A576" t="n">
@@ -59043,8 +61918,590 @@
         </is>
       </c>
       <c r="AY576" t="inlineStr"/>
+      <c r="AZ576" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127795740</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ271" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ272" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ273" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ274" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ275" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ276" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ277" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ279" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ280" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ281" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ282" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ283" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ284" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ285" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ286" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ287" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ288" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ289" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ290" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ291" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ292" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ293" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ294" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ295" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ296" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ297" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ298" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ299" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ300" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ301" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ302" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ303" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ304" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ305" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ306" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ307" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ308" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ309" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ310" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ311" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ312" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ313" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ314" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ315" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ316" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ317" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ318" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ319" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ320" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ321" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ322" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ323" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ324" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ325" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ326" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ327" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ328" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ329" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ330" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ331" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ332" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ333" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ334" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ335" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ336" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ337" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ338" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ339" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ340" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ341" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ342" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ343" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ344" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ345" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ346" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ347" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ348" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ349" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ350" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ351" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ352" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ353" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ354" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ355" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ356" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ357" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ358" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ359" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ360" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ361" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ362" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ363" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ364" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ365" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ366" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ367" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ368" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ369" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ370" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ371" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ372" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ373" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ374" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ375" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ376" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ377" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ378" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ379" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ380" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ381" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ382" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ383" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ384" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ385" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ386" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ387" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ388" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ389" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ390" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ391" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ392" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ393" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ394" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ395" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ396" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ397" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ398" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ399" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ400" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ401" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ402" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ403" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ404" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ405" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ406" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ407" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ408" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ409" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ410" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ411" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ412" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ413" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ414" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ415" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ416" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ417" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ418" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ419" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ420" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ421" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ422" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ423" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ424" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ425" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ426" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ427" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ428" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ429" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ430" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ431" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ432" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ433" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ434" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ435" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ436" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ437" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ438" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ439" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ440" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ441" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ442" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ443" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ444" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ445" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ446" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ447" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ448" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ449" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ450" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ451" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ452" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ453" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ454" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ455" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ456" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ457" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ458" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ459" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ460" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ461" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ462" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ463" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ464" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ465" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ466" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ467" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ468" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ469" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ470" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ471" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ472" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ473" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ474" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ475" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ476" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ477" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ478" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ479" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ480" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ481" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ482" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ483" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ484" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ485" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ486" r:id="rId485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ487" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ488" r:id="rId487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ489" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ490" r:id="rId489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ491" r:id="rId490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ492" r:id="rId491"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ493" r:id="rId492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ494" r:id="rId493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ495" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ496" r:id="rId495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ497" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ498" r:id="rId497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ499" r:id="rId498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ500" r:id="rId499"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ501" r:id="rId500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ502" r:id="rId501"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ503" r:id="rId502"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ504" r:id="rId503"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ505" r:id="rId504"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ506" r:id="rId505"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ507" r:id="rId506"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ508" r:id="rId507"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ509" r:id="rId508"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ510" r:id="rId509"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ511" r:id="rId510"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ512" r:id="rId511"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ513" r:id="rId512"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ514" r:id="rId513"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ515" r:id="rId514"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ516" r:id="rId515"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ517" r:id="rId516"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ518" r:id="rId517"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ519" r:id="rId518"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ520" r:id="rId519"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ521" r:id="rId520"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ522" r:id="rId521"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ523" r:id="rId522"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ524" r:id="rId523"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ525" r:id="rId524"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ526" r:id="rId525"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ527" r:id="rId526"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ528" r:id="rId527"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ529" r:id="rId528"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ530" r:id="rId529"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ531" r:id="rId530"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ532" r:id="rId531"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ533" r:id="rId532"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ534" r:id="rId533"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ535" r:id="rId534"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ536" r:id="rId535"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ537" r:id="rId536"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ538" r:id="rId537"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ539" r:id="rId538"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ540" r:id="rId539"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ541" r:id="rId540"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ542" r:id="rId541"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ543" r:id="rId542"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ544" r:id="rId543"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ545" r:id="rId544"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ546" r:id="rId545"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ547" r:id="rId546"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ548" r:id="rId547"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ549" r:id="rId548"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ550" r:id="rId549"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ551" r:id="rId550"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ552" r:id="rId551"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ553" r:id="rId552"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ554" r:id="rId553"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ555" r:id="rId554"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ556" r:id="rId555"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ557" r:id="rId556"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ558" r:id="rId557"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ559" r:id="rId558"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ560" r:id="rId559"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ561" r:id="rId560"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ562" r:id="rId561"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ563" r:id="rId562"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ564" r:id="rId563"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ565" r:id="rId564"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ566" r:id="rId565"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ567" r:id="rId566"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ568" r:id="rId567"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ569" r:id="rId568"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ570" r:id="rId569"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ571" r:id="rId570"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ572" r:id="rId571"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ573" r:id="rId572"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ574" r:id="rId573"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ575" r:id="rId574"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ576" r:id="rId575"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>